--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Desktop/mortality_data_test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B21F7E47-1DB9-F34D-A77F-B82F070D5355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68FF09D-81C0-2641-A071-F5EF229CF973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1760" yWindow="-19280" windowWidth="27640" windowHeight="15680" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="14900" windowHeight="16980" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="keywords" sheetId="2" r:id="rId1"/>
+    <sheet name="potential additional keywords" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="234">
   <si>
     <t>DIABETES</t>
   </si>
@@ -5654,4 +5655,61 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19A0243-1058-594D-AF94-4FF1EBCCFA95}">
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68FF09D-81C0-2641-A071-F5EF229CF973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E89BA9-0FBB-D34E-B0FA-D153F4F49E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="14900" windowHeight="16980" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="14900" windowHeight="17260" activeTab="1" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="keywords" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="307">
   <si>
     <t>DIABETES</t>
   </si>
@@ -739,13 +739,232 @@
   </si>
   <si>
     <t>SUDORS</t>
+  </si>
+  <si>
+    <t>5-FLOURO-ADB TOXICITY</t>
+  </si>
+  <si>
+    <t>5F-ADB-TOXICITY</t>
+  </si>
+  <si>
+    <t>ACUTE 5-FLUORO-ADB TOXICITY</t>
+  </si>
+  <si>
+    <t>RESPIRATORY FAILURE</t>
+  </si>
+  <si>
+    <t>LUKEMIA</t>
+  </si>
+  <si>
+    <t>LEUKEMIA</t>
+  </si>
+  <si>
+    <t>RESPIRATORY FAILURE WITH HYPOXIA</t>
+  </si>
+  <si>
+    <t>ADB-FUBINACA TOXICITY</t>
+  </si>
+  <si>
+    <t>ALS</t>
+  </si>
+  <si>
+    <t>DEMENTIS</t>
+  </si>
+  <si>
+    <t>ALZHEIMERS</t>
+  </si>
+  <si>
+    <t>AMYLOIDOSIS</t>
+  </si>
+  <si>
+    <t>HANGING</t>
+  </si>
+  <si>
+    <t>ASHD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEPATOCELLULAR CA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUICIDE BY HANGING </t>
+  </si>
+  <si>
+    <t>COPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA OF LUNG </t>
+  </si>
+  <si>
+    <t>MULTIPLE MYELOMA</t>
+  </si>
+  <si>
+    <t>CVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACUTE RESPIRATORY FAILURE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">END STAGE RENAL DISEASE </t>
+  </si>
+  <si>
+    <t>HYPOVOLEMIC SHOCK</t>
+  </si>
+  <si>
+    <t>CA OF PANCREAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIVER FIALURE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPOXIC RESPIRATORY FAILURE </t>
+  </si>
+  <si>
+    <t>METASTATIC MELANOMA</t>
+  </si>
+  <si>
+    <t>CA OF COLON</t>
+  </si>
+  <si>
+    <t>LIGATURE HANGING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUICIDE HANGING </t>
+  </si>
+  <si>
+    <t>END STAGE COPD</t>
+  </si>
+  <si>
+    <t>INTRACRANIAL HEMORRHAGE</t>
+  </si>
+  <si>
+    <t>INTRACEREBRAL HEMORRHAGE</t>
+  </si>
+  <si>
+    <t>ESRD</t>
+  </si>
+  <si>
+    <t>GI BLEED</t>
+  </si>
+  <si>
+    <t>PULMONARY FIBROSIS</t>
+  </si>
+  <si>
+    <t>ACUTE HYPOXIC RESPIRATORY FAILURE</t>
+  </si>
+  <si>
+    <t>SUICIDE/HANGING</t>
+  </si>
+  <si>
+    <t>ACUTE MYELOGENOUS LEUKEMIA</t>
+  </si>
+  <si>
+    <t>ASHCVD</t>
+  </si>
+  <si>
+    <t>GASTROINTESTINAL HEMORRHAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**natural causes? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACUTE MYELOID LEUKEMIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEREBROVASCULAR ACCIDENT </t>
+  </si>
+  <si>
+    <t>RESPIRATORY ARREST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACUTE RESPIRATORY FAILURE WITH HYPOXIA </t>
+  </si>
+  <si>
+    <t>CA OF PROSTATE</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>END STATE DEMENTIA</t>
+  </si>
+  <si>
+    <t>HEPATIC FAILURE</t>
+  </si>
+  <si>
+    <t>ACUTE LYMPHOBLASTIC LEUKEMIA</t>
+  </si>
+  <si>
+    <t>COMPLICATIONS OF SMALL BOWEL OBSTRUCTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PULMONARY EDEMA </t>
+  </si>
+  <si>
+    <t>SUICIDE-HANGING</t>
+  </si>
+  <si>
+    <t>AMYOTROPHIC LATERAL SCLEROSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA OF ESOPHAGUS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHRONIC LOWER RESPIRATORY DISEASE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEMORRHAGIC SHOCK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDIOPATHIC PULMONARY FIBROSIS </t>
+  </si>
+  <si>
+    <t>RESPIRATORY DISTRESS</t>
+  </si>
+  <si>
+    <t>ACUTE LEUKEMIA</t>
+  </si>
+  <si>
+    <t>ACUTE MI</t>
+  </si>
+  <si>
+    <t>ASCVD</t>
+  </si>
+  <si>
+    <t>ASPHXIA</t>
+  </si>
+  <si>
+    <t>CA OF RECTUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLICATIONS OF MULTIPLE MELOMA </t>
+  </si>
+  <si>
+    <t>ESLD</t>
+  </si>
+  <si>
+    <t>EXSANGUINATION</t>
+  </si>
+  <si>
+    <t>HEPATORENAL SYNDROME</t>
+  </si>
+  <si>
+    <t>MULTI-ORGAN FAILURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBDURAL HEMATOMA </t>
+  </si>
+  <si>
+    <t>SUICIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*currently stopped at line 69 (5 n or more) </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,6 +985,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Grande"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -788,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -800,6 +1025,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5659,7 +5885,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19A0243-1058-594D-AF94-4FF1EBCCFA95}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -5674,7 +5900,7 @@
     <col min="11" max="11" width="8.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>220</v>
       </c>
@@ -5707,6 +5933,341 @@
       </c>
       <c r="K1" s="4" t="s">
         <v>233</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="M3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="M4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="M5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>287</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F8" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F9" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F10" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F11" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F12" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F13" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F14" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F15" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F16" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F17" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F18" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F19" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F20" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F21" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F22" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F23" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F24" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F25" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F26" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="27" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F27" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="28" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F28" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F29" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F30" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F31" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F32" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F33" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F34" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F35" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F36" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F37" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F38" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F39" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F40" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F41" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F42" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F43" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F44" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F45" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F46" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F47" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F48" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F49" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F50" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F51" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F52" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F53" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F54" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F55" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F56" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F57" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="58" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F58" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F59" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E89BA9-0FBB-D34E-B0FA-D153F4F49E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1620E937-DA99-6A40-9403-CA8841F7F218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="14900" windowHeight="17260" activeTab="1" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="keywords" sheetId="2" r:id="rId1"/>
     <sheet name="potential additional keywords" sheetId="3" r:id="rId2"/>
+    <sheet name="keywords_additional" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="309">
   <si>
     <t>DIABETES</t>
   </si>
@@ -958,6 +959,12 @@
   </si>
   <si>
     <t xml:space="preserve">*currently stopped at line 69 (5 n or more) </t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>5-FLUORO-ADB TOXICITY</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1747,9 @@
       <c r="F14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>307</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="K14" s="1" t="s">
@@ -5940,7 +5949,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>234</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
         <v>246</v>
@@ -6269,6 +6278,4683 @@
       <c r="F59" s="1" t="s">
         <v>304</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08F483A4-8058-DB4E-A46F-535DD3F5F342}">
+  <dimension ref="A1:K355"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" customWidth="1"/>
+    <col min="3" max="3" width="43.5" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" t="s">
+        <v>246</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" t="s">
+        <v>262</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="K31" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" t="s">
+        <v>271</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" t="s">
+        <v>287</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="K38" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="K39" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>234</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>236</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="F142" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
+      <c r="E143" s="1"/>
+      <c r="F143" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="1"/>
+      <c r="F145" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="F146" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
+      <c r="F147" s="1"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1"/>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A158" s="1"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="F158" s="1"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="1"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="1"/>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+      <c r="E177" s="1"/>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+      <c r="G180" s="1"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+      <c r="G181" s="1"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="1"/>
+      <c r="G183" s="1"/>
+      <c r="H183" s="1"/>
+      <c r="I183" s="1"/>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
+      <c r="H184" s="1"/>
+      <c r="I184" s="1"/>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="1"/>
+      <c r="G185" s="1"/>
+      <c r="H185" s="1"/>
+      <c r="I185" s="1"/>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="1"/>
+      <c r="G186" s="1"/>
+      <c r="H186" s="1"/>
+      <c r="I186" s="1"/>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="1"/>
+      <c r="G187" s="1"/>
+      <c r="H187" s="1"/>
+      <c r="I187" s="1"/>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+      <c r="F196" s="1"/>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1"/>
+      <c r="I196" s="1"/>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1"/>
+      <c r="F197" s="1"/>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+      <c r="F198" s="1"/>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
+      <c r="E200" s="1"/>
+      <c r="F200" s="1"/>
+      <c r="G200" s="1"/>
+      <c r="H200" s="1"/>
+      <c r="I200" s="1"/>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+      <c r="F201" s="1"/>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="1"/>
+      <c r="F202" s="1"/>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1"/>
+      <c r="I202" s="1"/>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+      <c r="E203" s="1"/>
+      <c r="F203" s="1"/>
+      <c r="G203" s="1"/>
+      <c r="H203" s="1"/>
+      <c r="I203" s="1"/>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+      <c r="E204" s="1"/>
+      <c r="F204" s="1"/>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1"/>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+      <c r="E205" s="1"/>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1"/>
+      <c r="H205" s="1"/>
+      <c r="I205" s="1"/>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="1"/>
+      <c r="F206" s="1"/>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+      <c r="I206" s="1"/>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+      <c r="E207" s="1"/>
+      <c r="F207" s="1"/>
+      <c r="G207" s="1"/>
+      <c r="H207" s="1"/>
+      <c r="I207" s="1"/>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
+      <c r="E208" s="1"/>
+      <c r="F208" s="1"/>
+      <c r="G208" s="1"/>
+      <c r="H208" s="1"/>
+      <c r="I208" s="1"/>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
+      <c r="E209" s="1"/>
+      <c r="F209" s="1"/>
+      <c r="G209" s="1"/>
+      <c r="H209" s="1"/>
+      <c r="I209" s="1"/>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+      <c r="E210" s="1"/>
+      <c r="F210" s="1"/>
+      <c r="G210" s="1"/>
+      <c r="H210" s="1"/>
+      <c r="I210" s="1"/>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+      <c r="E211" s="1"/>
+      <c r="F211" s="1"/>
+      <c r="G211" s="1"/>
+      <c r="H211" s="1"/>
+      <c r="I211" s="1"/>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+      <c r="E212" s="1"/>
+      <c r="F212" s="1"/>
+      <c r="G212" s="1"/>
+      <c r="H212" s="1"/>
+      <c r="I212" s="1"/>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A213" s="1"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
+      <c r="E213" s="1"/>
+      <c r="F213" s="1"/>
+      <c r="G213" s="1"/>
+      <c r="H213" s="1"/>
+      <c r="I213" s="1"/>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="1"/>
+      <c r="F214" s="1"/>
+      <c r="G214" s="1"/>
+      <c r="H214" s="1"/>
+      <c r="I214" s="1"/>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A215" s="1"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
+      <c r="E215" s="1"/>
+      <c r="F215" s="1"/>
+      <c r="G215" s="1"/>
+      <c r="H215" s="1"/>
+      <c r="I215" s="1"/>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+      <c r="E216" s="1"/>
+      <c r="F216" s="1"/>
+      <c r="G216" s="1"/>
+      <c r="H216" s="1"/>
+      <c r="I216" s="1"/>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
+      <c r="E217" s="1"/>
+      <c r="F217" s="1"/>
+      <c r="G217" s="1"/>
+      <c r="H217" s="1"/>
+      <c r="I217" s="1"/>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
+      <c r="E218" s="1"/>
+      <c r="F218" s="1"/>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1"/>
+      <c r="I218" s="1"/>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
+      <c r="E220" s="1"/>
+      <c r="F220" s="1"/>
+      <c r="G220" s="1"/>
+      <c r="H220" s="1"/>
+      <c r="I220" s="1"/>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
+      <c r="E222" s="1"/>
+      <c r="F222" s="1"/>
+      <c r="G222" s="1"/>
+      <c r="H222" s="1"/>
+      <c r="I222" s="1"/>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+      <c r="E223" s="1"/>
+      <c r="F223" s="1"/>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A224" s="1"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+      <c r="E224" s="1"/>
+      <c r="F224" s="1"/>
+      <c r="G224" s="1"/>
+      <c r="H224" s="1"/>
+      <c r="I224" s="1"/>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
+      <c r="E225" s="1"/>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1"/>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
+      <c r="E226" s="1"/>
+      <c r="F226" s="1"/>
+      <c r="G226" s="1"/>
+      <c r="H226" s="1"/>
+      <c r="I226" s="1"/>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
+      <c r="E227" s="1"/>
+      <c r="F227" s="1"/>
+      <c r="G227" s="1"/>
+      <c r="H227" s="1"/>
+      <c r="I227" s="1"/>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1"/>
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
+      <c r="E229" s="1"/>
+      <c r="F229" s="1"/>
+      <c r="G229" s="1"/>
+      <c r="H229" s="1"/>
+      <c r="I229" s="1"/>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
+      <c r="E230" s="1"/>
+      <c r="F230" s="1"/>
+      <c r="G230" s="1"/>
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+      <c r="I231" s="1"/>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+      <c r="E232" s="1"/>
+      <c r="F232" s="1"/>
+      <c r="G232" s="1"/>
+      <c r="H232" s="1"/>
+      <c r="I232" s="1"/>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+      <c r="E233" s="1"/>
+      <c r="F233" s="1"/>
+      <c r="G233" s="1"/>
+      <c r="H233" s="1"/>
+      <c r="I233" s="1"/>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1"/>
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+      <c r="F236" s="1"/>
+      <c r="G236" s="1"/>
+      <c r="H236" s="1"/>
+      <c r="I236" s="1"/>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+      <c r="F240" s="1"/>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+      <c r="F241" s="1"/>
+      <c r="G241" s="1"/>
+      <c r="H241" s="1"/>
+      <c r="I241" s="1"/>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+      <c r="E242" s="1"/>
+      <c r="F242" s="1"/>
+      <c r="G242" s="1"/>
+      <c r="H242" s="1"/>
+      <c r="I242" s="1"/>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1"/>
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
+      <c r="G244" s="1"/>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1"/>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+      <c r="E245" s="1"/>
+      <c r="F245" s="1"/>
+      <c r="G245" s="1"/>
+      <c r="H245" s="1"/>
+      <c r="I245" s="1"/>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+      <c r="E246" s="1"/>
+      <c r="F246" s="1"/>
+      <c r="G246" s="1"/>
+      <c r="H246" s="1"/>
+      <c r="I246" s="1"/>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+      <c r="E247" s="1"/>
+      <c r="F247" s="1"/>
+      <c r="G247" s="1"/>
+      <c r="H247" s="1"/>
+      <c r="I247" s="1"/>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A248" s="1"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+      <c r="F248" s="1"/>
+      <c r="G248" s="1"/>
+      <c r="H248" s="1"/>
+      <c r="I248" s="1"/>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
+      <c r="G249" s="1"/>
+      <c r="H249" s="1"/>
+      <c r="I249" s="1"/>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
+      <c r="G250" s="1"/>
+      <c r="H250" s="1"/>
+      <c r="I250" s="1"/>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
+      <c r="E251" s="1"/>
+      <c r="F251" s="1"/>
+      <c r="G251" s="1"/>
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+      <c r="F252" s="1"/>
+      <c r="G252" s="1"/>
+      <c r="H252" s="1"/>
+      <c r="I252" s="1"/>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1"/>
+      <c r="F253" s="1"/>
+      <c r="G253" s="1"/>
+      <c r="H253" s="1"/>
+      <c r="I253" s="1"/>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+      <c r="F254" s="1"/>
+      <c r="G254" s="1"/>
+      <c r="H254" s="1"/>
+      <c r="I254" s="1"/>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
+      <c r="E255" s="1"/>
+      <c r="F255" s="1"/>
+      <c r="G255" s="1"/>
+      <c r="H255" s="1"/>
+      <c r="I255" s="1"/>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
+      <c r="G256" s="1"/>
+      <c r="H256" s="1"/>
+      <c r="I256" s="1"/>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A257" s="1"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
+      <c r="E257" s="1"/>
+      <c r="F257" s="1"/>
+      <c r="G257" s="1"/>
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
+      <c r="G258" s="1"/>
+      <c r="H258" s="1"/>
+      <c r="I258" s="1"/>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+      <c r="E259" s="1"/>
+      <c r="F259" s="1"/>
+      <c r="G259" s="1"/>
+      <c r="H259" s="1"/>
+      <c r="I259" s="1"/>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
+      <c r="E260" s="1"/>
+      <c r="F260" s="1"/>
+      <c r="G260" s="1"/>
+      <c r="H260" s="1"/>
+      <c r="I260" s="1"/>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
+      <c r="E261" s="1"/>
+      <c r="F261" s="1"/>
+      <c r="G261" s="1"/>
+      <c r="H261" s="1"/>
+      <c r="I261" s="1"/>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
+      <c r="E262" s="1"/>
+      <c r="F262" s="1"/>
+      <c r="G262" s="1"/>
+      <c r="H262" s="1"/>
+      <c r="I262" s="1"/>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+      <c r="E263" s="1"/>
+      <c r="F263" s="1"/>
+      <c r="G263" s="1"/>
+      <c r="H263" s="1"/>
+      <c r="I263" s="1"/>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A264" s="1"/>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
+      <c r="E264" s="1"/>
+      <c r="F264" s="1"/>
+      <c r="G264" s="1"/>
+      <c r="H264" s="1"/>
+      <c r="I264" s="1"/>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A265" s="1"/>
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
+      <c r="E265" s="1"/>
+      <c r="F265" s="1"/>
+      <c r="G265" s="1"/>
+      <c r="H265" s="1"/>
+      <c r="I265" s="1"/>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A266" s="1"/>
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
+      <c r="E266" s="1"/>
+      <c r="F266" s="1"/>
+      <c r="G266" s="1"/>
+      <c r="H266" s="1"/>
+      <c r="I266" s="1"/>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A267" s="1"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
+      <c r="E267" s="1"/>
+      <c r="F267" s="1"/>
+      <c r="G267" s="1"/>
+      <c r="H267" s="1"/>
+      <c r="I267" s="1"/>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A268" s="1"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
+      <c r="E268" s="1"/>
+      <c r="F268" s="1"/>
+      <c r="G268" s="1"/>
+      <c r="H268" s="1"/>
+      <c r="I268" s="1"/>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A269" s="1"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
+      <c r="E269" s="1"/>
+      <c r="F269" s="1"/>
+      <c r="G269" s="1"/>
+      <c r="H269" s="1"/>
+      <c r="I269" s="1"/>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A270" s="1"/>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
+      <c r="E270" s="1"/>
+      <c r="F270" s="1"/>
+      <c r="G270" s="1"/>
+      <c r="H270" s="1"/>
+      <c r="I270" s="1"/>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A271" s="1"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+      <c r="E271" s="1"/>
+      <c r="F271" s="1"/>
+      <c r="G271" s="1"/>
+      <c r="H271" s="1"/>
+      <c r="I271" s="1"/>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A272" s="1"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+      <c r="E272" s="1"/>
+      <c r="F272" s="1"/>
+      <c r="G272" s="1"/>
+      <c r="H272" s="1"/>
+      <c r="I272" s="1"/>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A273" s="1"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+      <c r="E273" s="1"/>
+      <c r="F273" s="1"/>
+      <c r="G273" s="1"/>
+      <c r="H273" s="1"/>
+      <c r="I273" s="1"/>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A274" s="1"/>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
+      <c r="E274" s="1"/>
+      <c r="F274" s="1"/>
+      <c r="G274" s="1"/>
+      <c r="H274" s="1"/>
+      <c r="I274" s="1"/>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A275" s="1"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+      <c r="E275" s="1"/>
+      <c r="F275" s="1"/>
+      <c r="G275" s="1"/>
+      <c r="H275" s="1"/>
+      <c r="I275" s="1"/>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A276" s="1"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+      <c r="E276" s="1"/>
+      <c r="F276" s="1"/>
+      <c r="G276" s="1"/>
+      <c r="H276" s="1"/>
+      <c r="I276" s="1"/>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A277" s="1"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+      <c r="E277" s="1"/>
+      <c r="F277" s="1"/>
+      <c r="G277" s="1"/>
+      <c r="H277" s="1"/>
+      <c r="I277" s="1"/>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A278" s="1"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+      <c r="E278" s="1"/>
+      <c r="F278" s="1"/>
+      <c r="G278" s="1"/>
+      <c r="H278" s="1"/>
+      <c r="I278" s="1"/>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A279" s="1"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
+      <c r="G279" s="1"/>
+      <c r="H279" s="1"/>
+      <c r="I279" s="1"/>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A280" s="1"/>
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
+      <c r="E280" s="1"/>
+      <c r="F280" s="1"/>
+      <c r="G280" s="1"/>
+      <c r="H280" s="1"/>
+      <c r="I280" s="1"/>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A281" s="1"/>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
+      <c r="E281" s="1"/>
+      <c r="F281" s="1"/>
+      <c r="G281" s="1"/>
+      <c r="H281" s="1"/>
+      <c r="I281" s="1"/>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A282" s="1"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
+      <c r="E282" s="1"/>
+      <c r="F282" s="1"/>
+      <c r="G282" s="1"/>
+      <c r="H282" s="1"/>
+      <c r="I282" s="1"/>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A283" s="1"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
+      <c r="E283" s="1"/>
+      <c r="F283" s="1"/>
+      <c r="G283" s="1"/>
+      <c r="H283" s="1"/>
+      <c r="I283" s="1"/>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A284" s="1"/>
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
+      <c r="E284" s="1"/>
+      <c r="F284" s="1"/>
+      <c r="G284" s="1"/>
+      <c r="H284" s="1"/>
+      <c r="I284" s="1"/>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A285" s="1"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
+      <c r="E285" s="1"/>
+      <c r="F285" s="1"/>
+      <c r="G285" s="1"/>
+      <c r="H285" s="1"/>
+      <c r="I285" s="1"/>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A286" s="1"/>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
+      <c r="E286" s="1"/>
+      <c r="F286" s="1"/>
+      <c r="G286" s="1"/>
+      <c r="H286" s="1"/>
+      <c r="I286" s="1"/>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A287" s="1"/>
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
+      <c r="E287" s="1"/>
+      <c r="F287" s="1"/>
+      <c r="G287" s="1"/>
+      <c r="H287" s="1"/>
+      <c r="I287" s="1"/>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A288" s="1"/>
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
+      <c r="E288" s="1"/>
+      <c r="F288" s="1"/>
+      <c r="G288" s="1"/>
+      <c r="H288" s="1"/>
+      <c r="I288" s="1"/>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A289" s="1"/>
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
+      <c r="E289" s="1"/>
+      <c r="F289" s="1"/>
+      <c r="G289" s="1"/>
+      <c r="H289" s="1"/>
+      <c r="I289" s="1"/>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A290" s="1"/>
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
+      <c r="E290" s="1"/>
+      <c r="F290" s="1"/>
+      <c r="G290" s="1"/>
+      <c r="H290" s="1"/>
+      <c r="I290" s="1"/>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A291" s="1"/>
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
+      <c r="E291" s="1"/>
+      <c r="F291" s="1"/>
+      <c r="G291" s="1"/>
+      <c r="H291" s="1"/>
+      <c r="I291" s="1"/>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A292" s="1"/>
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
+      <c r="E292" s="1"/>
+      <c r="F292" s="1"/>
+      <c r="G292" s="1"/>
+      <c r="H292" s="1"/>
+      <c r="I292" s="1"/>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A293" s="1"/>
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
+      <c r="E293" s="1"/>
+      <c r="F293" s="1"/>
+      <c r="G293" s="1"/>
+      <c r="H293" s="1"/>
+      <c r="I293" s="1"/>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A294" s="1"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
+      <c r="E294" s="1"/>
+      <c r="F294" s="1"/>
+      <c r="G294" s="1"/>
+      <c r="H294" s="1"/>
+      <c r="I294" s="1"/>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A295" s="1"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
+      <c r="E295" s="1"/>
+      <c r="F295" s="1"/>
+      <c r="G295" s="1"/>
+      <c r="H295" s="1"/>
+      <c r="I295" s="1"/>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A296" s="1"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="1"/>
+      <c r="E296" s="1"/>
+      <c r="F296" s="1"/>
+      <c r="G296" s="1"/>
+      <c r="H296" s="1"/>
+      <c r="I296" s="1"/>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A297" s="1"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="1"/>
+      <c r="E297" s="1"/>
+      <c r="F297" s="1"/>
+      <c r="G297" s="1"/>
+      <c r="H297" s="1"/>
+      <c r="I297" s="1"/>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A298" s="1"/>
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="1"/>
+      <c r="E298" s="1"/>
+      <c r="F298" s="1"/>
+      <c r="G298" s="1"/>
+      <c r="H298" s="1"/>
+      <c r="I298" s="1"/>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A299" s="1"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
+      <c r="E299" s="1"/>
+      <c r="F299" s="1"/>
+      <c r="G299" s="1"/>
+      <c r="H299" s="1"/>
+      <c r="I299" s="1"/>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A300" s="1"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="1"/>
+      <c r="E300" s="1"/>
+      <c r="F300" s="1"/>
+      <c r="G300" s="1"/>
+      <c r="H300" s="1"/>
+      <c r="I300" s="1"/>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A301" s="1"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="1"/>
+      <c r="E301" s="1"/>
+      <c r="F301" s="1"/>
+      <c r="G301" s="1"/>
+      <c r="H301" s="1"/>
+      <c r="I301" s="1"/>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A302" s="1"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="1"/>
+      <c r="E302" s="1"/>
+      <c r="F302" s="1"/>
+      <c r="G302" s="1"/>
+      <c r="H302" s="1"/>
+      <c r="I302" s="1"/>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A303" s="1"/>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="1"/>
+      <c r="E303" s="1"/>
+      <c r="F303" s="1"/>
+      <c r="G303" s="1"/>
+      <c r="H303" s="1"/>
+      <c r="I303" s="1"/>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A304" s="1"/>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="1"/>
+      <c r="E304" s="1"/>
+      <c r="F304" s="1"/>
+      <c r="G304" s="1"/>
+      <c r="H304" s="1"/>
+      <c r="I304" s="1"/>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A305" s="1"/>
+      <c r="B305" s="1"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="1"/>
+      <c r="E305" s="1"/>
+      <c r="F305" s="1"/>
+      <c r="G305" s="1"/>
+      <c r="H305" s="1"/>
+      <c r="I305" s="1"/>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A306" s="1"/>
+      <c r="B306" s="1"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="1"/>
+      <c r="E306" s="1"/>
+      <c r="F306" s="1"/>
+      <c r="G306" s="1"/>
+      <c r="H306" s="1"/>
+      <c r="I306" s="1"/>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A307" s="1"/>
+      <c r="B307" s="1"/>
+      <c r="C307" s="1"/>
+      <c r="D307" s="1"/>
+      <c r="E307" s="1"/>
+      <c r="F307" s="1"/>
+      <c r="G307" s="1"/>
+      <c r="H307" s="1"/>
+      <c r="I307" s="1"/>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A308" s="1"/>
+      <c r="B308" s="1"/>
+      <c r="C308" s="1"/>
+      <c r="D308" s="1"/>
+      <c r="E308" s="1"/>
+      <c r="F308" s="1"/>
+      <c r="G308" s="1"/>
+      <c r="H308" s="1"/>
+      <c r="I308" s="1"/>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A309" s="1"/>
+      <c r="B309" s="1"/>
+      <c r="C309" s="1"/>
+      <c r="D309" s="1"/>
+      <c r="E309" s="1"/>
+      <c r="F309" s="1"/>
+      <c r="G309" s="1"/>
+      <c r="H309" s="1"/>
+      <c r="I309" s="1"/>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A310" s="1"/>
+      <c r="B310" s="1"/>
+      <c r="C310" s="1"/>
+      <c r="D310" s="1"/>
+      <c r="E310" s="1"/>
+      <c r="F310" s="1"/>
+      <c r="G310" s="1"/>
+      <c r="H310" s="1"/>
+      <c r="I310" s="1"/>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A311" s="1"/>
+      <c r="B311" s="1"/>
+      <c r="C311" s="1"/>
+      <c r="D311" s="1"/>
+      <c r="E311" s="1"/>
+      <c r="F311" s="1"/>
+      <c r="G311" s="1"/>
+      <c r="H311" s="1"/>
+      <c r="I311" s="1"/>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A312" s="1"/>
+      <c r="B312" s="1"/>
+      <c r="C312" s="1"/>
+      <c r="D312" s="1"/>
+      <c r="E312" s="1"/>
+      <c r="F312" s="1"/>
+      <c r="G312" s="1"/>
+      <c r="H312" s="1"/>
+      <c r="I312" s="1"/>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A313" s="1"/>
+      <c r="B313" s="1"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
+      <c r="E313" s="1"/>
+      <c r="F313" s="1"/>
+      <c r="G313" s="1"/>
+      <c r="H313" s="1"/>
+      <c r="I313" s="1"/>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A314" s="1"/>
+      <c r="B314" s="1"/>
+      <c r="C314" s="1"/>
+      <c r="D314" s="1"/>
+      <c r="E314" s="1"/>
+      <c r="F314" s="1"/>
+      <c r="G314" s="1"/>
+      <c r="H314" s="1"/>
+      <c r="I314" s="1"/>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A315" s="1"/>
+      <c r="B315" s="1"/>
+      <c r="C315" s="1"/>
+      <c r="D315" s="1"/>
+      <c r="E315" s="1"/>
+      <c r="F315" s="1"/>
+      <c r="G315" s="1"/>
+      <c r="H315" s="1"/>
+      <c r="I315" s="1"/>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A316" s="1"/>
+      <c r="B316" s="1"/>
+      <c r="C316" s="1"/>
+      <c r="D316" s="1"/>
+      <c r="E316" s="1"/>
+      <c r="F316" s="1"/>
+      <c r="G316" s="1"/>
+      <c r="H316" s="1"/>
+      <c r="I316" s="1"/>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A317" s="1"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1"/>
+      <c r="E317" s="1"/>
+      <c r="F317" s="1"/>
+      <c r="G317" s="1"/>
+      <c r="H317" s="1"/>
+      <c r="I317" s="1"/>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A318" s="1"/>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
+      <c r="D318" s="1"/>
+      <c r="E318" s="1"/>
+      <c r="F318" s="1"/>
+      <c r="G318" s="1"/>
+      <c r="H318" s="1"/>
+      <c r="I318" s="1"/>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A319" s="1"/>
+      <c r="B319" s="1"/>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1"/>
+      <c r="E319" s="1"/>
+      <c r="F319" s="1"/>
+      <c r="G319" s="1"/>
+      <c r="H319" s="1"/>
+      <c r="I319" s="1"/>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A320" s="1"/>
+      <c r="B320" s="1"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
+      <c r="E320" s="1"/>
+      <c r="F320" s="1"/>
+      <c r="G320" s="1"/>
+      <c r="H320" s="1"/>
+      <c r="I320" s="1"/>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A321" s="1"/>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1"/>
+      <c r="E321" s="1"/>
+      <c r="F321" s="1"/>
+      <c r="G321" s="1"/>
+      <c r="H321" s="1"/>
+      <c r="I321" s="1"/>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A322" s="1"/>
+      <c r="B322" s="1"/>
+      <c r="C322" s="1"/>
+      <c r="D322" s="1"/>
+      <c r="E322" s="1"/>
+      <c r="F322" s="1"/>
+      <c r="G322" s="1"/>
+      <c r="H322" s="1"/>
+      <c r="I322" s="1"/>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A323" s="1"/>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1"/>
+      <c r="E323" s="1"/>
+      <c r="F323" s="1"/>
+      <c r="G323" s="1"/>
+      <c r="H323" s="1"/>
+      <c r="I323" s="1"/>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A324" s="1"/>
+      <c r="B324" s="1"/>
+      <c r="C324" s="1"/>
+      <c r="D324" s="1"/>
+      <c r="E324" s="1"/>
+      <c r="F324" s="1"/>
+      <c r="G324" s="1"/>
+      <c r="H324" s="1"/>
+      <c r="I324" s="1"/>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A325" s="1"/>
+      <c r="B325" s="1"/>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1"/>
+      <c r="E325" s="1"/>
+      <c r="F325" s="1"/>
+      <c r="G325" s="1"/>
+      <c r="H325" s="1"/>
+      <c r="I325" s="1"/>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A326" s="1"/>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
+      <c r="D326" s="1"/>
+      <c r="E326" s="1"/>
+      <c r="F326" s="1"/>
+      <c r="G326" s="1"/>
+      <c r="H326" s="1"/>
+      <c r="I326" s="1"/>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A327" s="1"/>
+      <c r="B327" s="1"/>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
+      <c r="E327" s="1"/>
+      <c r="F327" s="1"/>
+      <c r="G327" s="1"/>
+      <c r="H327" s="1"/>
+      <c r="I327" s="1"/>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A328" s="1"/>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
+      <c r="D328" s="1"/>
+      <c r="E328" s="1"/>
+      <c r="F328" s="1"/>
+      <c r="G328" s="1"/>
+      <c r="H328" s="1"/>
+      <c r="I328" s="1"/>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A329" s="1"/>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1"/>
+      <c r="E329" s="1"/>
+      <c r="F329" s="1"/>
+      <c r="G329" s="1"/>
+      <c r="H329" s="1"/>
+      <c r="I329" s="1"/>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A330" s="1"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
+      <c r="D330" s="1"/>
+      <c r="E330" s="1"/>
+      <c r="F330" s="1"/>
+      <c r="G330" s="1"/>
+      <c r="H330" s="1"/>
+      <c r="I330" s="1"/>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A331" s="1"/>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1"/>
+      <c r="E331" s="1"/>
+      <c r="F331" s="1"/>
+      <c r="G331" s="1"/>
+      <c r="H331" s="1"/>
+      <c r="I331" s="1"/>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A332" s="1"/>
+      <c r="B332" s="1"/>
+      <c r="C332" s="1"/>
+      <c r="D332" s="1"/>
+      <c r="E332" s="1"/>
+      <c r="F332" s="1"/>
+      <c r="G332" s="1"/>
+      <c r="H332" s="1"/>
+      <c r="I332" s="1"/>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A333" s="1"/>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1"/>
+      <c r="E333" s="1"/>
+      <c r="F333" s="1"/>
+      <c r="G333" s="1"/>
+      <c r="H333" s="1"/>
+      <c r="I333" s="1"/>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A334" s="1"/>
+      <c r="B334" s="1"/>
+      <c r="C334" s="1"/>
+      <c r="D334" s="1"/>
+      <c r="E334" s="1"/>
+      <c r="F334" s="1"/>
+      <c r="G334" s="1"/>
+      <c r="H334" s="1"/>
+      <c r="I334" s="1"/>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A335" s="1"/>
+      <c r="B335" s="1"/>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1"/>
+      <c r="E335" s="1"/>
+      <c r="F335" s="1"/>
+      <c r="G335" s="1"/>
+      <c r="H335" s="1"/>
+      <c r="I335" s="1"/>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A336" s="1"/>
+      <c r="B336" s="1"/>
+      <c r="C336" s="1"/>
+      <c r="D336" s="1"/>
+      <c r="E336" s="1"/>
+      <c r="F336" s="1"/>
+      <c r="G336" s="1"/>
+      <c r="H336" s="1"/>
+      <c r="I336" s="1"/>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A337" s="1"/>
+      <c r="B337" s="1"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1"/>
+      <c r="E337" s="1"/>
+      <c r="F337" s="1"/>
+      <c r="G337" s="1"/>
+      <c r="H337" s="1"/>
+      <c r="I337" s="1"/>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A338" s="1"/>
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
+      <c r="E338" s="1"/>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
+      <c r="H338" s="1"/>
+      <c r="I338" s="1"/>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A339" s="1"/>
+      <c r="B339" s="1"/>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1"/>
+      <c r="E339" s="1"/>
+      <c r="F339" s="1"/>
+      <c r="G339" s="1"/>
+      <c r="H339" s="1"/>
+      <c r="I339" s="1"/>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A340" s="1"/>
+      <c r="B340" s="1"/>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
+      <c r="E340" s="1"/>
+      <c r="F340" s="1"/>
+      <c r="G340" s="1"/>
+      <c r="H340" s="1"/>
+      <c r="I340" s="1"/>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A341" s="1"/>
+      <c r="B341" s="1"/>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1"/>
+      <c r="E341" s="1"/>
+      <c r="F341" s="1"/>
+      <c r="G341" s="1"/>
+      <c r="H341" s="1"/>
+      <c r="I341" s="1"/>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A342" s="1"/>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1"/>
+      <c r="E342" s="1"/>
+      <c r="F342" s="1"/>
+      <c r="G342" s="1"/>
+      <c r="H342" s="1"/>
+      <c r="I342" s="1"/>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A343" s="1"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1"/>
+      <c r="E343" s="1"/>
+      <c r="F343" s="1"/>
+      <c r="G343" s="1"/>
+      <c r="H343" s="1"/>
+      <c r="I343" s="1"/>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A344" s="1"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1"/>
+      <c r="E344" s="1"/>
+      <c r="F344" s="1"/>
+      <c r="G344" s="1"/>
+      <c r="H344" s="1"/>
+      <c r="I344" s="1"/>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A345" s="1"/>
+      <c r="B345" s="1"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1"/>
+      <c r="E345" s="1"/>
+      <c r="F345" s="1"/>
+      <c r="G345" s="1"/>
+      <c r="H345" s="1"/>
+      <c r="I345" s="1"/>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A346" s="1"/>
+      <c r="B346" s="1"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1"/>
+      <c r="E346" s="1"/>
+      <c r="F346" s="1"/>
+      <c r="G346" s="1"/>
+      <c r="H346" s="1"/>
+      <c r="I346" s="1"/>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A347" s="1"/>
+      <c r="B347" s="1"/>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1"/>
+      <c r="E347" s="1"/>
+      <c r="F347" s="1"/>
+      <c r="G347" s="1"/>
+      <c r="H347" s="1"/>
+      <c r="I347" s="1"/>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A348" s="1"/>
+      <c r="B348" s="1"/>
+      <c r="C348" s="1"/>
+      <c r="D348" s="1"/>
+      <c r="E348" s="1"/>
+      <c r="F348" s="1"/>
+      <c r="G348" s="1"/>
+      <c r="H348" s="1"/>
+      <c r="I348" s="1"/>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A349" s="1"/>
+      <c r="B349" s="1"/>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1"/>
+      <c r="E349" s="1"/>
+      <c r="F349" s="1"/>
+      <c r="G349" s="1"/>
+      <c r="H349" s="1"/>
+      <c r="I349" s="1"/>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A350" s="1"/>
+      <c r="B350" s="1"/>
+      <c r="C350" s="1"/>
+      <c r="D350" s="1"/>
+      <c r="E350" s="1"/>
+      <c r="F350" s="1"/>
+      <c r="G350" s="1"/>
+      <c r="H350" s="1"/>
+      <c r="I350" s="1"/>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A351" s="1"/>
+      <c r="B351" s="1"/>
+      <c r="C351" s="1"/>
+      <c r="D351" s="1"/>
+      <c r="E351" s="1"/>
+      <c r="F351" s="1"/>
+      <c r="G351" s="1"/>
+      <c r="H351" s="1"/>
+      <c r="I351" s="1"/>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A352" s="1"/>
+      <c r="B352" s="1"/>
+      <c r="C352" s="1"/>
+      <c r="D352" s="1"/>
+      <c r="E352" s="1"/>
+      <c r="F352" s="1"/>
+      <c r="G352" s="1"/>
+      <c r="H352" s="1"/>
+      <c r="I352" s="1"/>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A353" s="1"/>
+      <c r="B353" s="1"/>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
+      <c r="E353" s="1"/>
+      <c r="F353" s="1"/>
+      <c r="G353" s="1"/>
+      <c r="H353" s="1"/>
+      <c r="I353" s="1"/>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A354" s="1"/>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
+      <c r="E354" s="1"/>
+      <c r="F354" s="1"/>
+      <c r="G354" s="1"/>
+      <c r="H354" s="1"/>
+      <c r="I354" s="1"/>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A355" s="1"/>
+      <c r="B355" s="1"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="1"/>
+      <c r="E355" s="1"/>
+      <c r="F355" s="1"/>
+      <c r="G355" s="1"/>
+      <c r="H355" s="1"/>
+      <c r="I355" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1620E937-DA99-6A40-9403-CA8841F7F218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D9362-C04F-0A42-830C-F755712464CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="3900" yWindow="12740" windowWidth="30240" windowHeight="17540" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="keywords" sheetId="2" r:id="rId1"/>
     <sheet name="potential additional keywords" sheetId="3" r:id="rId2"/>
     <sheet name="keywords_additional" sheetId="4" r:id="rId3"/>
+    <sheet name="adapted_keywords" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10959,4 +10960,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9374F8-5EC0-2B4D-B147-6130FD66FA7B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D9362-C04F-0A42-830C-F755712464CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D488EF-E804-B94F-B0C7-D228244B0966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="12740" windowWidth="30240" windowHeight="17540" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="15180" yWindow="920" windowWidth="14900" windowHeight="17220" activeTab="3" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="keywords" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="313">
   <si>
     <t>DIABETES</t>
   </si>
@@ -966,6 +966,18 @@
   </si>
   <si>
     <t>5-FLUORO-ADB TOXICITY</t>
+  </si>
+  <si>
+    <t>SUICIDE KEYWORDS</t>
+  </si>
+  <si>
+    <t>HOMICIDE KEYWORDS</t>
+  </si>
+  <si>
+    <t>NON-COMMUNICABLE DISEASE KEYWORDS</t>
+  </si>
+  <si>
+    <t>COMMUNICABLE DISEASE KEYWORDS</t>
   </si>
 </sst>
 </file>
@@ -10964,9 +10976,6095 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9374F8-5EC0-2B4D-B147-6130FD66FA7B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:O355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" customWidth="1"/>
+    <col min="4" max="5" width="43.5" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="24.83203125" customWidth="1"/>
+    <col min="10" max="10" width="33.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="23.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="O19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="O20" s="1"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="O21" s="1"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="O22" s="1"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="O23" s="1"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="O32" s="1"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="O41" s="1"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="O42" s="1"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="O43" s="1"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="O44" s="1"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+    </row>
+    <row r="46" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+    </row>
+    <row r="49" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>236</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>241</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+    </row>
+    <row r="56" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+    </row>
+    <row r="59" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+    </row>
+    <row r="64" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+    </row>
+    <row r="68" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+    </row>
+    <row r="74" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+    </row>
+    <row r="79" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+    </row>
+    <row r="82" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="K116" s="1"/>
+      <c r="L116" s="1"/>
+      <c r="M116" s="1"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K118" s="1"/>
+      <c r="L118" s="1"/>
+      <c r="M118" s="1"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K119" s="1"/>
+      <c r="L119" s="1"/>
+      <c r="M119" s="1"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="K120" s="1"/>
+      <c r="L120" s="1"/>
+      <c r="M120" s="1"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="1"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="K122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="1"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="K123" s="1"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="1"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="K124" s="1"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="1"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="K125" s="1"/>
+      <c r="L125" s="1"/>
+      <c r="M125" s="1"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="K126" s="1"/>
+      <c r="L126" s="1"/>
+      <c r="M126" s="1"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K127" s="1"/>
+      <c r="L127" s="1"/>
+      <c r="M127" s="1"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="K128" s="1"/>
+      <c r="L128" s="1"/>
+      <c r="M128" s="1"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="K130" s="1"/>
+      <c r="L130" s="1"/>
+      <c r="M130" s="1"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="K131" s="1"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="1"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K132" s="1"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="1"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K133" s="1"/>
+      <c r="L133" s="1"/>
+      <c r="M133" s="1"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="1"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="K135" s="1"/>
+      <c r="L135" s="1"/>
+      <c r="M135" s="1"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="K137" s="1"/>
+      <c r="L137" s="1"/>
+      <c r="M137" s="1"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="K138" s="1"/>
+      <c r="L138" s="1"/>
+      <c r="M138" s="1"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="K139" s="1"/>
+      <c r="L139" s="1"/>
+      <c r="M139" s="1"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K140" s="1"/>
+      <c r="L140" s="1"/>
+      <c r="M140" s="1"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="K141" s="1"/>
+      <c r="L141" s="1"/>
+      <c r="M141" s="1"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K142" s="1"/>
+      <c r="L142" s="1"/>
+      <c r="M142" s="1"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
+      <c r="E143" s="1"/>
+      <c r="F143" s="1"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
+      <c r="K143" s="1"/>
+      <c r="L143" s="1"/>
+      <c r="M143" s="1"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
+      <c r="K144" s="1"/>
+      <c r="L144" s="1"/>
+      <c r="M144" s="1"/>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="1"/>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1"/>
+      <c r="L145" s="1"/>
+      <c r="M145" s="1"/>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="1"/>
+      <c r="M146" s="1"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
+      <c r="F147" s="1"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
+      <c r="K147" s="1"/>
+      <c r="L147" s="1"/>
+      <c r="M147" s="1"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
+      <c r="K148" s="1"/>
+      <c r="L148" s="1"/>
+      <c r="M148" s="1"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1"/>
+      <c r="L149" s="1"/>
+      <c r="M149" s="1"/>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
+      <c r="K150" s="1"/>
+      <c r="L150" s="1"/>
+      <c r="M150" s="1"/>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
+      <c r="K151" s="1"/>
+      <c r="L151" s="1"/>
+      <c r="M151" s="1"/>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
+      <c r="K152" s="1"/>
+      <c r="L152" s="1"/>
+      <c r="M152" s="1"/>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
+      <c r="K153" s="1"/>
+      <c r="L153" s="1"/>
+      <c r="M153" s="1"/>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1"/>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
+      <c r="K154" s="1"/>
+      <c r="L154" s="1"/>
+      <c r="M154" s="1"/>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
+      <c r="K155" s="1"/>
+      <c r="L155" s="1"/>
+      <c r="M155" s="1"/>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
+      <c r="K156" s="1"/>
+      <c r="L156" s="1"/>
+      <c r="M156" s="1"/>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
+      <c r="K157" s="1"/>
+      <c r="L157" s="1"/>
+      <c r="M157" s="1"/>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A158" s="1"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="F158" s="1"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+      <c r="J158" s="1"/>
+      <c r="K158" s="1"/>
+      <c r="L158" s="1"/>
+      <c r="M158" s="1"/>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+      <c r="J159" s="1"/>
+      <c r="K159" s="1"/>
+      <c r="L159" s="1"/>
+      <c r="M159" s="1"/>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+      <c r="J162" s="1"/>
+      <c r="K162" s="1"/>
+      <c r="L162" s="1"/>
+      <c r="M162" s="1"/>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+      <c r="J163" s="1"/>
+      <c r="K163" s="1"/>
+      <c r="L163" s="1"/>
+      <c r="M163" s="1"/>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+      <c r="J164" s="1"/>
+      <c r="K164" s="1"/>
+      <c r="L164" s="1"/>
+      <c r="M164" s="1"/>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="K165" s="1"/>
+      <c r="L165" s="1"/>
+      <c r="M165" s="1"/>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+      <c r="J166" s="1"/>
+      <c r="K166" s="1"/>
+      <c r="L166" s="1"/>
+      <c r="M166" s="1"/>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="1"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+      <c r="J167" s="1"/>
+      <c r="K167" s="1"/>
+      <c r="L167" s="1"/>
+      <c r="M167" s="1"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
+      <c r="K168" s="1"/>
+      <c r="L168" s="1"/>
+      <c r="M168" s="1"/>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+      <c r="L169" s="1"/>
+      <c r="M169" s="1"/>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="K170" s="1"/>
+      <c r="L170" s="1"/>
+      <c r="M170" s="1"/>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="K171" s="1"/>
+      <c r="L171" s="1"/>
+      <c r="M171" s="1"/>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+      <c r="K172" s="1"/>
+      <c r="L172" s="1"/>
+      <c r="M172" s="1"/>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="K173" s="1"/>
+      <c r="L173" s="1"/>
+      <c r="M173" s="1"/>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="K174" s="1"/>
+      <c r="L174" s="1"/>
+      <c r="M174" s="1"/>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="1"/>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
+      <c r="L175" s="1"/>
+      <c r="M175" s="1"/>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+      <c r="K176" s="1"/>
+      <c r="L176" s="1"/>
+      <c r="M176" s="1"/>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+      <c r="E177" s="1"/>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+      <c r="J177" s="1"/>
+      <c r="K177" s="1"/>
+      <c r="L177" s="1"/>
+      <c r="M177" s="1"/>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="K178" s="1"/>
+      <c r="L178" s="1"/>
+      <c r="M178" s="1"/>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+      <c r="J179" s="1"/>
+      <c r="K179" s="1"/>
+      <c r="L179" s="1"/>
+      <c r="M179" s="1"/>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+      <c r="G180" s="1"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+      <c r="J180" s="1"/>
+      <c r="K180" s="1"/>
+      <c r="L180" s="1"/>
+      <c r="M180" s="1"/>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+      <c r="G181" s="1"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="K181" s="1"/>
+      <c r="L181" s="1"/>
+      <c r="M181" s="1"/>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="K182" s="1"/>
+      <c r="L182" s="1"/>
+      <c r="M182" s="1"/>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="1"/>
+      <c r="G183" s="1"/>
+      <c r="H183" s="1"/>
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+      <c r="K183" s="1"/>
+      <c r="L183" s="1"/>
+      <c r="M183" s="1"/>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
+      <c r="H184" s="1"/>
+      <c r="I184" s="1"/>
+      <c r="J184" s="1"/>
+      <c r="K184" s="1"/>
+      <c r="L184" s="1"/>
+      <c r="M184" s="1"/>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="1"/>
+      <c r="G185" s="1"/>
+      <c r="H185" s="1"/>
+      <c r="I185" s="1"/>
+      <c r="J185" s="1"/>
+      <c r="K185" s="1"/>
+      <c r="L185" s="1"/>
+      <c r="M185" s="1"/>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="1"/>
+      <c r="G186" s="1"/>
+      <c r="H186" s="1"/>
+      <c r="I186" s="1"/>
+      <c r="J186" s="1"/>
+      <c r="K186" s="1"/>
+      <c r="L186" s="1"/>
+      <c r="M186" s="1"/>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="1"/>
+      <c r="G187" s="1"/>
+      <c r="H187" s="1"/>
+      <c r="I187" s="1"/>
+      <c r="J187" s="1"/>
+      <c r="K187" s="1"/>
+      <c r="L187" s="1"/>
+      <c r="M187" s="1"/>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+      <c r="L188" s="1"/>
+      <c r="M188" s="1"/>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
+      <c r="L189" s="1"/>
+      <c r="M189" s="1"/>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+      <c r="K190" s="1"/>
+      <c r="L190" s="1"/>
+      <c r="M190" s="1"/>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+      <c r="K191" s="1"/>
+      <c r="L191" s="1"/>
+      <c r="M191" s="1"/>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+      <c r="J192" s="1"/>
+      <c r="K192" s="1"/>
+      <c r="L192" s="1"/>
+      <c r="M192" s="1"/>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+      <c r="J193" s="1"/>
+      <c r="K193" s="1"/>
+      <c r="L193" s="1"/>
+      <c r="M193" s="1"/>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+      <c r="J194" s="1"/>
+      <c r="K194" s="1"/>
+      <c r="L194" s="1"/>
+      <c r="M194" s="1"/>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195" s="1"/>
+      <c r="K195" s="1"/>
+      <c r="L195" s="1"/>
+      <c r="M195" s="1"/>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+      <c r="F196" s="1"/>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1"/>
+      <c r="I196" s="1"/>
+      <c r="J196" s="1"/>
+      <c r="K196" s="1"/>
+      <c r="L196" s="1"/>
+      <c r="M196" s="1"/>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1"/>
+      <c r="F197" s="1"/>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+      <c r="J197" s="1"/>
+      <c r="K197" s="1"/>
+      <c r="L197" s="1"/>
+      <c r="M197" s="1"/>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+      <c r="F198" s="1"/>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+      <c r="J198" s="1"/>
+      <c r="K198" s="1"/>
+      <c r="L198" s="1"/>
+      <c r="M198" s="1"/>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+      <c r="J199" s="1"/>
+      <c r="K199" s="1"/>
+      <c r="L199" s="1"/>
+      <c r="M199" s="1"/>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
+      <c r="E200" s="1"/>
+      <c r="F200" s="1"/>
+      <c r="G200" s="1"/>
+      <c r="H200" s="1"/>
+      <c r="I200" s="1"/>
+      <c r="J200" s="1"/>
+      <c r="K200" s="1"/>
+      <c r="L200" s="1"/>
+      <c r="M200" s="1"/>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+      <c r="F201" s="1"/>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+      <c r="J201" s="1"/>
+      <c r="K201" s="1"/>
+      <c r="L201" s="1"/>
+      <c r="M201" s="1"/>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="1"/>
+      <c r="F202" s="1"/>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1"/>
+      <c r="I202" s="1"/>
+      <c r="J202" s="1"/>
+      <c r="K202" s="1"/>
+      <c r="L202" s="1"/>
+      <c r="M202" s="1"/>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+      <c r="E203" s="1"/>
+      <c r="F203" s="1"/>
+      <c r="G203" s="1"/>
+      <c r="H203" s="1"/>
+      <c r="I203" s="1"/>
+      <c r="J203" s="1"/>
+      <c r="K203" s="1"/>
+      <c r="L203" s="1"/>
+      <c r="M203" s="1"/>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+      <c r="E204" s="1"/>
+      <c r="F204" s="1"/>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1"/>
+      <c r="J204" s="1"/>
+      <c r="K204" s="1"/>
+      <c r="L204" s="1"/>
+      <c r="M204" s="1"/>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+      <c r="E205" s="1"/>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1"/>
+      <c r="H205" s="1"/>
+      <c r="I205" s="1"/>
+      <c r="J205" s="1"/>
+      <c r="K205" s="1"/>
+      <c r="L205" s="1"/>
+      <c r="M205" s="1"/>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="1"/>
+      <c r="F206" s="1"/>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+      <c r="I206" s="1"/>
+      <c r="J206" s="1"/>
+      <c r="K206" s="1"/>
+      <c r="L206" s="1"/>
+      <c r="M206" s="1"/>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+      <c r="E207" s="1"/>
+      <c r="F207" s="1"/>
+      <c r="G207" s="1"/>
+      <c r="H207" s="1"/>
+      <c r="I207" s="1"/>
+      <c r="J207" s="1"/>
+      <c r="K207" s="1"/>
+      <c r="L207" s="1"/>
+      <c r="M207" s="1"/>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
+      <c r="E208" s="1"/>
+      <c r="F208" s="1"/>
+      <c r="G208" s="1"/>
+      <c r="H208" s="1"/>
+      <c r="I208" s="1"/>
+      <c r="J208" s="1"/>
+      <c r="K208" s="1"/>
+      <c r="L208" s="1"/>
+      <c r="M208" s="1"/>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
+      <c r="E209" s="1"/>
+      <c r="F209" s="1"/>
+      <c r="G209" s="1"/>
+      <c r="H209" s="1"/>
+      <c r="I209" s="1"/>
+      <c r="J209" s="1"/>
+      <c r="K209" s="1"/>
+      <c r="L209" s="1"/>
+      <c r="M209" s="1"/>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+      <c r="E210" s="1"/>
+      <c r="F210" s="1"/>
+      <c r="G210" s="1"/>
+      <c r="H210" s="1"/>
+      <c r="I210" s="1"/>
+      <c r="J210" s="1"/>
+      <c r="K210" s="1"/>
+      <c r="L210" s="1"/>
+      <c r="M210" s="1"/>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+      <c r="E211" s="1"/>
+      <c r="F211" s="1"/>
+      <c r="G211" s="1"/>
+      <c r="H211" s="1"/>
+      <c r="I211" s="1"/>
+      <c r="J211" s="1"/>
+      <c r="K211" s="1"/>
+      <c r="L211" s="1"/>
+      <c r="M211" s="1"/>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+      <c r="E212" s="1"/>
+      <c r="F212" s="1"/>
+      <c r="G212" s="1"/>
+      <c r="H212" s="1"/>
+      <c r="I212" s="1"/>
+      <c r="J212" s="1"/>
+      <c r="K212" s="1"/>
+      <c r="L212" s="1"/>
+      <c r="M212" s="1"/>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A213" s="1"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
+      <c r="E213" s="1"/>
+      <c r="F213" s="1"/>
+      <c r="G213" s="1"/>
+      <c r="H213" s="1"/>
+      <c r="I213" s="1"/>
+      <c r="J213" s="1"/>
+      <c r="K213" s="1"/>
+      <c r="L213" s="1"/>
+      <c r="M213" s="1"/>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="1"/>
+      <c r="F214" s="1"/>
+      <c r="G214" s="1"/>
+      <c r="H214" s="1"/>
+      <c r="I214" s="1"/>
+      <c r="J214" s="1"/>
+      <c r="K214" s="1"/>
+      <c r="L214" s="1"/>
+      <c r="M214" s="1"/>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A215" s="1"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
+      <c r="E215" s="1"/>
+      <c r="F215" s="1"/>
+      <c r="G215" s="1"/>
+      <c r="H215" s="1"/>
+      <c r="I215" s="1"/>
+      <c r="J215" s="1"/>
+      <c r="K215" s="1"/>
+      <c r="L215" s="1"/>
+      <c r="M215" s="1"/>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+      <c r="E216" s="1"/>
+      <c r="F216" s="1"/>
+      <c r="G216" s="1"/>
+      <c r="H216" s="1"/>
+      <c r="I216" s="1"/>
+      <c r="J216" s="1"/>
+      <c r="K216" s="1"/>
+      <c r="L216" s="1"/>
+      <c r="M216" s="1"/>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
+      <c r="E217" s="1"/>
+      <c r="F217" s="1"/>
+      <c r="G217" s="1"/>
+      <c r="H217" s="1"/>
+      <c r="I217" s="1"/>
+      <c r="J217" s="1"/>
+      <c r="K217" s="1"/>
+      <c r="L217" s="1"/>
+      <c r="M217" s="1"/>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
+      <c r="E218" s="1"/>
+      <c r="F218" s="1"/>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1"/>
+      <c r="I218" s="1"/>
+      <c r="J218" s="1"/>
+      <c r="K218" s="1"/>
+      <c r="L218" s="1"/>
+      <c r="M218" s="1"/>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+      <c r="K219" s="1"/>
+      <c r="L219" s="1"/>
+      <c r="M219" s="1"/>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
+      <c r="E220" s="1"/>
+      <c r="F220" s="1"/>
+      <c r="G220" s="1"/>
+      <c r="H220" s="1"/>
+      <c r="I220" s="1"/>
+      <c r="J220" s="1"/>
+      <c r="K220" s="1"/>
+      <c r="L220" s="1"/>
+      <c r="M220" s="1"/>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+      <c r="J221" s="1"/>
+      <c r="K221" s="1"/>
+      <c r="L221" s="1"/>
+      <c r="M221" s="1"/>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
+      <c r="E222" s="1"/>
+      <c r="F222" s="1"/>
+      <c r="G222" s="1"/>
+      <c r="H222" s="1"/>
+      <c r="I222" s="1"/>
+      <c r="J222" s="1"/>
+      <c r="K222" s="1"/>
+      <c r="L222" s="1"/>
+      <c r="M222" s="1"/>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+      <c r="E223" s="1"/>
+      <c r="F223" s="1"/>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
+      <c r="J223" s="1"/>
+      <c r="K223" s="1"/>
+      <c r="L223" s="1"/>
+      <c r="M223" s="1"/>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A224" s="1"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+      <c r="E224" s="1"/>
+      <c r="F224" s="1"/>
+      <c r="G224" s="1"/>
+      <c r="H224" s="1"/>
+      <c r="I224" s="1"/>
+      <c r="J224" s="1"/>
+      <c r="K224" s="1"/>
+      <c r="L224" s="1"/>
+      <c r="M224" s="1"/>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
+      <c r="E225" s="1"/>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1"/>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+      <c r="J225" s="1"/>
+      <c r="K225" s="1"/>
+      <c r="L225" s="1"/>
+      <c r="M225" s="1"/>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
+      <c r="E226" s="1"/>
+      <c r="F226" s="1"/>
+      <c r="G226" s="1"/>
+      <c r="H226" s="1"/>
+      <c r="I226" s="1"/>
+      <c r="J226" s="1"/>
+      <c r="K226" s="1"/>
+      <c r="L226" s="1"/>
+      <c r="M226" s="1"/>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
+      <c r="E227" s="1"/>
+      <c r="F227" s="1"/>
+      <c r="G227" s="1"/>
+      <c r="H227" s="1"/>
+      <c r="I227" s="1"/>
+      <c r="J227" s="1"/>
+      <c r="K227" s="1"/>
+      <c r="L227" s="1"/>
+      <c r="M227" s="1"/>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1"/>
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+      <c r="J228" s="1"/>
+      <c r="K228" s="1"/>
+      <c r="L228" s="1"/>
+      <c r="M228" s="1"/>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
+      <c r="E229" s="1"/>
+      <c r="F229" s="1"/>
+      <c r="G229" s="1"/>
+      <c r="H229" s="1"/>
+      <c r="I229" s="1"/>
+      <c r="J229" s="1"/>
+      <c r="K229" s="1"/>
+      <c r="L229" s="1"/>
+      <c r="M229" s="1"/>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
+      <c r="E230" s="1"/>
+      <c r="F230" s="1"/>
+      <c r="G230" s="1"/>
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
+      <c r="J230" s="1"/>
+      <c r="K230" s="1"/>
+      <c r="L230" s="1"/>
+      <c r="M230" s="1"/>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+      <c r="I231" s="1"/>
+      <c r="J231" s="1"/>
+      <c r="K231" s="1"/>
+      <c r="L231" s="1"/>
+      <c r="M231" s="1"/>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+      <c r="E232" s="1"/>
+      <c r="F232" s="1"/>
+      <c r="G232" s="1"/>
+      <c r="H232" s="1"/>
+      <c r="I232" s="1"/>
+      <c r="J232" s="1"/>
+      <c r="K232" s="1"/>
+      <c r="L232" s="1"/>
+      <c r="M232" s="1"/>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+      <c r="E233" s="1"/>
+      <c r="F233" s="1"/>
+      <c r="G233" s="1"/>
+      <c r="H233" s="1"/>
+      <c r="I233" s="1"/>
+      <c r="J233" s="1"/>
+      <c r="K233" s="1"/>
+      <c r="L233" s="1"/>
+      <c r="M233" s="1"/>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1"/>
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+      <c r="J234" s="1"/>
+      <c r="K234" s="1"/>
+      <c r="L234" s="1"/>
+      <c r="M234" s="1"/>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+      <c r="J235" s="1"/>
+      <c r="K235" s="1"/>
+      <c r="L235" s="1"/>
+      <c r="M235" s="1"/>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+      <c r="F236" s="1"/>
+      <c r="G236" s="1"/>
+      <c r="H236" s="1"/>
+      <c r="I236" s="1"/>
+      <c r="J236" s="1"/>
+      <c r="K236" s="1"/>
+      <c r="L236" s="1"/>
+      <c r="M236" s="1"/>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+      <c r="J237" s="1"/>
+      <c r="K237" s="1"/>
+      <c r="L237" s="1"/>
+      <c r="M237" s="1"/>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="K238" s="1"/>
+      <c r="L238" s="1"/>
+      <c r="M238" s="1"/>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
+      <c r="K239" s="1"/>
+      <c r="L239" s="1"/>
+      <c r="M239" s="1"/>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+      <c r="F240" s="1"/>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+      <c r="J240" s="1"/>
+      <c r="K240" s="1"/>
+      <c r="L240" s="1"/>
+      <c r="M240" s="1"/>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+      <c r="F241" s="1"/>
+      <c r="G241" s="1"/>
+      <c r="H241" s="1"/>
+      <c r="I241" s="1"/>
+      <c r="J241" s="1"/>
+      <c r="K241" s="1"/>
+      <c r="L241" s="1"/>
+      <c r="M241" s="1"/>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+      <c r="E242" s="1"/>
+      <c r="F242" s="1"/>
+      <c r="G242" s="1"/>
+      <c r="H242" s="1"/>
+      <c r="I242" s="1"/>
+      <c r="J242" s="1"/>
+      <c r="K242" s="1"/>
+      <c r="L242" s="1"/>
+      <c r="M242" s="1"/>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1"/>
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+      <c r="J243" s="1"/>
+      <c r="K243" s="1"/>
+      <c r="L243" s="1"/>
+      <c r="M243" s="1"/>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
+      <c r="G244" s="1"/>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1"/>
+      <c r="J244" s="1"/>
+      <c r="K244" s="1"/>
+      <c r="L244" s="1"/>
+      <c r="M244" s="1"/>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+      <c r="E245" s="1"/>
+      <c r="F245" s="1"/>
+      <c r="G245" s="1"/>
+      <c r="H245" s="1"/>
+      <c r="I245" s="1"/>
+      <c r="J245" s="1"/>
+      <c r="K245" s="1"/>
+      <c r="L245" s="1"/>
+      <c r="M245" s="1"/>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+      <c r="E246" s="1"/>
+      <c r="F246" s="1"/>
+      <c r="G246" s="1"/>
+      <c r="H246" s="1"/>
+      <c r="I246" s="1"/>
+      <c r="J246" s="1"/>
+      <c r="K246" s="1"/>
+      <c r="L246" s="1"/>
+      <c r="M246" s="1"/>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+      <c r="E247" s="1"/>
+      <c r="F247" s="1"/>
+      <c r="G247" s="1"/>
+      <c r="H247" s="1"/>
+      <c r="I247" s="1"/>
+      <c r="J247" s="1"/>
+      <c r="K247" s="1"/>
+      <c r="L247" s="1"/>
+      <c r="M247" s="1"/>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A248" s="1"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+      <c r="F248" s="1"/>
+      <c r="G248" s="1"/>
+      <c r="H248" s="1"/>
+      <c r="I248" s="1"/>
+      <c r="J248" s="1"/>
+      <c r="K248" s="1"/>
+      <c r="L248" s="1"/>
+      <c r="M248" s="1"/>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
+      <c r="G249" s="1"/>
+      <c r="H249" s="1"/>
+      <c r="I249" s="1"/>
+      <c r="J249" s="1"/>
+      <c r="K249" s="1"/>
+      <c r="L249" s="1"/>
+      <c r="M249" s="1"/>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
+      <c r="G250" s="1"/>
+      <c r="H250" s="1"/>
+      <c r="I250" s="1"/>
+      <c r="J250" s="1"/>
+      <c r="K250" s="1"/>
+      <c r="L250" s="1"/>
+      <c r="M250" s="1"/>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
+      <c r="E251" s="1"/>
+      <c r="F251" s="1"/>
+      <c r="G251" s="1"/>
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
+      <c r="J251" s="1"/>
+      <c r="K251" s="1"/>
+      <c r="L251" s="1"/>
+      <c r="M251" s="1"/>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+      <c r="F252" s="1"/>
+      <c r="G252" s="1"/>
+      <c r="H252" s="1"/>
+      <c r="I252" s="1"/>
+      <c r="J252" s="1"/>
+      <c r="K252" s="1"/>
+      <c r="L252" s="1"/>
+      <c r="M252" s="1"/>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1"/>
+      <c r="F253" s="1"/>
+      <c r="G253" s="1"/>
+      <c r="H253" s="1"/>
+      <c r="I253" s="1"/>
+      <c r="J253" s="1"/>
+      <c r="K253" s="1"/>
+      <c r="L253" s="1"/>
+      <c r="M253" s="1"/>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+      <c r="F254" s="1"/>
+      <c r="G254" s="1"/>
+      <c r="H254" s="1"/>
+      <c r="I254" s="1"/>
+      <c r="J254" s="1"/>
+      <c r="K254" s="1"/>
+      <c r="L254" s="1"/>
+      <c r="M254" s="1"/>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
+      <c r="E255" s="1"/>
+      <c r="F255" s="1"/>
+      <c r="G255" s="1"/>
+      <c r="H255" s="1"/>
+      <c r="I255" s="1"/>
+      <c r="J255" s="1"/>
+      <c r="K255" s="1"/>
+      <c r="L255" s="1"/>
+      <c r="M255" s="1"/>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
+      <c r="G256" s="1"/>
+      <c r="H256" s="1"/>
+      <c r="I256" s="1"/>
+      <c r="J256" s="1"/>
+      <c r="K256" s="1"/>
+      <c r="L256" s="1"/>
+      <c r="M256" s="1"/>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A257" s="1"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
+      <c r="E257" s="1"/>
+      <c r="F257" s="1"/>
+      <c r="G257" s="1"/>
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+      <c r="J257" s="1"/>
+      <c r="K257" s="1"/>
+      <c r="L257" s="1"/>
+      <c r="M257" s="1"/>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
+      <c r="G258" s="1"/>
+      <c r="H258" s="1"/>
+      <c r="I258" s="1"/>
+      <c r="J258" s="1"/>
+      <c r="K258" s="1"/>
+      <c r="L258" s="1"/>
+      <c r="M258" s="1"/>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+      <c r="E259" s="1"/>
+      <c r="F259" s="1"/>
+      <c r="G259" s="1"/>
+      <c r="H259" s="1"/>
+      <c r="I259" s="1"/>
+      <c r="J259" s="1"/>
+      <c r="K259" s="1"/>
+      <c r="L259" s="1"/>
+      <c r="M259" s="1"/>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
+      <c r="E260" s="1"/>
+      <c r="F260" s="1"/>
+      <c r="G260" s="1"/>
+      <c r="H260" s="1"/>
+      <c r="I260" s="1"/>
+      <c r="J260" s="1"/>
+      <c r="K260" s="1"/>
+      <c r="L260" s="1"/>
+      <c r="M260" s="1"/>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
+      <c r="E261" s="1"/>
+      <c r="F261" s="1"/>
+      <c r="G261" s="1"/>
+      <c r="H261" s="1"/>
+      <c r="I261" s="1"/>
+      <c r="J261" s="1"/>
+      <c r="K261" s="1"/>
+      <c r="L261" s="1"/>
+      <c r="M261" s="1"/>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
+      <c r="E262" s="1"/>
+      <c r="F262" s="1"/>
+      <c r="G262" s="1"/>
+      <c r="H262" s="1"/>
+      <c r="I262" s="1"/>
+      <c r="J262" s="1"/>
+      <c r="K262" s="1"/>
+      <c r="L262" s="1"/>
+      <c r="M262" s="1"/>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+      <c r="E263" s="1"/>
+      <c r="F263" s="1"/>
+      <c r="G263" s="1"/>
+      <c r="H263" s="1"/>
+      <c r="I263" s="1"/>
+      <c r="J263" s="1"/>
+      <c r="K263" s="1"/>
+      <c r="L263" s="1"/>
+      <c r="M263" s="1"/>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A264" s="1"/>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
+      <c r="E264" s="1"/>
+      <c r="F264" s="1"/>
+      <c r="G264" s="1"/>
+      <c r="H264" s="1"/>
+      <c r="I264" s="1"/>
+      <c r="J264" s="1"/>
+      <c r="K264" s="1"/>
+      <c r="L264" s="1"/>
+      <c r="M264" s="1"/>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A265" s="1"/>
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
+      <c r="E265" s="1"/>
+      <c r="F265" s="1"/>
+      <c r="G265" s="1"/>
+      <c r="H265" s="1"/>
+      <c r="I265" s="1"/>
+      <c r="J265" s="1"/>
+      <c r="K265" s="1"/>
+      <c r="L265" s="1"/>
+      <c r="M265" s="1"/>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A266" s="1"/>
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
+      <c r="E266" s="1"/>
+      <c r="F266" s="1"/>
+      <c r="G266" s="1"/>
+      <c r="H266" s="1"/>
+      <c r="I266" s="1"/>
+      <c r="J266" s="1"/>
+      <c r="K266" s="1"/>
+      <c r="L266" s="1"/>
+      <c r="M266" s="1"/>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A267" s="1"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
+      <c r="E267" s="1"/>
+      <c r="F267" s="1"/>
+      <c r="G267" s="1"/>
+      <c r="H267" s="1"/>
+      <c r="I267" s="1"/>
+      <c r="J267" s="1"/>
+      <c r="K267" s="1"/>
+      <c r="L267" s="1"/>
+      <c r="M267" s="1"/>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A268" s="1"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
+      <c r="E268" s="1"/>
+      <c r="F268" s="1"/>
+      <c r="G268" s="1"/>
+      <c r="H268" s="1"/>
+      <c r="I268" s="1"/>
+      <c r="J268" s="1"/>
+      <c r="K268" s="1"/>
+      <c r="L268" s="1"/>
+      <c r="M268" s="1"/>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A269" s="1"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
+      <c r="E269" s="1"/>
+      <c r="F269" s="1"/>
+      <c r="G269" s="1"/>
+      <c r="H269" s="1"/>
+      <c r="I269" s="1"/>
+      <c r="J269" s="1"/>
+      <c r="K269" s="1"/>
+      <c r="L269" s="1"/>
+      <c r="M269" s="1"/>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A270" s="1"/>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
+      <c r="E270" s="1"/>
+      <c r="F270" s="1"/>
+      <c r="G270" s="1"/>
+      <c r="H270" s="1"/>
+      <c r="I270" s="1"/>
+      <c r="J270" s="1"/>
+      <c r="K270" s="1"/>
+      <c r="L270" s="1"/>
+      <c r="M270" s="1"/>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A271" s="1"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+      <c r="E271" s="1"/>
+      <c r="F271" s="1"/>
+      <c r="G271" s="1"/>
+      <c r="H271" s="1"/>
+      <c r="I271" s="1"/>
+      <c r="J271" s="1"/>
+      <c r="K271" s="1"/>
+      <c r="L271" s="1"/>
+      <c r="M271" s="1"/>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A272" s="1"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+      <c r="E272" s="1"/>
+      <c r="F272" s="1"/>
+      <c r="G272" s="1"/>
+      <c r="H272" s="1"/>
+      <c r="I272" s="1"/>
+      <c r="J272" s="1"/>
+      <c r="K272" s="1"/>
+      <c r="L272" s="1"/>
+      <c r="M272" s="1"/>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A273" s="1"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+      <c r="E273" s="1"/>
+      <c r="F273" s="1"/>
+      <c r="G273" s="1"/>
+      <c r="H273" s="1"/>
+      <c r="I273" s="1"/>
+      <c r="J273" s="1"/>
+      <c r="K273" s="1"/>
+      <c r="L273" s="1"/>
+      <c r="M273" s="1"/>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A274" s="1"/>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
+      <c r="E274" s="1"/>
+      <c r="F274" s="1"/>
+      <c r="G274" s="1"/>
+      <c r="H274" s="1"/>
+      <c r="I274" s="1"/>
+      <c r="J274" s="1"/>
+      <c r="K274" s="1"/>
+      <c r="L274" s="1"/>
+      <c r="M274" s="1"/>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A275" s="1"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+      <c r="E275" s="1"/>
+      <c r="F275" s="1"/>
+      <c r="G275" s="1"/>
+      <c r="H275" s="1"/>
+      <c r="I275" s="1"/>
+      <c r="J275" s="1"/>
+      <c r="K275" s="1"/>
+      <c r="L275" s="1"/>
+      <c r="M275" s="1"/>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A276" s="1"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+      <c r="E276" s="1"/>
+      <c r="F276" s="1"/>
+      <c r="G276" s="1"/>
+      <c r="H276" s="1"/>
+      <c r="I276" s="1"/>
+      <c r="J276" s="1"/>
+      <c r="K276" s="1"/>
+      <c r="L276" s="1"/>
+      <c r="M276" s="1"/>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A277" s="1"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+      <c r="E277" s="1"/>
+      <c r="F277" s="1"/>
+      <c r="G277" s="1"/>
+      <c r="H277" s="1"/>
+      <c r="I277" s="1"/>
+      <c r="J277" s="1"/>
+      <c r="K277" s="1"/>
+      <c r="L277" s="1"/>
+      <c r="M277" s="1"/>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A278" s="1"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+      <c r="E278" s="1"/>
+      <c r="F278" s="1"/>
+      <c r="G278" s="1"/>
+      <c r="H278" s="1"/>
+      <c r="I278" s="1"/>
+      <c r="J278" s="1"/>
+      <c r="K278" s="1"/>
+      <c r="L278" s="1"/>
+      <c r="M278" s="1"/>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A279" s="1"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
+      <c r="G279" s="1"/>
+      <c r="H279" s="1"/>
+      <c r="I279" s="1"/>
+      <c r="J279" s="1"/>
+      <c r="K279" s="1"/>
+      <c r="L279" s="1"/>
+      <c r="M279" s="1"/>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A280" s="1"/>
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
+      <c r="E280" s="1"/>
+      <c r="F280" s="1"/>
+      <c r="G280" s="1"/>
+      <c r="H280" s="1"/>
+      <c r="I280" s="1"/>
+      <c r="J280" s="1"/>
+      <c r="K280" s="1"/>
+      <c r="L280" s="1"/>
+      <c r="M280" s="1"/>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A281" s="1"/>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
+      <c r="E281" s="1"/>
+      <c r="F281" s="1"/>
+      <c r="G281" s="1"/>
+      <c r="H281" s="1"/>
+      <c r="I281" s="1"/>
+      <c r="J281" s="1"/>
+      <c r="K281" s="1"/>
+      <c r="L281" s="1"/>
+      <c r="M281" s="1"/>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A282" s="1"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
+      <c r="E282" s="1"/>
+      <c r="F282" s="1"/>
+      <c r="G282" s="1"/>
+      <c r="H282" s="1"/>
+      <c r="I282" s="1"/>
+      <c r="J282" s="1"/>
+      <c r="K282" s="1"/>
+      <c r="L282" s="1"/>
+      <c r="M282" s="1"/>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A283" s="1"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
+      <c r="E283" s="1"/>
+      <c r="F283" s="1"/>
+      <c r="G283" s="1"/>
+      <c r="H283" s="1"/>
+      <c r="I283" s="1"/>
+      <c r="J283" s="1"/>
+      <c r="K283" s="1"/>
+      <c r="L283" s="1"/>
+      <c r="M283" s="1"/>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A284" s="1"/>
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
+      <c r="E284" s="1"/>
+      <c r="F284" s="1"/>
+      <c r="G284" s="1"/>
+      <c r="H284" s="1"/>
+      <c r="I284" s="1"/>
+      <c r="J284" s="1"/>
+      <c r="K284" s="1"/>
+      <c r="L284" s="1"/>
+      <c r="M284" s="1"/>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A285" s="1"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
+      <c r="E285" s="1"/>
+      <c r="F285" s="1"/>
+      <c r="G285" s="1"/>
+      <c r="H285" s="1"/>
+      <c r="I285" s="1"/>
+      <c r="J285" s="1"/>
+      <c r="K285" s="1"/>
+      <c r="L285" s="1"/>
+      <c r="M285" s="1"/>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A286" s="1"/>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
+      <c r="E286" s="1"/>
+      <c r="F286" s="1"/>
+      <c r="G286" s="1"/>
+      <c r="H286" s="1"/>
+      <c r="I286" s="1"/>
+      <c r="J286" s="1"/>
+      <c r="K286" s="1"/>
+      <c r="L286" s="1"/>
+      <c r="M286" s="1"/>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A287" s="1"/>
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
+      <c r="E287" s="1"/>
+      <c r="F287" s="1"/>
+      <c r="G287" s="1"/>
+      <c r="H287" s="1"/>
+      <c r="I287" s="1"/>
+      <c r="J287" s="1"/>
+      <c r="K287" s="1"/>
+      <c r="L287" s="1"/>
+      <c r="M287" s="1"/>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A288" s="1"/>
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
+      <c r="E288" s="1"/>
+      <c r="F288" s="1"/>
+      <c r="G288" s="1"/>
+      <c r="H288" s="1"/>
+      <c r="I288" s="1"/>
+      <c r="J288" s="1"/>
+      <c r="K288" s="1"/>
+      <c r="L288" s="1"/>
+      <c r="M288" s="1"/>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A289" s="1"/>
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
+      <c r="E289" s="1"/>
+      <c r="F289" s="1"/>
+      <c r="G289" s="1"/>
+      <c r="H289" s="1"/>
+      <c r="I289" s="1"/>
+      <c r="J289" s="1"/>
+      <c r="K289" s="1"/>
+      <c r="L289" s="1"/>
+      <c r="M289" s="1"/>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A290" s="1"/>
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
+      <c r="E290" s="1"/>
+      <c r="F290" s="1"/>
+      <c r="G290" s="1"/>
+      <c r="H290" s="1"/>
+      <c r="I290" s="1"/>
+      <c r="J290" s="1"/>
+      <c r="K290" s="1"/>
+      <c r="L290" s="1"/>
+      <c r="M290" s="1"/>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A291" s="1"/>
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
+      <c r="E291" s="1"/>
+      <c r="F291" s="1"/>
+      <c r="G291" s="1"/>
+      <c r="H291" s="1"/>
+      <c r="I291" s="1"/>
+      <c r="J291" s="1"/>
+      <c r="K291" s="1"/>
+      <c r="L291" s="1"/>
+      <c r="M291" s="1"/>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A292" s="1"/>
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
+      <c r="E292" s="1"/>
+      <c r="F292" s="1"/>
+      <c r="G292" s="1"/>
+      <c r="H292" s="1"/>
+      <c r="I292" s="1"/>
+      <c r="J292" s="1"/>
+      <c r="K292" s="1"/>
+      <c r="L292" s="1"/>
+      <c r="M292" s="1"/>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A293" s="1"/>
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
+      <c r="E293" s="1"/>
+      <c r="F293" s="1"/>
+      <c r="G293" s="1"/>
+      <c r="H293" s="1"/>
+      <c r="I293" s="1"/>
+      <c r="J293" s="1"/>
+      <c r="K293" s="1"/>
+      <c r="L293" s="1"/>
+      <c r="M293" s="1"/>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A294" s="1"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
+      <c r="E294" s="1"/>
+      <c r="F294" s="1"/>
+      <c r="G294" s="1"/>
+      <c r="H294" s="1"/>
+      <c r="I294" s="1"/>
+      <c r="J294" s="1"/>
+      <c r="K294" s="1"/>
+      <c r="L294" s="1"/>
+      <c r="M294" s="1"/>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A295" s="1"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
+      <c r="E295" s="1"/>
+      <c r="F295" s="1"/>
+      <c r="G295" s="1"/>
+      <c r="H295" s="1"/>
+      <c r="I295" s="1"/>
+      <c r="J295" s="1"/>
+      <c r="K295" s="1"/>
+      <c r="L295" s="1"/>
+      <c r="M295" s="1"/>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A296" s="1"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="1"/>
+      <c r="E296" s="1"/>
+      <c r="F296" s="1"/>
+      <c r="G296" s="1"/>
+      <c r="H296" s="1"/>
+      <c r="I296" s="1"/>
+      <c r="J296" s="1"/>
+      <c r="K296" s="1"/>
+      <c r="L296" s="1"/>
+      <c r="M296" s="1"/>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A297" s="1"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="1"/>
+      <c r="E297" s="1"/>
+      <c r="F297" s="1"/>
+      <c r="G297" s="1"/>
+      <c r="H297" s="1"/>
+      <c r="I297" s="1"/>
+      <c r="J297" s="1"/>
+      <c r="K297" s="1"/>
+      <c r="L297" s="1"/>
+      <c r="M297" s="1"/>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A298" s="1"/>
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="1"/>
+      <c r="E298" s="1"/>
+      <c r="F298" s="1"/>
+      <c r="G298" s="1"/>
+      <c r="H298" s="1"/>
+      <c r="I298" s="1"/>
+      <c r="J298" s="1"/>
+      <c r="K298" s="1"/>
+      <c r="L298" s="1"/>
+      <c r="M298" s="1"/>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A299" s="1"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
+      <c r="E299" s="1"/>
+      <c r="F299" s="1"/>
+      <c r="G299" s="1"/>
+      <c r="H299" s="1"/>
+      <c r="I299" s="1"/>
+      <c r="J299" s="1"/>
+      <c r="K299" s="1"/>
+      <c r="L299" s="1"/>
+      <c r="M299" s="1"/>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A300" s="1"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="1"/>
+      <c r="E300" s="1"/>
+      <c r="F300" s="1"/>
+      <c r="G300" s="1"/>
+      <c r="H300" s="1"/>
+      <c r="I300" s="1"/>
+      <c r="J300" s="1"/>
+      <c r="K300" s="1"/>
+      <c r="L300" s="1"/>
+      <c r="M300" s="1"/>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A301" s="1"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="1"/>
+      <c r="E301" s="1"/>
+      <c r="F301" s="1"/>
+      <c r="G301" s="1"/>
+      <c r="H301" s="1"/>
+      <c r="I301" s="1"/>
+      <c r="J301" s="1"/>
+      <c r="K301" s="1"/>
+      <c r="L301" s="1"/>
+      <c r="M301" s="1"/>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A302" s="1"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="1"/>
+      <c r="E302" s="1"/>
+      <c r="F302" s="1"/>
+      <c r="G302" s="1"/>
+      <c r="H302" s="1"/>
+      <c r="I302" s="1"/>
+      <c r="J302" s="1"/>
+      <c r="K302" s="1"/>
+      <c r="L302" s="1"/>
+      <c r="M302" s="1"/>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A303" s="1"/>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="1"/>
+      <c r="E303" s="1"/>
+      <c r="F303" s="1"/>
+      <c r="G303" s="1"/>
+      <c r="H303" s="1"/>
+      <c r="I303" s="1"/>
+      <c r="J303" s="1"/>
+      <c r="K303" s="1"/>
+      <c r="L303" s="1"/>
+      <c r="M303" s="1"/>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A304" s="1"/>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="1"/>
+      <c r="E304" s="1"/>
+      <c r="F304" s="1"/>
+      <c r="G304" s="1"/>
+      <c r="H304" s="1"/>
+      <c r="I304" s="1"/>
+      <c r="J304" s="1"/>
+      <c r="K304" s="1"/>
+      <c r="L304" s="1"/>
+      <c r="M304" s="1"/>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A305" s="1"/>
+      <c r="B305" s="1"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="1"/>
+      <c r="E305" s="1"/>
+      <c r="F305" s="1"/>
+      <c r="G305" s="1"/>
+      <c r="H305" s="1"/>
+      <c r="I305" s="1"/>
+      <c r="J305" s="1"/>
+      <c r="K305" s="1"/>
+      <c r="L305" s="1"/>
+      <c r="M305" s="1"/>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A306" s="1"/>
+      <c r="B306" s="1"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="1"/>
+      <c r="E306" s="1"/>
+      <c r="F306" s="1"/>
+      <c r="G306" s="1"/>
+      <c r="H306" s="1"/>
+      <c r="I306" s="1"/>
+      <c r="J306" s="1"/>
+      <c r="K306" s="1"/>
+      <c r="L306" s="1"/>
+      <c r="M306" s="1"/>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A307" s="1"/>
+      <c r="B307" s="1"/>
+      <c r="C307" s="1"/>
+      <c r="D307" s="1"/>
+      <c r="E307" s="1"/>
+      <c r="F307" s="1"/>
+      <c r="G307" s="1"/>
+      <c r="H307" s="1"/>
+      <c r="I307" s="1"/>
+      <c r="J307" s="1"/>
+      <c r="K307" s="1"/>
+      <c r="L307" s="1"/>
+      <c r="M307" s="1"/>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A308" s="1"/>
+      <c r="B308" s="1"/>
+      <c r="C308" s="1"/>
+      <c r="D308" s="1"/>
+      <c r="E308" s="1"/>
+      <c r="F308" s="1"/>
+      <c r="G308" s="1"/>
+      <c r="H308" s="1"/>
+      <c r="I308" s="1"/>
+      <c r="J308" s="1"/>
+      <c r="K308" s="1"/>
+      <c r="L308" s="1"/>
+      <c r="M308" s="1"/>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A309" s="1"/>
+      <c r="B309" s="1"/>
+      <c r="C309" s="1"/>
+      <c r="D309" s="1"/>
+      <c r="E309" s="1"/>
+      <c r="F309" s="1"/>
+      <c r="G309" s="1"/>
+      <c r="H309" s="1"/>
+      <c r="I309" s="1"/>
+      <c r="J309" s="1"/>
+      <c r="K309" s="1"/>
+      <c r="L309" s="1"/>
+      <c r="M309" s="1"/>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A310" s="1"/>
+      <c r="B310" s="1"/>
+      <c r="C310" s="1"/>
+      <c r="D310" s="1"/>
+      <c r="E310" s="1"/>
+      <c r="F310" s="1"/>
+      <c r="G310" s="1"/>
+      <c r="H310" s="1"/>
+      <c r="I310" s="1"/>
+      <c r="J310" s="1"/>
+      <c r="K310" s="1"/>
+      <c r="L310" s="1"/>
+      <c r="M310" s="1"/>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A311" s="1"/>
+      <c r="B311" s="1"/>
+      <c r="C311" s="1"/>
+      <c r="D311" s="1"/>
+      <c r="E311" s="1"/>
+      <c r="F311" s="1"/>
+      <c r="G311" s="1"/>
+      <c r="H311" s="1"/>
+      <c r="I311" s="1"/>
+      <c r="J311" s="1"/>
+      <c r="K311" s="1"/>
+      <c r="L311" s="1"/>
+      <c r="M311" s="1"/>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A312" s="1"/>
+      <c r="B312" s="1"/>
+      <c r="C312" s="1"/>
+      <c r="D312" s="1"/>
+      <c r="E312" s="1"/>
+      <c r="F312" s="1"/>
+      <c r="G312" s="1"/>
+      <c r="H312" s="1"/>
+      <c r="I312" s="1"/>
+      <c r="J312" s="1"/>
+      <c r="K312" s="1"/>
+      <c r="L312" s="1"/>
+      <c r="M312" s="1"/>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A313" s="1"/>
+      <c r="B313" s="1"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
+      <c r="E313" s="1"/>
+      <c r="F313" s="1"/>
+      <c r="G313" s="1"/>
+      <c r="H313" s="1"/>
+      <c r="I313" s="1"/>
+      <c r="J313" s="1"/>
+      <c r="K313" s="1"/>
+      <c r="L313" s="1"/>
+      <c r="M313" s="1"/>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A314" s="1"/>
+      <c r="B314" s="1"/>
+      <c r="C314" s="1"/>
+      <c r="D314" s="1"/>
+      <c r="E314" s="1"/>
+      <c r="F314" s="1"/>
+      <c r="G314" s="1"/>
+      <c r="H314" s="1"/>
+      <c r="I314" s="1"/>
+      <c r="J314" s="1"/>
+      <c r="K314" s="1"/>
+      <c r="L314" s="1"/>
+      <c r="M314" s="1"/>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A315" s="1"/>
+      <c r="B315" s="1"/>
+      <c r="C315" s="1"/>
+      <c r="D315" s="1"/>
+      <c r="E315" s="1"/>
+      <c r="F315" s="1"/>
+      <c r="G315" s="1"/>
+      <c r="H315" s="1"/>
+      <c r="I315" s="1"/>
+      <c r="J315" s="1"/>
+      <c r="K315" s="1"/>
+      <c r="L315" s="1"/>
+      <c r="M315" s="1"/>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A316" s="1"/>
+      <c r="B316" s="1"/>
+      <c r="C316" s="1"/>
+      <c r="D316" s="1"/>
+      <c r="E316" s="1"/>
+      <c r="F316" s="1"/>
+      <c r="G316" s="1"/>
+      <c r="H316" s="1"/>
+      <c r="I316" s="1"/>
+      <c r="J316" s="1"/>
+      <c r="K316" s="1"/>
+      <c r="L316" s="1"/>
+      <c r="M316" s="1"/>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A317" s="1"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1"/>
+      <c r="E317" s="1"/>
+      <c r="F317" s="1"/>
+      <c r="G317" s="1"/>
+      <c r="H317" s="1"/>
+      <c r="I317" s="1"/>
+      <c r="J317" s="1"/>
+      <c r="K317" s="1"/>
+      <c r="L317" s="1"/>
+      <c r="M317" s="1"/>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A318" s="1"/>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
+      <c r="D318" s="1"/>
+      <c r="E318" s="1"/>
+      <c r="F318" s="1"/>
+      <c r="G318" s="1"/>
+      <c r="H318" s="1"/>
+      <c r="I318" s="1"/>
+      <c r="J318" s="1"/>
+      <c r="K318" s="1"/>
+      <c r="L318" s="1"/>
+      <c r="M318" s="1"/>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A319" s="1"/>
+      <c r="B319" s="1"/>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1"/>
+      <c r="E319" s="1"/>
+      <c r="F319" s="1"/>
+      <c r="G319" s="1"/>
+      <c r="H319" s="1"/>
+      <c r="I319" s="1"/>
+      <c r="J319" s="1"/>
+      <c r="K319" s="1"/>
+      <c r="L319" s="1"/>
+      <c r="M319" s="1"/>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A320" s="1"/>
+      <c r="B320" s="1"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
+      <c r="E320" s="1"/>
+      <c r="F320" s="1"/>
+      <c r="G320" s="1"/>
+      <c r="H320" s="1"/>
+      <c r="I320" s="1"/>
+      <c r="J320" s="1"/>
+      <c r="K320" s="1"/>
+      <c r="L320" s="1"/>
+      <c r="M320" s="1"/>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A321" s="1"/>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1"/>
+      <c r="E321" s="1"/>
+      <c r="F321" s="1"/>
+      <c r="G321" s="1"/>
+      <c r="H321" s="1"/>
+      <c r="I321" s="1"/>
+      <c r="J321" s="1"/>
+      <c r="K321" s="1"/>
+      <c r="L321" s="1"/>
+      <c r="M321" s="1"/>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A322" s="1"/>
+      <c r="B322" s="1"/>
+      <c r="C322" s="1"/>
+      <c r="D322" s="1"/>
+      <c r="E322" s="1"/>
+      <c r="F322" s="1"/>
+      <c r="G322" s="1"/>
+      <c r="H322" s="1"/>
+      <c r="I322" s="1"/>
+      <c r="J322" s="1"/>
+      <c r="K322" s="1"/>
+      <c r="L322" s="1"/>
+      <c r="M322" s="1"/>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A323" s="1"/>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1"/>
+      <c r="E323" s="1"/>
+      <c r="F323" s="1"/>
+      <c r="G323" s="1"/>
+      <c r="H323" s="1"/>
+      <c r="I323" s="1"/>
+      <c r="J323" s="1"/>
+      <c r="K323" s="1"/>
+      <c r="L323" s="1"/>
+      <c r="M323" s="1"/>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A324" s="1"/>
+      <c r="B324" s="1"/>
+      <c r="C324" s="1"/>
+      <c r="D324" s="1"/>
+      <c r="E324" s="1"/>
+      <c r="F324" s="1"/>
+      <c r="G324" s="1"/>
+      <c r="H324" s="1"/>
+      <c r="I324" s="1"/>
+      <c r="J324" s="1"/>
+      <c r="K324" s="1"/>
+      <c r="L324" s="1"/>
+      <c r="M324" s="1"/>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A325" s="1"/>
+      <c r="B325" s="1"/>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1"/>
+      <c r="E325" s="1"/>
+      <c r="F325" s="1"/>
+      <c r="G325" s="1"/>
+      <c r="H325" s="1"/>
+      <c r="I325" s="1"/>
+      <c r="J325" s="1"/>
+      <c r="K325" s="1"/>
+      <c r="L325" s="1"/>
+      <c r="M325" s="1"/>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A326" s="1"/>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
+      <c r="D326" s="1"/>
+      <c r="E326" s="1"/>
+      <c r="F326" s="1"/>
+      <c r="G326" s="1"/>
+      <c r="H326" s="1"/>
+      <c r="I326" s="1"/>
+      <c r="J326" s="1"/>
+      <c r="K326" s="1"/>
+      <c r="L326" s="1"/>
+      <c r="M326" s="1"/>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A327" s="1"/>
+      <c r="B327" s="1"/>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
+      <c r="E327" s="1"/>
+      <c r="F327" s="1"/>
+      <c r="G327" s="1"/>
+      <c r="H327" s="1"/>
+      <c r="I327" s="1"/>
+      <c r="J327" s="1"/>
+      <c r="K327" s="1"/>
+      <c r="L327" s="1"/>
+      <c r="M327" s="1"/>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A328" s="1"/>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
+      <c r="D328" s="1"/>
+      <c r="E328" s="1"/>
+      <c r="F328" s="1"/>
+      <c r="G328" s="1"/>
+      <c r="H328" s="1"/>
+      <c r="I328" s="1"/>
+      <c r="J328" s="1"/>
+      <c r="K328" s="1"/>
+      <c r="L328" s="1"/>
+      <c r="M328" s="1"/>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A329" s="1"/>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1"/>
+      <c r="E329" s="1"/>
+      <c r="F329" s="1"/>
+      <c r="G329" s="1"/>
+      <c r="H329" s="1"/>
+      <c r="I329" s="1"/>
+      <c r="J329" s="1"/>
+      <c r="K329" s="1"/>
+      <c r="L329" s="1"/>
+      <c r="M329" s="1"/>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A330" s="1"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
+      <c r="D330" s="1"/>
+      <c r="E330" s="1"/>
+      <c r="F330" s="1"/>
+      <c r="G330" s="1"/>
+      <c r="H330" s="1"/>
+      <c r="I330" s="1"/>
+      <c r="J330" s="1"/>
+      <c r="K330" s="1"/>
+      <c r="L330" s="1"/>
+      <c r="M330" s="1"/>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A331" s="1"/>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1"/>
+      <c r="E331" s="1"/>
+      <c r="F331" s="1"/>
+      <c r="G331" s="1"/>
+      <c r="H331" s="1"/>
+      <c r="I331" s="1"/>
+      <c r="J331" s="1"/>
+      <c r="K331" s="1"/>
+      <c r="L331" s="1"/>
+      <c r="M331" s="1"/>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A332" s="1"/>
+      <c r="B332" s="1"/>
+      <c r="C332" s="1"/>
+      <c r="D332" s="1"/>
+      <c r="E332" s="1"/>
+      <c r="F332" s="1"/>
+      <c r="G332" s="1"/>
+      <c r="H332" s="1"/>
+      <c r="I332" s="1"/>
+      <c r="J332" s="1"/>
+      <c r="K332" s="1"/>
+      <c r="L332" s="1"/>
+      <c r="M332" s="1"/>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A333" s="1"/>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1"/>
+      <c r="E333" s="1"/>
+      <c r="F333" s="1"/>
+      <c r="G333" s="1"/>
+      <c r="H333" s="1"/>
+      <c r="I333" s="1"/>
+      <c r="J333" s="1"/>
+      <c r="K333" s="1"/>
+      <c r="L333" s="1"/>
+      <c r="M333" s="1"/>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A334" s="1"/>
+      <c r="B334" s="1"/>
+      <c r="C334" s="1"/>
+      <c r="D334" s="1"/>
+      <c r="E334" s="1"/>
+      <c r="F334" s="1"/>
+      <c r="G334" s="1"/>
+      <c r="H334" s="1"/>
+      <c r="I334" s="1"/>
+      <c r="J334" s="1"/>
+      <c r="K334" s="1"/>
+      <c r="L334" s="1"/>
+      <c r="M334" s="1"/>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A335" s="1"/>
+      <c r="B335" s="1"/>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1"/>
+      <c r="E335" s="1"/>
+      <c r="F335" s="1"/>
+      <c r="G335" s="1"/>
+      <c r="H335" s="1"/>
+      <c r="I335" s="1"/>
+      <c r="J335" s="1"/>
+      <c r="K335" s="1"/>
+      <c r="L335" s="1"/>
+      <c r="M335" s="1"/>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A336" s="1"/>
+      <c r="B336" s="1"/>
+      <c r="C336" s="1"/>
+      <c r="D336" s="1"/>
+      <c r="E336" s="1"/>
+      <c r="F336" s="1"/>
+      <c r="G336" s="1"/>
+      <c r="H336" s="1"/>
+      <c r="I336" s="1"/>
+      <c r="J336" s="1"/>
+      <c r="K336" s="1"/>
+      <c r="L336" s="1"/>
+      <c r="M336" s="1"/>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A337" s="1"/>
+      <c r="B337" s="1"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1"/>
+      <c r="E337" s="1"/>
+      <c r="F337" s="1"/>
+      <c r="G337" s="1"/>
+      <c r="H337" s="1"/>
+      <c r="I337" s="1"/>
+      <c r="J337" s="1"/>
+      <c r="K337" s="1"/>
+      <c r="L337" s="1"/>
+      <c r="M337" s="1"/>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A338" s="1"/>
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
+      <c r="E338" s="1"/>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
+      <c r="H338" s="1"/>
+      <c r="I338" s="1"/>
+      <c r="J338" s="1"/>
+      <c r="K338" s="1"/>
+      <c r="L338" s="1"/>
+      <c r="M338" s="1"/>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A339" s="1"/>
+      <c r="B339" s="1"/>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1"/>
+      <c r="E339" s="1"/>
+      <c r="F339" s="1"/>
+      <c r="G339" s="1"/>
+      <c r="H339" s="1"/>
+      <c r="I339" s="1"/>
+      <c r="J339" s="1"/>
+      <c r="K339" s="1"/>
+      <c r="L339" s="1"/>
+      <c r="M339" s="1"/>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A340" s="1"/>
+      <c r="B340" s="1"/>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
+      <c r="E340" s="1"/>
+      <c r="F340" s="1"/>
+      <c r="G340" s="1"/>
+      <c r="H340" s="1"/>
+      <c r="I340" s="1"/>
+      <c r="J340" s="1"/>
+      <c r="K340" s="1"/>
+      <c r="L340" s="1"/>
+      <c r="M340" s="1"/>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A341" s="1"/>
+      <c r="B341" s="1"/>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1"/>
+      <c r="E341" s="1"/>
+      <c r="F341" s="1"/>
+      <c r="G341" s="1"/>
+      <c r="H341" s="1"/>
+      <c r="I341" s="1"/>
+      <c r="J341" s="1"/>
+      <c r="K341" s="1"/>
+      <c r="L341" s="1"/>
+      <c r="M341" s="1"/>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A342" s="1"/>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1"/>
+      <c r="E342" s="1"/>
+      <c r="F342" s="1"/>
+      <c r="G342" s="1"/>
+      <c r="H342" s="1"/>
+      <c r="I342" s="1"/>
+      <c r="J342" s="1"/>
+      <c r="K342" s="1"/>
+      <c r="L342" s="1"/>
+      <c r="M342" s="1"/>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A343" s="1"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1"/>
+      <c r="E343" s="1"/>
+      <c r="F343" s="1"/>
+      <c r="G343" s="1"/>
+      <c r="H343" s="1"/>
+      <c r="I343" s="1"/>
+      <c r="J343" s="1"/>
+      <c r="K343" s="1"/>
+      <c r="L343" s="1"/>
+      <c r="M343" s="1"/>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A344" s="1"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1"/>
+      <c r="E344" s="1"/>
+      <c r="F344" s="1"/>
+      <c r="G344" s="1"/>
+      <c r="H344" s="1"/>
+      <c r="I344" s="1"/>
+      <c r="J344" s="1"/>
+      <c r="K344" s="1"/>
+      <c r="L344" s="1"/>
+      <c r="M344" s="1"/>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A345" s="1"/>
+      <c r="B345" s="1"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1"/>
+      <c r="E345" s="1"/>
+      <c r="F345" s="1"/>
+      <c r="G345" s="1"/>
+      <c r="H345" s="1"/>
+      <c r="I345" s="1"/>
+      <c r="J345" s="1"/>
+      <c r="K345" s="1"/>
+      <c r="L345" s="1"/>
+      <c r="M345" s="1"/>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A346" s="1"/>
+      <c r="B346" s="1"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1"/>
+      <c r="E346" s="1"/>
+      <c r="F346" s="1"/>
+      <c r="G346" s="1"/>
+      <c r="H346" s="1"/>
+      <c r="I346" s="1"/>
+      <c r="J346" s="1"/>
+      <c r="K346" s="1"/>
+      <c r="L346" s="1"/>
+      <c r="M346" s="1"/>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A347" s="1"/>
+      <c r="B347" s="1"/>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1"/>
+      <c r="E347" s="1"/>
+      <c r="F347" s="1"/>
+      <c r="G347" s="1"/>
+      <c r="H347" s="1"/>
+      <c r="I347" s="1"/>
+      <c r="J347" s="1"/>
+      <c r="K347" s="1"/>
+      <c r="L347" s="1"/>
+      <c r="M347" s="1"/>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A348" s="1"/>
+      <c r="B348" s="1"/>
+      <c r="C348" s="1"/>
+      <c r="D348" s="1"/>
+      <c r="E348" s="1"/>
+      <c r="F348" s="1"/>
+      <c r="G348" s="1"/>
+      <c r="H348" s="1"/>
+      <c r="I348" s="1"/>
+      <c r="J348" s="1"/>
+      <c r="K348" s="1"/>
+      <c r="L348" s="1"/>
+      <c r="M348" s="1"/>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A349" s="1"/>
+      <c r="B349" s="1"/>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1"/>
+      <c r="E349" s="1"/>
+      <c r="G349" s="1"/>
+      <c r="H349" s="1"/>
+      <c r="I349" s="1"/>
+      <c r="J349" s="1"/>
+      <c r="K349" s="1"/>
+      <c r="L349" s="1"/>
+      <c r="M349" s="1"/>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A350" s="1"/>
+      <c r="B350" s="1"/>
+      <c r="C350" s="1"/>
+      <c r="D350" s="1"/>
+      <c r="E350" s="1"/>
+      <c r="G350" s="1"/>
+      <c r="H350" s="1"/>
+      <c r="I350" s="1"/>
+      <c r="J350" s="1"/>
+      <c r="K350" s="1"/>
+      <c r="L350" s="1"/>
+      <c r="M350" s="1"/>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A351" s="1"/>
+      <c r="B351" s="1"/>
+      <c r="C351" s="1"/>
+      <c r="D351" s="1"/>
+      <c r="E351" s="1"/>
+      <c r="G351" s="1"/>
+      <c r="H351" s="1"/>
+      <c r="I351" s="1"/>
+      <c r="J351" s="1"/>
+      <c r="K351" s="1"/>
+      <c r="L351" s="1"/>
+      <c r="M351" s="1"/>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A352" s="1"/>
+      <c r="B352" s="1"/>
+      <c r="C352" s="1"/>
+      <c r="D352" s="1"/>
+      <c r="E352" s="1"/>
+      <c r="G352" s="1"/>
+      <c r="H352" s="1"/>
+      <c r="I352" s="1"/>
+      <c r="K352" s="1"/>
+      <c r="L352" s="1"/>
+      <c r="M352" s="1"/>
+    </row>
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A353" s="1"/>
+      <c r="B353" s="1"/>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
+      <c r="E353" s="1"/>
+      <c r="G353" s="1"/>
+      <c r="H353" s="1"/>
+      <c r="I353" s="1"/>
+      <c r="K353" s="1"/>
+      <c r="L353" s="1"/>
+      <c r="M353" s="1"/>
+    </row>
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A354" s="1"/>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
+      <c r="E354" s="1"/>
+      <c r="G354" s="1"/>
+      <c r="H354" s="1"/>
+      <c r="I354" s="1"/>
+      <c r="K354" s="1"/>
+      <c r="L354" s="1"/>
+      <c r="M354" s="1"/>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A355" s="1"/>
+      <c r="B355" s="1"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="1"/>
+      <c r="E355" s="1"/>
+      <c r="G355" s="1"/>
+      <c r="H355" s="1"/>
+      <c r="I355" s="1"/>
+      <c r="K355" s="1"/>
+      <c r="L355" s="1"/>
+      <c r="M355" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D488EF-E804-B94F-B0C7-D228244B0966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7D0A9F-484B-9A4D-920C-C0D03D60DD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15180" yWindow="920" windowWidth="14900" windowHeight="17220" activeTab="3" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="6120" yWindow="880" windowWidth="14900" windowHeight="17220" activeTab="3" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="keywords" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="313">
   <si>
     <t>DIABETES</t>
   </si>
@@ -974,10 +974,10 @@
     <t>HOMICIDE KEYWORDS</t>
   </si>
   <si>
-    <t>NON-COMMUNICABLE DISEASE KEYWORDS</t>
-  </si>
-  <si>
     <t>COMMUNICABLE DISEASE KEYWORDS</t>
+  </si>
+  <si>
+    <t>NON-COMMUNICABLE DISEASE/ILLNESS</t>
   </si>
 </sst>
 </file>
@@ -10976,7 +10976,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9374F8-5EC0-2B4D-B147-6130FD66FA7B}">
-  <dimension ref="A1:O355"/>
+  <dimension ref="A1:N355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="21.5" customWidth="1"/>
@@ -10984,15 +10984,15 @@
     <col min="4" max="5" width="43.5" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" customWidth="1"/>
     <col min="7" max="7" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="24.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="23.33203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="33.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>220</v>
       </c>
@@ -11015,29 +11015,26 @@
         <v>224</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>311</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>219</v>
       </c>
@@ -11062,25 +11059,24 @@
       <c r="H2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>215</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>213</v>
       </c>
@@ -11105,25 +11101,24 @@
       <c r="H3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="J3" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>208</v>
+        <v>1</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
@@ -11148,23 +11143,22 @@
       <c r="H4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="K4" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="L4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="M4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>202</v>
       </c>
@@ -11189,18 +11183,17 @@
       <c r="H5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>197</v>
       </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>196</v>
       </c>
@@ -11223,18 +11216,17 @@
         <v>5</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="J6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="1" t="s">
         <v>193</v>
       </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>192</v>
       </c>
@@ -11255,18 +11247,17 @@
         <v>115</v>
       </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="K7" s="1" t="s">
         <v>189</v>
       </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>188</v>
       </c>
@@ -11287,18 +11278,17 @@
         <v>194</v>
       </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>186</v>
       </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>185</v>
       </c>
@@ -11316,18 +11306,17 @@
         <v>21</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>180</v>
       </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>179</v>
       </c>
@@ -11348,16 +11337,15 @@
         <v>47</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>176</v>
       </c>
@@ -11378,16 +11366,15 @@
         <v>182</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>86</v>
       </c>
@@ -11406,16 +11393,15 @@
         <v>177</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>172</v>
       </c>
@@ -11434,16 +11420,15 @@
         <v>173</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>168</v>
       </c>
@@ -11462,16 +11447,15 @@
         <v>169</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>162</v>
       </c>
+      <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
@@ -11488,16 +11472,15 @@
         <v>43</v>
       </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>144</v>
       </c>
+      <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>161</v>
       </c>
@@ -11514,16 +11497,15 @@
         <v>163</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>157</v>
       </c>
+      <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
@@ -11538,16 +11520,15 @@
         <v>158</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>154</v>
       </c>
@@ -11562,16 +11543,15 @@
         <v>25</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>153</v>
       </c>
@@ -11586,16 +11566,15 @@
         <v>22</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>150</v>
       </c>
+      <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -11610,16 +11589,15 @@
         <v>151</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>148</v>
       </c>
+      <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>147</v>
       </c>
@@ -11631,16 +11609,15 @@
         <v>149</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>143</v>
       </c>
@@ -11652,16 +11629,15 @@
         <v>145</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>139</v>
       </c>
+      <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>140</v>
       </c>
@@ -11673,16 +11649,15 @@
         <v>126</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>138</v>
       </c>
@@ -11694,16 +11669,15 @@
         <v>123</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>134</v>
       </c>
@@ -11715,16 +11689,15 @@
         <v>141</v>
       </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>129</v>
       </c>
+      <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>132</v>
       </c>
@@ -11736,16 +11709,15 @@
         <v>29</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>128</v>
       </c>
@@ -11758,16 +11730,15 @@
         <v>113</v>
       </c>
       <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>124</v>
       </c>
@@ -11779,16 +11750,15 @@
         <v>136</v>
       </c>
       <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>121</v>
       </c>
@@ -11800,16 +11770,15 @@
         <v>6</v>
       </c>
       <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>119</v>
       </c>
@@ -11821,16 +11790,15 @@
         <v>120</v>
       </c>
       <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>118</v>
       </c>
@@ -11842,16 +11810,15 @@
         <v>130</v>
       </c>
       <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>116</v>
       </c>
@@ -11863,16 +11830,15 @@
         <v>230</v>
       </c>
       <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>114</v>
       </c>
@@ -11882,16 +11848,15 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>111</v>
       </c>
@@ -11902,16 +11867,15 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1" t="s">
+      <c r="I34" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>109</v>
       </c>
@@ -11922,16 +11886,15 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>108</v>
       </c>
@@ -11942,16 +11905,15 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>107</v>
       </c>
@@ -11962,16 +11924,15 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>105</v>
       </c>
@@ -11982,16 +11943,15 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>227</v>
       </c>
@@ -12002,16 +11962,15 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>88</v>
       </c>
@@ -12022,16 +11981,15 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>103</v>
       </c>
@@ -12042,16 +12000,15 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="O41" s="1"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>101</v>
       </c>
@@ -12062,16 +12019,15 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="O42" s="1"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>99</v>
       </c>
@@ -12082,16 +12038,15 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="O43" s="1"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>98</v>
       </c>
@@ -12102,16 +12057,15 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1" t="s">
+      <c r="I44" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="O44" s="1"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>96</v>
       </c>
@@ -12122,15 +12076,14 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-    </row>
-    <row r="46" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>94</v>
       </c>
@@ -12141,15 +12094,14 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="2" t="s">
+      <c r="I46" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>92</v>
       </c>
@@ -12160,15 +12112,14 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>91</v>
       </c>
@@ -12179,15 +12130,14 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-    </row>
-    <row r="49" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>90</v>
       </c>
@@ -12198,15 +12148,14 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="2" t="s">
+      <c r="I49" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>229</v>
       </c>
@@ -12217,15 +12166,14 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>66</v>
       </c>
+      <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>234</v>
       </c>
@@ -12235,15 +12183,14 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1" t="s">
+      <c r="I51" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>235</v>
       </c>
@@ -12254,15 +12201,14 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1" t="s">
+      <c r="I52" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>236</v>
       </c>
@@ -12272,15 +12218,14 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>241</v>
       </c>
@@ -12290,15 +12235,14 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>219</v>
       </c>
@@ -12309,15 +12253,14 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1" t="s">
+      <c r="I55" s="1" t="s">
         <v>81</v>
       </c>
+      <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-    </row>
-    <row r="56" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>213</v>
       </c>
@@ -12328,15 +12271,14 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="2" t="s">
+      <c r="I56" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>188</v>
       </c>
@@ -12347,15 +12289,14 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>185</v>
       </c>
@@ -12366,15 +12307,14 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-    </row>
-    <row r="59" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>179</v>
       </c>
@@ -12385,15 +12325,14 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="2" t="s">
+      <c r="I59" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>176</v>
       </c>
@@ -12404,15 +12343,14 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1" t="s">
+      <c r="I60" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>86</v>
       </c>
@@ -12423,15 +12361,14 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>172</v>
       </c>
@@ -12442,15 +12379,14 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1" t="s">
+      <c r="I62" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>168</v>
       </c>
@@ -12461,15 +12397,14 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1" t="s">
+      <c r="I63" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-    </row>
-    <row r="64" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
@@ -12480,15 +12415,14 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="2" t="s">
+      <c r="I64" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>161</v>
       </c>
@@ -12499,15 +12433,14 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1" t="s">
+      <c r="I65" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>156</v>
       </c>
@@ -12518,15 +12451,14 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1" t="s">
+      <c r="I66" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>154</v>
       </c>
@@ -12537,15 +12469,14 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1" t="s">
+      <c r="I67" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-    </row>
-    <row r="68" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>153</v>
       </c>
@@ -12556,15 +12487,14 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="2" t="s">
+      <c r="I68" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>45</v>
       </c>
@@ -12575,15 +12505,14 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
@@ -12594,15 +12523,14 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1" t="s">
+      <c r="I70" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>138</v>
       </c>
@@ -12613,15 +12541,14 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1" t="s">
+      <c r="I71" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>134</v>
       </c>
@@ -12632,15 +12559,14 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1" t="s">
+      <c r="I72" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>132</v>
       </c>
@@ -12651,15 +12577,14 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1" t="s">
+      <c r="I73" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-    </row>
-    <row r="74" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>128</v>
       </c>
@@ -12670,15 +12595,14 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="2" t="s">
+      <c r="I74" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
-      <c r="M74" s="1"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>124</v>
       </c>
@@ -12689,15 +12613,14 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1" t="s">
+      <c r="I75" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>121</v>
       </c>
@@ -12708,15 +12631,14 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1" t="s">
+      <c r="I76" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>119</v>
       </c>
@@ -12727,15 +12649,14 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1" t="s">
+      <c r="I77" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>118</v>
       </c>
@@ -12746,15 +12667,14 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
-    </row>
-    <row r="79" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>116</v>
       </c>
@@ -12765,15 +12685,14 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="2" t="s">
+      <c r="I79" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>114</v>
       </c>
@@ -12784,15 +12703,14 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1" t="s">
+      <c r="I80" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
-      <c r="M80" s="1"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>111</v>
       </c>
@@ -12803,15 +12721,14 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1" t="s">
+      <c r="I81" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
-      <c r="M81" s="1"/>
-    </row>
-    <row r="82" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -12822,15 +12739,14 @@
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="2" t="s">
+      <c r="I82" s="2" t="s">
         <v>68</v>
       </c>
+      <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>108</v>
       </c>
@@ -12841,15 +12757,14 @@
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1" t="s">
+      <c r="I83" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
-      <c r="M83" s="1"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>107</v>
       </c>
@@ -12860,15 +12775,14 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1" t="s">
+      <c r="I84" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
-      <c r="M84" s="1"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>105</v>
       </c>
@@ -12879,15 +12793,14 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1" t="s">
+      <c r="I85" s="1" t="s">
         <v>237</v>
       </c>
+      <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
-      <c r="M85" s="1"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>227</v>
       </c>
@@ -12898,15 +12811,14 @@
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1" t="s">
+      <c r="I86" s="1" t="s">
         <v>238</v>
       </c>
+      <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
-      <c r="M86" s="1"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -12917,15 +12829,14 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1" t="s">
+      <c r="I87" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
-      <c r="M87" s="1"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>103</v>
       </c>
@@ -12936,15 +12847,14 @@
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>240</v>
       </c>
+      <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
-      <c r="M88" s="1"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>101</v>
       </c>
@@ -12955,15 +12865,14 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1" t="s">
+      <c r="I89" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="J89" s="1"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
-      <c r="M89" s="1"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>99</v>
       </c>
@@ -12974,15 +12883,14 @@
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1" t="s">
+      <c r="I90" s="1" t="s">
         <v>243</v>
       </c>
+      <c r="J90" s="1"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
-      <c r="M90" s="1"/>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
@@ -12993,15 +12901,14 @@
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1" t="s">
+      <c r="I91" s="1" t="s">
         <v>244</v>
       </c>
+      <c r="J91" s="1"/>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
-      <c r="M91" s="1"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>96</v>
       </c>
@@ -13012,15 +12919,14 @@
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1" t="s">
+      <c r="I92" s="1" t="s">
         <v>245</v>
       </c>
+      <c r="J92" s="1"/>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
-      <c r="M92" s="1"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -13031,15 +12937,14 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1" t="s">
+      <c r="I93" s="1" t="s">
         <v>247</v>
       </c>
+      <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
-      <c r="M93" s="1"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -13050,15 +12955,14 @@
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1" t="s">
+      <c r="I94" s="1" t="s">
         <v>248</v>
       </c>
+      <c r="J94" s="1"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
-      <c r="M94" s="1"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>91</v>
       </c>
@@ -13069,15 +12973,14 @@
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1" t="s">
+      <c r="I95" s="1" t="s">
         <v>250</v>
       </c>
+      <c r="J95" s="1"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
-      <c r="M95" s="1"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>90</v>
       </c>
@@ -13088,15 +12991,14 @@
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1" t="s">
+      <c r="I96" s="1" t="s">
         <v>251</v>
       </c>
+      <c r="J96" s="1"/>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
-      <c r="M96" s="1"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>229</v>
       </c>
@@ -13107,15 +13009,14 @@
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1" t="s">
+      <c r="I97" s="1" t="s">
         <v>252</v>
       </c>
+      <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
-      <c r="M97" s="1"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -13124,15 +13025,14 @@
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1" t="s">
+      <c r="I98" s="1" t="s">
         <v>253</v>
       </c>
+      <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
-      <c r="M98" s="1"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -13141,15 +13041,14 @@
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1" t="s">
+      <c r="I99" s="1" t="s">
         <v>254</v>
       </c>
+      <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
-      <c r="M99" s="1"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -13158,15 +13057,14 @@
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1" t="s">
+      <c r="I100" s="1" t="s">
         <v>255</v>
       </c>
+      <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
-      <c r="M100" s="1"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -13175,15 +13073,14 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1" t="s">
+      <c r="I101" s="1" t="s">
         <v>256</v>
       </c>
+      <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
-      <c r="M101" s="1"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -13192,15 +13089,14 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1" t="s">
+      <c r="I102" s="1" t="s">
         <v>257</v>
       </c>
+      <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
-      <c r="M102" s="1"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -13209,15 +13105,14 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1" t="s">
+      <c r="I103" s="1" t="s">
         <v>258</v>
       </c>
+      <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
-      <c r="M103" s="1"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -13226,15 +13121,14 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1" t="s">
+      <c r="I104" s="1" t="s">
         <v>259</v>
       </c>
+      <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
-      <c r="M104" s="1"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -13243,15 +13137,14 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>260</v>
       </c>
+      <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
-      <c r="M105" s="1"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -13260,15 +13153,14 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>261</v>
       </c>
+      <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
-      <c r="M106" s="1"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -13277,15 +13169,14 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1" t="s">
+      <c r="I107" s="1" t="s">
         <v>264</v>
       </c>
+      <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -13294,15 +13185,14 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1" t="s">
+      <c r="I108" s="1" t="s">
         <v>265</v>
       </c>
+      <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
-      <c r="M108" s="1"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -13311,15 +13201,14 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1" t="s">
+      <c r="I109" s="1" t="s">
         <v>266</v>
       </c>
+      <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
-      <c r="M109" s="1"/>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -13328,15 +13217,14 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1" t="s">
+      <c r="I110" s="1" t="s">
         <v>267</v>
       </c>
+      <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
-      <c r="M110" s="1"/>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -13345,15 +13233,14 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1" t="s">
+      <c r="I111" s="1" t="s">
         <v>268</v>
       </c>
+      <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
-      <c r="M111" s="1"/>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -13362,15 +13249,14 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1" t="s">
+      <c r="I112" s="1" t="s">
         <v>269</v>
       </c>
+      <c r="J112" s="1"/>
       <c r="K112" s="1"/>
       <c r="L112" s="1"/>
-      <c r="M112" s="1"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -13379,15 +13265,14 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1" t="s">
+      <c r="I113" s="1" t="s">
         <v>270</v>
       </c>
+      <c r="J113" s="1"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
-      <c r="M113" s="1"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -13396,15 +13281,14 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1" t="s">
+      <c r="I114" s="1" t="s">
         <v>272</v>
       </c>
+      <c r="J114" s="1"/>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
-      <c r="M114" s="1"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -13413,15 +13297,14 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1" t="s">
+      <c r="I115" s="1" t="s">
         <v>273</v>
       </c>
+      <c r="J115" s="1"/>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
-      <c r="M115" s="1"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -13430,15 +13313,14 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1" t="s">
+      <c r="I116" s="1" t="s">
         <v>274</v>
       </c>
+      <c r="J116" s="1"/>
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
-      <c r="M116" s="1"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -13447,15 +13329,14 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1" t="s">
+      <c r="I117" s="1" t="s">
         <v>276</v>
       </c>
+      <c r="J117" s="1"/>
       <c r="K117" s="1"/>
       <c r="L117" s="1"/>
-      <c r="M117" s="1"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -13464,15 +13345,14 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="1" t="s">
+      <c r="I118" s="1" t="s">
         <v>277</v>
       </c>
+      <c r="J118" s="1"/>
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
-      <c r="M118" s="1"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -13481,15 +13361,14 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
-      <c r="I119" s="1"/>
-      <c r="J119" s="1" t="s">
+      <c r="I119" s="1" t="s">
         <v>278</v>
       </c>
+      <c r="J119" s="1"/>
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
-      <c r="M119" s="1"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -13498,15 +13377,14 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1" t="s">
+      <c r="I120" s="1" t="s">
         <v>279</v>
       </c>
+      <c r="J120" s="1"/>
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
-      <c r="M120" s="1"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -13515,15 +13393,14 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
-      <c r="I121" s="1"/>
-      <c r="J121" s="1" t="s">
+      <c r="I121" s="1" t="s">
         <v>280</v>
       </c>
+      <c r="J121" s="1"/>
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
-      <c r="M121" s="1"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -13532,15 +13409,14 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1" t="s">
+      <c r="I122" s="1" t="s">
         <v>281</v>
       </c>
+      <c r="J122" s="1"/>
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
-      <c r="M122" s="1"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -13549,15 +13425,14 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1" t="s">
+      <c r="I123" s="1" t="s">
         <v>282</v>
       </c>
+      <c r="J123" s="1"/>
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
-      <c r="M123" s="1"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -13566,15 +13441,14 @@
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1" t="s">
+      <c r="I124" s="1" t="s">
         <v>283</v>
       </c>
+      <c r="J124" s="1"/>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
-      <c r="M124" s="1"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -13583,15 +13457,14 @@
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1" t="s">
+      <c r="I125" s="1" t="s">
         <v>284</v>
       </c>
+      <c r="J125" s="1"/>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
-      <c r="M125" s="1"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -13600,15 +13473,14 @@
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>285</v>
       </c>
+      <c r="J126" s="1"/>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -13617,15 +13489,14 @@
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1" t="s">
+      <c r="I127" s="1" t="s">
         <v>286</v>
       </c>
+      <c r="J127" s="1"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
-      <c r="M127" s="1"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -13634,15 +13505,14 @@
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1" t="s">
+      <c r="I128" s="1" t="s">
         <v>288</v>
       </c>
+      <c r="J128" s="1"/>
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
-      <c r="M128" s="1"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -13651,15 +13521,14 @@
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
-      <c r="J129" s="1" t="s">
+      <c r="I129" s="1" t="s">
         <v>289</v>
       </c>
+      <c r="J129" s="1"/>
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
-      <c r="M129" s="1"/>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -13668,15 +13537,14 @@
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1" t="s">
+      <c r="I130" s="1" t="s">
         <v>290</v>
       </c>
+      <c r="J130" s="1"/>
       <c r="K130" s="1"/>
       <c r="L130" s="1"/>
-      <c r="M130" s="1"/>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -13685,15 +13553,14 @@
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1" t="s">
+      <c r="I131" s="1" t="s">
         <v>291</v>
       </c>
+      <c r="J131" s="1"/>
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
-      <c r="M131" s="1"/>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -13702,15 +13569,14 @@
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
       <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1" t="s">
+      <c r="I132" s="1" t="s">
         <v>292</v>
       </c>
+      <c r="J132" s="1"/>
       <c r="K132" s="1"/>
       <c r="L132" s="1"/>
-      <c r="M132" s="1"/>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -13719,15 +13585,14 @@
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1" t="s">
+      <c r="I133" s="1" t="s">
         <v>293</v>
       </c>
+      <c r="J133" s="1"/>
       <c r="K133" s="1"/>
       <c r="L133" s="1"/>
-      <c r="M133" s="1"/>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -13736,15 +13601,14 @@
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1" t="s">
+      <c r="I134" s="1" t="s">
         <v>294</v>
       </c>
+      <c r="J134" s="1"/>
       <c r="K134" s="1"/>
       <c r="L134" s="1"/>
-      <c r="M134" s="1"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -13753,15 +13617,14 @@
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
-      <c r="I135" s="1"/>
-      <c r="J135" s="1" t="s">
+      <c r="I135" s="1" t="s">
         <v>295</v>
       </c>
+      <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
-      <c r="M135" s="1"/>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -13770,15 +13633,14 @@
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="1" t="s">
+      <c r="I136" s="1" t="s">
         <v>296</v>
       </c>
+      <c r="J136" s="1"/>
       <c r="K136" s="1"/>
       <c r="L136" s="1"/>
-      <c r="M136" s="1"/>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -13787,15 +13649,14 @@
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1" t="s">
+      <c r="I137" s="1" t="s">
         <v>298</v>
       </c>
+      <c r="J137" s="1"/>
       <c r="K137" s="1"/>
       <c r="L137" s="1"/>
-      <c r="M137" s="1"/>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -13804,15 +13665,14 @@
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
-      <c r="J138" s="1" t="s">
+      <c r="I138" s="1" t="s">
         <v>299</v>
       </c>
+      <c r="J138" s="1"/>
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
-      <c r="M138" s="1"/>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -13821,15 +13681,14 @@
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="1" t="s">
+      <c r="I139" s="1" t="s">
         <v>300</v>
       </c>
+      <c r="J139" s="1"/>
       <c r="K139" s="1"/>
       <c r="L139" s="1"/>
-      <c r="M139" s="1"/>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -13838,15 +13697,14 @@
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1" t="s">
+      <c r="I140" s="1" t="s">
         <v>302</v>
       </c>
+      <c r="J140" s="1"/>
       <c r="K140" s="1"/>
       <c r="L140" s="1"/>
-      <c r="M140" s="1"/>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -13855,15 +13713,14 @@
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="1" t="s">
+      <c r="I141" s="1" t="s">
         <v>303</v>
       </c>
+      <c r="J141" s="1"/>
       <c r="K141" s="1"/>
       <c r="L141" s="1"/>
-      <c r="M141" s="1"/>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -13872,15 +13729,14 @@
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
-      <c r="I142" s="1"/>
-      <c r="J142" s="1" t="s">
+      <c r="I142" s="1" t="s">
         <v>304</v>
       </c>
+      <c r="J142" s="1"/>
       <c r="K142" s="1"/>
       <c r="L142" s="1"/>
-      <c r="M142" s="1"/>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -13893,9 +13749,8 @@
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
-      <c r="M143" s="1"/>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -13908,9 +13763,8 @@
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="1"/>
-      <c r="M144" s="1"/>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -13923,9 +13777,8 @@
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
-      <c r="M145" s="1"/>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -13938,9 +13791,8 @@
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
       <c r="L146" s="1"/>
-      <c r="M146" s="1"/>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -13953,9 +13805,8 @@
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
       <c r="L147" s="1"/>
-      <c r="M147" s="1"/>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -13968,9 +13819,8 @@
       <c r="J148" s="1"/>
       <c r="K148" s="1"/>
       <c r="L148" s="1"/>
-      <c r="M148" s="1"/>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -13983,9 +13833,8 @@
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
       <c r="L149" s="1"/>
-      <c r="M149" s="1"/>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -13998,9 +13847,8 @@
       <c r="J150" s="1"/>
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
-      <c r="M150" s="1"/>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -14013,9 +13861,8 @@
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
-      <c r="M151" s="1"/>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -14028,9 +13875,8 @@
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
-      <c r="M152" s="1"/>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -14043,9 +13889,8 @@
       <c r="J153" s="1"/>
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
-      <c r="M153" s="1"/>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -14058,9 +13903,8 @@
       <c r="J154" s="1"/>
       <c r="K154" s="1"/>
       <c r="L154" s="1"/>
-      <c r="M154" s="1"/>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -14073,9 +13917,8 @@
       <c r="J155" s="1"/>
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
-      <c r="M155" s="1"/>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -14088,9 +13931,8 @@
       <c r="J156" s="1"/>
       <c r="K156" s="1"/>
       <c r="L156" s="1"/>
-      <c r="M156" s="1"/>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -14103,9 +13945,8 @@
       <c r="J157" s="1"/>
       <c r="K157" s="1"/>
       <c r="L157" s="1"/>
-      <c r="M157" s="1"/>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -14118,9 +13959,8 @@
       <c r="J158" s="1"/>
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
-      <c r="M158" s="1"/>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -14133,9 +13973,8 @@
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
-      <c r="M159" s="1"/>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -14148,9 +13987,8 @@
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
-      <c r="M160" s="1"/>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -14163,9 +14001,8 @@
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
-      <c r="M161" s="1"/>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -14178,9 +14015,8 @@
       <c r="J162" s="1"/>
       <c r="K162" s="1"/>
       <c r="L162" s="1"/>
-      <c r="M162" s="1"/>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -14193,9 +14029,8 @@
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
-      <c r="M163" s="1"/>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -14208,9 +14043,8 @@
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
       <c r="L164" s="1"/>
-      <c r="M164" s="1"/>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -14223,9 +14057,8 @@
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
-      <c r="M165" s="1"/>
-    </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -14238,9 +14071,8 @@
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
-      <c r="M166" s="1"/>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -14253,9 +14085,8 @@
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
-      <c r="M167" s="1"/>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -14268,9 +14099,8 @@
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
-      <c r="M168" s="1"/>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -14283,9 +14113,8 @@
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
       <c r="L169" s="1"/>
-      <c r="M169" s="1"/>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -14298,9 +14127,8 @@
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
-      <c r="M170" s="1"/>
-    </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -14313,9 +14141,8 @@
       <c r="J171" s="1"/>
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
-      <c r="M171" s="1"/>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -14328,9 +14155,8 @@
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
-      <c r="M172" s="1"/>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -14343,9 +14169,8 @@
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
-      <c r="M173" s="1"/>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -14358,9 +14183,8 @@
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
-      <c r="M174" s="1"/>
-    </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -14373,9 +14197,8 @@
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
-      <c r="M175" s="1"/>
-    </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -14388,9 +14211,8 @@
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
-      <c r="M176" s="1"/>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -14403,9 +14225,8 @@
       <c r="J177" s="1"/>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
-      <c r="M177" s="1"/>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -14418,9 +14239,8 @@
       <c r="J178" s="1"/>
       <c r="K178" s="1"/>
       <c r="L178" s="1"/>
-      <c r="M178" s="1"/>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -14433,9 +14253,8 @@
       <c r="J179" s="1"/>
       <c r="K179" s="1"/>
       <c r="L179" s="1"/>
-      <c r="M179" s="1"/>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -14448,9 +14267,8 @@
       <c r="J180" s="1"/>
       <c r="K180" s="1"/>
       <c r="L180" s="1"/>
-      <c r="M180" s="1"/>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -14463,9 +14281,8 @@
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
       <c r="L181" s="1"/>
-      <c r="M181" s="1"/>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -14478,9 +14295,8 @@
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
       <c r="L182" s="1"/>
-      <c r="M182" s="1"/>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -14493,9 +14309,8 @@
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
       <c r="L183" s="1"/>
-      <c r="M183" s="1"/>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -14508,9 +14323,8 @@
       <c r="J184" s="1"/>
       <c r="K184" s="1"/>
       <c r="L184" s="1"/>
-      <c r="M184" s="1"/>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -14523,9 +14337,8 @@
       <c r="J185" s="1"/>
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
-      <c r="M185" s="1"/>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -14538,9 +14351,8 @@
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
       <c r="L186" s="1"/>
-      <c r="M186" s="1"/>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -14553,9 +14365,8 @@
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
       <c r="L187" s="1"/>
-      <c r="M187" s="1"/>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -14568,9 +14379,8 @@
       <c r="J188" s="1"/>
       <c r="K188" s="1"/>
       <c r="L188" s="1"/>
-      <c r="M188" s="1"/>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -14583,9 +14393,8 @@
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
       <c r="L189" s="1"/>
-      <c r="M189" s="1"/>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -14598,9 +14407,8 @@
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
       <c r="L190" s="1"/>
-      <c r="M190" s="1"/>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -14613,9 +14421,8 @@
       <c r="J191" s="1"/>
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
-      <c r="M191" s="1"/>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -14628,9 +14435,8 @@
       <c r="J192" s="1"/>
       <c r="K192" s="1"/>
       <c r="L192" s="1"/>
-      <c r="M192" s="1"/>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -14643,9 +14449,8 @@
       <c r="J193" s="1"/>
       <c r="K193" s="1"/>
       <c r="L193" s="1"/>
-      <c r="M193" s="1"/>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -14658,9 +14463,8 @@
       <c r="J194" s="1"/>
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
-      <c r="M194" s="1"/>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -14673,9 +14477,8 @@
       <c r="J195" s="1"/>
       <c r="K195" s="1"/>
       <c r="L195" s="1"/>
-      <c r="M195" s="1"/>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -14688,9 +14491,8 @@
       <c r="J196" s="1"/>
       <c r="K196" s="1"/>
       <c r="L196" s="1"/>
-      <c r="M196" s="1"/>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -14703,9 +14505,8 @@
       <c r="J197" s="1"/>
       <c r="K197" s="1"/>
       <c r="L197" s="1"/>
-      <c r="M197" s="1"/>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -14718,9 +14519,8 @@
       <c r="J198" s="1"/>
       <c r="K198" s="1"/>
       <c r="L198" s="1"/>
-      <c r="M198" s="1"/>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -14733,9 +14533,8 @@
       <c r="J199" s="1"/>
       <c r="K199" s="1"/>
       <c r="L199" s="1"/>
-      <c r="M199" s="1"/>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -14748,9 +14547,8 @@
       <c r="J200" s="1"/>
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
-      <c r="M200" s="1"/>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -14763,9 +14561,8 @@
       <c r="J201" s="1"/>
       <c r="K201" s="1"/>
       <c r="L201" s="1"/>
-      <c r="M201" s="1"/>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -14778,9 +14575,8 @@
       <c r="J202" s="1"/>
       <c r="K202" s="1"/>
       <c r="L202" s="1"/>
-      <c r="M202" s="1"/>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -14793,9 +14589,8 @@
       <c r="J203" s="1"/>
       <c r="K203" s="1"/>
       <c r="L203" s="1"/>
-      <c r="M203" s="1"/>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -14808,9 +14603,8 @@
       <c r="J204" s="1"/>
       <c r="K204" s="1"/>
       <c r="L204" s="1"/>
-      <c r="M204" s="1"/>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -14823,9 +14617,8 @@
       <c r="J205" s="1"/>
       <c r="K205" s="1"/>
       <c r="L205" s="1"/>
-      <c r="M205" s="1"/>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -14838,9 +14631,8 @@
       <c r="J206" s="1"/>
       <c r="K206" s="1"/>
       <c r="L206" s="1"/>
-      <c r="M206" s="1"/>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -14853,9 +14645,8 @@
       <c r="J207" s="1"/>
       <c r="K207" s="1"/>
       <c r="L207" s="1"/>
-      <c r="M207" s="1"/>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -14868,9 +14659,8 @@
       <c r="J208" s="1"/>
       <c r="K208" s="1"/>
       <c r="L208" s="1"/>
-      <c r="M208" s="1"/>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -14883,9 +14673,8 @@
       <c r="J209" s="1"/>
       <c r="K209" s="1"/>
       <c r="L209" s="1"/>
-      <c r="M209" s="1"/>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -14898,9 +14687,8 @@
       <c r="J210" s="1"/>
       <c r="K210" s="1"/>
       <c r="L210" s="1"/>
-      <c r="M210" s="1"/>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -14913,9 +14701,8 @@
       <c r="J211" s="1"/>
       <c r="K211" s="1"/>
       <c r="L211" s="1"/>
-      <c r="M211" s="1"/>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -14928,9 +14715,8 @@
       <c r="J212" s="1"/>
       <c r="K212" s="1"/>
       <c r="L212" s="1"/>
-      <c r="M212" s="1"/>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -14943,9 +14729,8 @@
       <c r="J213" s="1"/>
       <c r="K213" s="1"/>
       <c r="L213" s="1"/>
-      <c r="M213" s="1"/>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -14958,9 +14743,8 @@
       <c r="J214" s="1"/>
       <c r="K214" s="1"/>
       <c r="L214" s="1"/>
-      <c r="M214" s="1"/>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -14973,9 +14757,8 @@
       <c r="J215" s="1"/>
       <c r="K215" s="1"/>
       <c r="L215" s="1"/>
-      <c r="M215" s="1"/>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -14988,9 +14771,8 @@
       <c r="J216" s="1"/>
       <c r="K216" s="1"/>
       <c r="L216" s="1"/>
-      <c r="M216" s="1"/>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -15003,9 +14785,8 @@
       <c r="J217" s="1"/>
       <c r="K217" s="1"/>
       <c r="L217" s="1"/>
-      <c r="M217" s="1"/>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -15018,9 +14799,8 @@
       <c r="J218" s="1"/>
       <c r="K218" s="1"/>
       <c r="L218" s="1"/>
-      <c r="M218" s="1"/>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -15033,9 +14813,8 @@
       <c r="J219" s="1"/>
       <c r="K219" s="1"/>
       <c r="L219" s="1"/>
-      <c r="M219" s="1"/>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -15048,9 +14827,8 @@
       <c r="J220" s="1"/>
       <c r="K220" s="1"/>
       <c r="L220" s="1"/>
-      <c r="M220" s="1"/>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -15063,9 +14841,8 @@
       <c r="J221" s="1"/>
       <c r="K221" s="1"/>
       <c r="L221" s="1"/>
-      <c r="M221" s="1"/>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -15078,9 +14855,8 @@
       <c r="J222" s="1"/>
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
-      <c r="M222" s="1"/>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -15093,9 +14869,8 @@
       <c r="J223" s="1"/>
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
-      <c r="M223" s="1"/>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -15108,9 +14883,8 @@
       <c r="J224" s="1"/>
       <c r="K224" s="1"/>
       <c r="L224" s="1"/>
-      <c r="M224" s="1"/>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -15123,9 +14897,8 @@
       <c r="J225" s="1"/>
       <c r="K225" s="1"/>
       <c r="L225" s="1"/>
-      <c r="M225" s="1"/>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -15138,9 +14911,8 @@
       <c r="J226" s="1"/>
       <c r="K226" s="1"/>
       <c r="L226" s="1"/>
-      <c r="M226" s="1"/>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -15153,9 +14925,8 @@
       <c r="J227" s="1"/>
       <c r="K227" s="1"/>
       <c r="L227" s="1"/>
-      <c r="M227" s="1"/>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -15168,9 +14939,8 @@
       <c r="J228" s="1"/>
       <c r="K228" s="1"/>
       <c r="L228" s="1"/>
-      <c r="M228" s="1"/>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -15183,9 +14953,8 @@
       <c r="J229" s="1"/>
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
-      <c r="M229" s="1"/>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -15198,9 +14967,8 @@
       <c r="J230" s="1"/>
       <c r="K230" s="1"/>
       <c r="L230" s="1"/>
-      <c r="M230" s="1"/>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -15213,9 +14981,8 @@
       <c r="J231" s="1"/>
       <c r="K231" s="1"/>
       <c r="L231" s="1"/>
-      <c r="M231" s="1"/>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -15228,9 +14995,8 @@
       <c r="J232" s="1"/>
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
-      <c r="M232" s="1"/>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -15243,9 +15009,8 @@
       <c r="J233" s="1"/>
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
-      <c r="M233" s="1"/>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -15258,9 +15023,8 @@
       <c r="J234" s="1"/>
       <c r="K234" s="1"/>
       <c r="L234" s="1"/>
-      <c r="M234" s="1"/>
-    </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -15273,9 +15037,8 @@
       <c r="J235" s="1"/>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
-      <c r="M235" s="1"/>
-    </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -15288,9 +15051,8 @@
       <c r="J236" s="1"/>
       <c r="K236" s="1"/>
       <c r="L236" s="1"/>
-      <c r="M236" s="1"/>
-    </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -15303,9 +15065,8 @@
       <c r="J237" s="1"/>
       <c r="K237" s="1"/>
       <c r="L237" s="1"/>
-      <c r="M237" s="1"/>
-    </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -15318,9 +15079,8 @@
       <c r="J238" s="1"/>
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
-      <c r="M238" s="1"/>
-    </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -15333,9 +15093,8 @@
       <c r="J239" s="1"/>
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
-      <c r="M239" s="1"/>
-    </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -15348,9 +15107,8 @@
       <c r="J240" s="1"/>
       <c r="K240" s="1"/>
       <c r="L240" s="1"/>
-      <c r="M240" s="1"/>
-    </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -15363,9 +15121,8 @@
       <c r="J241" s="1"/>
       <c r="K241" s="1"/>
       <c r="L241" s="1"/>
-      <c r="M241" s="1"/>
-    </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -15378,9 +15135,8 @@
       <c r="J242" s="1"/>
       <c r="K242" s="1"/>
       <c r="L242" s="1"/>
-      <c r="M242" s="1"/>
-    </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -15393,9 +15149,8 @@
       <c r="J243" s="1"/>
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
-      <c r="M243" s="1"/>
-    </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -15408,9 +15163,8 @@
       <c r="J244" s="1"/>
       <c r="K244" s="1"/>
       <c r="L244" s="1"/>
-      <c r="M244" s="1"/>
-    </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -15423,9 +15177,8 @@
       <c r="J245" s="1"/>
       <c r="K245" s="1"/>
       <c r="L245" s="1"/>
-      <c r="M245" s="1"/>
-    </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -15438,9 +15191,8 @@
       <c r="J246" s="1"/>
       <c r="K246" s="1"/>
       <c r="L246" s="1"/>
-      <c r="M246" s="1"/>
-    </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -15453,9 +15205,8 @@
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
       <c r="L247" s="1"/>
-      <c r="M247" s="1"/>
-    </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -15468,9 +15219,8 @@
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
       <c r="L248" s="1"/>
-      <c r="M248" s="1"/>
-    </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -15483,9 +15233,8 @@
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
       <c r="L249" s="1"/>
-      <c r="M249" s="1"/>
-    </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -15498,9 +15247,8 @@
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
       <c r="L250" s="1"/>
-      <c r="M250" s="1"/>
-    </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -15513,9 +15261,8 @@
       <c r="J251" s="1"/>
       <c r="K251" s="1"/>
       <c r="L251" s="1"/>
-      <c r="M251" s="1"/>
-    </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -15528,9 +15275,8 @@
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
       <c r="L252" s="1"/>
-      <c r="M252" s="1"/>
-    </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -15543,9 +15289,8 @@
       <c r="J253" s="1"/>
       <c r="K253" s="1"/>
       <c r="L253" s="1"/>
-      <c r="M253" s="1"/>
-    </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -15558,9 +15303,8 @@
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
       <c r="L254" s="1"/>
-      <c r="M254" s="1"/>
-    </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -15573,9 +15317,8 @@
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
       <c r="L255" s="1"/>
-      <c r="M255" s="1"/>
-    </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -15588,9 +15331,8 @@
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
       <c r="L256" s="1"/>
-      <c r="M256" s="1"/>
-    </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -15603,9 +15345,8 @@
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
       <c r="L257" s="1"/>
-      <c r="M257" s="1"/>
-    </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -15618,9 +15359,8 @@
       <c r="J258" s="1"/>
       <c r="K258" s="1"/>
       <c r="L258" s="1"/>
-      <c r="M258" s="1"/>
-    </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -15633,9 +15373,8 @@
       <c r="J259" s="1"/>
       <c r="K259" s="1"/>
       <c r="L259" s="1"/>
-      <c r="M259" s="1"/>
-    </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -15648,9 +15387,8 @@
       <c r="J260" s="1"/>
       <c r="K260" s="1"/>
       <c r="L260" s="1"/>
-      <c r="M260" s="1"/>
-    </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -15663,9 +15401,8 @@
       <c r="J261" s="1"/>
       <c r="K261" s="1"/>
       <c r="L261" s="1"/>
-      <c r="M261" s="1"/>
-    </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -15678,9 +15415,8 @@
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
       <c r="L262" s="1"/>
-      <c r="M262" s="1"/>
-    </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -15693,9 +15429,8 @@
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
       <c r="L263" s="1"/>
-      <c r="M263" s="1"/>
-    </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -15708,9 +15443,8 @@
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
       <c r="L264" s="1"/>
-      <c r="M264" s="1"/>
-    </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -15723,9 +15457,8 @@
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
       <c r="L265" s="1"/>
-      <c r="M265" s="1"/>
-    </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -15738,9 +15471,8 @@
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
       <c r="L266" s="1"/>
-      <c r="M266" s="1"/>
-    </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -15753,9 +15485,8 @@
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
       <c r="L267" s="1"/>
-      <c r="M267" s="1"/>
-    </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -15768,9 +15499,8 @@
       <c r="J268" s="1"/>
       <c r="K268" s="1"/>
       <c r="L268" s="1"/>
-      <c r="M268" s="1"/>
-    </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -15783,9 +15513,8 @@
       <c r="J269" s="1"/>
       <c r="K269" s="1"/>
       <c r="L269" s="1"/>
-      <c r="M269" s="1"/>
-    </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -15798,9 +15527,8 @@
       <c r="J270" s="1"/>
       <c r="K270" s="1"/>
       <c r="L270" s="1"/>
-      <c r="M270" s="1"/>
-    </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -15813,9 +15541,8 @@
       <c r="J271" s="1"/>
       <c r="K271" s="1"/>
       <c r="L271" s="1"/>
-      <c r="M271" s="1"/>
-    </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -15828,9 +15555,8 @@
       <c r="J272" s="1"/>
       <c r="K272" s="1"/>
       <c r="L272" s="1"/>
-      <c r="M272" s="1"/>
-    </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -15843,9 +15569,8 @@
       <c r="J273" s="1"/>
       <c r="K273" s="1"/>
       <c r="L273" s="1"/>
-      <c r="M273" s="1"/>
-    </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -15858,9 +15583,8 @@
       <c r="J274" s="1"/>
       <c r="K274" s="1"/>
       <c r="L274" s="1"/>
-      <c r="M274" s="1"/>
-    </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -15873,9 +15597,8 @@
       <c r="J275" s="1"/>
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
-      <c r="M275" s="1"/>
-    </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -15888,9 +15611,8 @@
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
       <c r="L276" s="1"/>
-      <c r="M276" s="1"/>
-    </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -15903,9 +15625,8 @@
       <c r="J277" s="1"/>
       <c r="K277" s="1"/>
       <c r="L277" s="1"/>
-      <c r="M277" s="1"/>
-    </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -15918,9 +15639,8 @@
       <c r="J278" s="1"/>
       <c r="K278" s="1"/>
       <c r="L278" s="1"/>
-      <c r="M278" s="1"/>
-    </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -15933,9 +15653,8 @@
       <c r="J279" s="1"/>
       <c r="K279" s="1"/>
       <c r="L279" s="1"/>
-      <c r="M279" s="1"/>
-    </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -15948,9 +15667,8 @@
       <c r="J280" s="1"/>
       <c r="K280" s="1"/>
       <c r="L280" s="1"/>
-      <c r="M280" s="1"/>
-    </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -15963,9 +15681,8 @@
       <c r="J281" s="1"/>
       <c r="K281" s="1"/>
       <c r="L281" s="1"/>
-      <c r="M281" s="1"/>
-    </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -15978,9 +15695,8 @@
       <c r="J282" s="1"/>
       <c r="K282" s="1"/>
       <c r="L282" s="1"/>
-      <c r="M282" s="1"/>
-    </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -15993,9 +15709,8 @@
       <c r="J283" s="1"/>
       <c r="K283" s="1"/>
       <c r="L283" s="1"/>
-      <c r="M283" s="1"/>
-    </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -16008,9 +15723,8 @@
       <c r="J284" s="1"/>
       <c r="K284" s="1"/>
       <c r="L284" s="1"/>
-      <c r="M284" s="1"/>
-    </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -16023,9 +15737,8 @@
       <c r="J285" s="1"/>
       <c r="K285" s="1"/>
       <c r="L285" s="1"/>
-      <c r="M285" s="1"/>
-    </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -16038,9 +15751,8 @@
       <c r="J286" s="1"/>
       <c r="K286" s="1"/>
       <c r="L286" s="1"/>
-      <c r="M286" s="1"/>
-    </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -16053,9 +15765,8 @@
       <c r="J287" s="1"/>
       <c r="K287" s="1"/>
       <c r="L287" s="1"/>
-      <c r="M287" s="1"/>
-    </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -16068,9 +15779,8 @@
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
-      <c r="M288" s="1"/>
-    </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -16083,9 +15793,8 @@
       <c r="J289" s="1"/>
       <c r="K289" s="1"/>
       <c r="L289" s="1"/>
-      <c r="M289" s="1"/>
-    </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -16098,9 +15807,8 @@
       <c r="J290" s="1"/>
       <c r="K290" s="1"/>
       <c r="L290" s="1"/>
-      <c r="M290" s="1"/>
-    </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -16113,9 +15821,8 @@
       <c r="J291" s="1"/>
       <c r="K291" s="1"/>
       <c r="L291" s="1"/>
-      <c r="M291" s="1"/>
-    </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -16128,9 +15835,8 @@
       <c r="J292" s="1"/>
       <c r="K292" s="1"/>
       <c r="L292" s="1"/>
-      <c r="M292" s="1"/>
-    </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -16143,9 +15849,8 @@
       <c r="J293" s="1"/>
       <c r="K293" s="1"/>
       <c r="L293" s="1"/>
-      <c r="M293" s="1"/>
-    </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -16158,9 +15863,8 @@
       <c r="J294" s="1"/>
       <c r="K294" s="1"/>
       <c r="L294" s="1"/>
-      <c r="M294" s="1"/>
-    </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -16173,9 +15877,8 @@
       <c r="J295" s="1"/>
       <c r="K295" s="1"/>
       <c r="L295" s="1"/>
-      <c r="M295" s="1"/>
-    </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -16188,9 +15891,8 @@
       <c r="J296" s="1"/>
       <c r="K296" s="1"/>
       <c r="L296" s="1"/>
-      <c r="M296" s="1"/>
-    </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -16203,9 +15905,8 @@
       <c r="J297" s="1"/>
       <c r="K297" s="1"/>
       <c r="L297" s="1"/>
-      <c r="M297" s="1"/>
-    </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -16218,9 +15919,8 @@
       <c r="J298" s="1"/>
       <c r="K298" s="1"/>
       <c r="L298" s="1"/>
-      <c r="M298" s="1"/>
-    </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -16233,9 +15933,8 @@
       <c r="J299" s="1"/>
       <c r="K299" s="1"/>
       <c r="L299" s="1"/>
-      <c r="M299" s="1"/>
-    </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -16248,9 +15947,8 @@
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
       <c r="L300" s="1"/>
-      <c r="M300" s="1"/>
-    </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -16263,9 +15961,8 @@
       <c r="J301" s="1"/>
       <c r="K301" s="1"/>
       <c r="L301" s="1"/>
-      <c r="M301" s="1"/>
-    </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -16278,9 +15975,8 @@
       <c r="J302" s="1"/>
       <c r="K302" s="1"/>
       <c r="L302" s="1"/>
-      <c r="M302" s="1"/>
-    </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -16293,9 +15989,8 @@
       <c r="J303" s="1"/>
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
-      <c r="M303" s="1"/>
-    </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -16308,9 +16003,8 @@
       <c r="J304" s="1"/>
       <c r="K304" s="1"/>
       <c r="L304" s="1"/>
-      <c r="M304" s="1"/>
-    </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -16323,9 +16017,8 @@
       <c r="J305" s="1"/>
       <c r="K305" s="1"/>
       <c r="L305" s="1"/>
-      <c r="M305" s="1"/>
-    </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -16338,9 +16031,8 @@
       <c r="J306" s="1"/>
       <c r="K306" s="1"/>
       <c r="L306" s="1"/>
-      <c r="M306" s="1"/>
-    </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -16353,9 +16045,8 @@
       <c r="J307" s="1"/>
       <c r="K307" s="1"/>
       <c r="L307" s="1"/>
-      <c r="M307" s="1"/>
-    </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -16368,9 +16059,8 @@
       <c r="J308" s="1"/>
       <c r="K308" s="1"/>
       <c r="L308" s="1"/>
-      <c r="M308" s="1"/>
-    </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -16383,9 +16073,8 @@
       <c r="J309" s="1"/>
       <c r="K309" s="1"/>
       <c r="L309" s="1"/>
-      <c r="M309" s="1"/>
-    </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -16398,9 +16087,8 @@
       <c r="J310" s="1"/>
       <c r="K310" s="1"/>
       <c r="L310" s="1"/>
-      <c r="M310" s="1"/>
-    </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -16413,9 +16101,8 @@
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
       <c r="L311" s="1"/>
-      <c r="M311" s="1"/>
-    </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -16428,9 +16115,8 @@
       <c r="J312" s="1"/>
       <c r="K312" s="1"/>
       <c r="L312" s="1"/>
-      <c r="M312" s="1"/>
-    </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -16443,9 +16129,8 @@
       <c r="J313" s="1"/>
       <c r="K313" s="1"/>
       <c r="L313" s="1"/>
-      <c r="M313" s="1"/>
-    </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -16458,9 +16143,8 @@
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
       <c r="L314" s="1"/>
-      <c r="M314" s="1"/>
-    </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -16473,9 +16157,8 @@
       <c r="J315" s="1"/>
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
-      <c r="M315" s="1"/>
-    </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -16488,9 +16171,8 @@
       <c r="J316" s="1"/>
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
-      <c r="M316" s="1"/>
-    </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -16503,9 +16185,8 @@
       <c r="J317" s="1"/>
       <c r="K317" s="1"/>
       <c r="L317" s="1"/>
-      <c r="M317" s="1"/>
-    </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -16518,9 +16199,8 @@
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
       <c r="L318" s="1"/>
-      <c r="M318" s="1"/>
-    </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -16533,9 +16213,8 @@
       <c r="J319" s="1"/>
       <c r="K319" s="1"/>
       <c r="L319" s="1"/>
-      <c r="M319" s="1"/>
-    </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -16548,9 +16227,8 @@
       <c r="J320" s="1"/>
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
-      <c r="M320" s="1"/>
-    </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -16563,9 +16241,8 @@
       <c r="J321" s="1"/>
       <c r="K321" s="1"/>
       <c r="L321" s="1"/>
-      <c r="M321" s="1"/>
-    </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -16578,9 +16255,8 @@
       <c r="J322" s="1"/>
       <c r="K322" s="1"/>
       <c r="L322" s="1"/>
-      <c r="M322" s="1"/>
-    </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -16593,9 +16269,8 @@
       <c r="J323" s="1"/>
       <c r="K323" s="1"/>
       <c r="L323" s="1"/>
-      <c r="M323" s="1"/>
-    </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -16608,9 +16283,8 @@
       <c r="J324" s="1"/>
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
-      <c r="M324" s="1"/>
-    </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -16623,9 +16297,8 @@
       <c r="J325" s="1"/>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
-      <c r="M325" s="1"/>
-    </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -16638,9 +16311,8 @@
       <c r="J326" s="1"/>
       <c r="K326" s="1"/>
       <c r="L326" s="1"/>
-      <c r="M326" s="1"/>
-    </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -16653,9 +16325,8 @@
       <c r="J327" s="1"/>
       <c r="K327" s="1"/>
       <c r="L327" s="1"/>
-      <c r="M327" s="1"/>
-    </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -16668,9 +16339,8 @@
       <c r="J328" s="1"/>
       <c r="K328" s="1"/>
       <c r="L328" s="1"/>
-      <c r="M328" s="1"/>
-    </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -16683,9 +16353,8 @@
       <c r="J329" s="1"/>
       <c r="K329" s="1"/>
       <c r="L329" s="1"/>
-      <c r="M329" s="1"/>
-    </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -16698,9 +16367,8 @@
       <c r="J330" s="1"/>
       <c r="K330" s="1"/>
       <c r="L330" s="1"/>
-      <c r="M330" s="1"/>
-    </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -16713,9 +16381,8 @@
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
       <c r="L331" s="1"/>
-      <c r="M331" s="1"/>
-    </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -16728,9 +16395,8 @@
       <c r="J332" s="1"/>
       <c r="K332" s="1"/>
       <c r="L332" s="1"/>
-      <c r="M332" s="1"/>
-    </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -16743,9 +16409,8 @@
       <c r="J333" s="1"/>
       <c r="K333" s="1"/>
       <c r="L333" s="1"/>
-      <c r="M333" s="1"/>
-    </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -16758,9 +16423,8 @@
       <c r="J334" s="1"/>
       <c r="K334" s="1"/>
       <c r="L334" s="1"/>
-      <c r="M334" s="1"/>
-    </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -16773,9 +16437,8 @@
       <c r="J335" s="1"/>
       <c r="K335" s="1"/>
       <c r="L335" s="1"/>
-      <c r="M335" s="1"/>
-    </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -16788,9 +16451,8 @@
       <c r="J336" s="1"/>
       <c r="K336" s="1"/>
       <c r="L336" s="1"/>
-      <c r="M336" s="1"/>
-    </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -16803,9 +16465,8 @@
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
       <c r="L337" s="1"/>
-      <c r="M337" s="1"/>
-    </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -16818,9 +16479,8 @@
       <c r="J338" s="1"/>
       <c r="K338" s="1"/>
       <c r="L338" s="1"/>
-      <c r="M338" s="1"/>
-    </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -16833,9 +16493,8 @@
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
       <c r="L339" s="1"/>
-      <c r="M339" s="1"/>
-    </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -16848,9 +16507,8 @@
       <c r="J340" s="1"/>
       <c r="K340" s="1"/>
       <c r="L340" s="1"/>
-      <c r="M340" s="1"/>
-    </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -16863,9 +16521,8 @@
       <c r="J341" s="1"/>
       <c r="K341" s="1"/>
       <c r="L341" s="1"/>
-      <c r="M341" s="1"/>
-    </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -16878,9 +16535,8 @@
       <c r="J342" s="1"/>
       <c r="K342" s="1"/>
       <c r="L342" s="1"/>
-      <c r="M342" s="1"/>
-    </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -16893,9 +16549,8 @@
       <c r="J343" s="1"/>
       <c r="K343" s="1"/>
       <c r="L343" s="1"/>
-      <c r="M343" s="1"/>
-    </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -16908,9 +16563,8 @@
       <c r="J344" s="1"/>
       <c r="K344" s="1"/>
       <c r="L344" s="1"/>
-      <c r="M344" s="1"/>
-    </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -16923,9 +16577,8 @@
       <c r="J345" s="1"/>
       <c r="K345" s="1"/>
       <c r="L345" s="1"/>
-      <c r="M345" s="1"/>
-    </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -16938,9 +16591,8 @@
       <c r="J346" s="1"/>
       <c r="K346" s="1"/>
       <c r="L346" s="1"/>
-      <c r="M346" s="1"/>
-    </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -16953,9 +16605,8 @@
       <c r="J347" s="1"/>
       <c r="K347" s="1"/>
       <c r="L347" s="1"/>
-      <c r="M347" s="1"/>
-    </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -16968,9 +16619,8 @@
       <c r="J348" s="1"/>
       <c r="K348" s="1"/>
       <c r="L348" s="1"/>
-      <c r="M348" s="1"/>
-    </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -16982,9 +16632,8 @@
       <c r="J349" s="1"/>
       <c r="K349" s="1"/>
       <c r="L349" s="1"/>
-      <c r="M349" s="1"/>
-    </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -16996,9 +16645,8 @@
       <c r="J350" s="1"/>
       <c r="K350" s="1"/>
       <c r="L350" s="1"/>
-      <c r="M350" s="1"/>
-    </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -17010,9 +16658,8 @@
       <c r="J351" s="1"/>
       <c r="K351" s="1"/>
       <c r="L351" s="1"/>
-      <c r="M351" s="1"/>
-    </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -17020,12 +16667,11 @@
       <c r="E352" s="1"/>
       <c r="G352" s="1"/>
       <c r="H352" s="1"/>
-      <c r="I352" s="1"/>
+      <c r="J352" s="1"/>
       <c r="K352" s="1"/>
       <c r="L352" s="1"/>
-      <c r="M352" s="1"/>
-    </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -17033,12 +16679,11 @@
       <c r="E353" s="1"/>
       <c r="G353" s="1"/>
       <c r="H353" s="1"/>
-      <c r="I353" s="1"/>
+      <c r="J353" s="1"/>
       <c r="K353" s="1"/>
       <c r="L353" s="1"/>
-      <c r="M353" s="1"/>
-    </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -17046,12 +16691,11 @@
       <c r="E354" s="1"/>
       <c r="G354" s="1"/>
       <c r="H354" s="1"/>
-      <c r="I354" s="1"/>
+      <c r="J354" s="1"/>
       <c r="K354" s="1"/>
       <c r="L354" s="1"/>
-      <c r="M354" s="1"/>
-    </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -17059,10 +16703,9 @@
       <c r="E355" s="1"/>
       <c r="G355" s="1"/>
       <c r="H355" s="1"/>
-      <c r="I355" s="1"/>
+      <c r="J355" s="1"/>
       <c r="K355" s="1"/>
       <c r="L355" s="1"/>
-      <c r="M355" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7D0A9F-484B-9A4D-920C-C0D03D60DD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8EDC20-1B88-1340-9A33-ADF8785ACE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="880" windowWidth="14900" windowHeight="17220" activeTab="3" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
@@ -977,7 +977,7 @@
     <t>COMMUNICABLE DISEASE KEYWORDS</t>
   </si>
   <si>
-    <t>NON-COMMUNICABLE DISEASE/ILLNESS</t>
+    <t>NON-COMMUNICABLE DISEASE OR ILLNESS KEYWORDS</t>
   </si>
 </sst>
 </file>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8EDC20-1B88-1340-9A33-ADF8785ACE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E2749-1D7C-E649-94BF-0F78D1572307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="880" windowWidth="14900" windowHeight="17220" activeTab="3" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="6120" yWindow="880" windowWidth="14900" windowHeight="17220" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
-    <sheet name="keywords" sheetId="2" r:id="rId1"/>
-    <sheet name="potential additional keywords" sheetId="3" r:id="rId2"/>
-    <sheet name="keywords_additional" sheetId="4" r:id="rId3"/>
-    <sheet name="adapted_keywords" sheetId="5" r:id="rId4"/>
+    <sheet name="sheet_names" sheetId="6" r:id="rId1"/>
+    <sheet name="keywords" sheetId="2" r:id="rId2"/>
+    <sheet name="additional keywords" sheetId="3" r:id="rId3"/>
+    <sheet name="keywords_additional" sheetId="4" r:id="rId4"/>
+    <sheet name="adapted_keywords" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="323">
   <si>
     <t>DIABETES</t>
   </si>
@@ -978,6 +979,36 @@
   </si>
   <si>
     <t>NON-COMMUNICABLE DISEASE OR ILLNESS KEYWORDS</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>keywords</t>
+  </si>
+  <si>
+    <t>additional keywords</t>
+  </si>
+  <si>
+    <t>keywords_additional</t>
+  </si>
+  <si>
+    <t>adapted_keywords</t>
+  </si>
+  <si>
+    <t>original keywords from McCord paper</t>
+  </si>
+  <si>
+    <t>list of keywords that I manually added by looking through unmatched CODs</t>
+  </si>
+  <si>
+    <t>original keywords list plus additional keywords</t>
+  </si>
+  <si>
+    <t>original keywords list plus additional keywords with group titles to match ICD logic</t>
   </si>
 </sst>
 </file>
@@ -1359,6 +1390,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{343C0F03-4DFE-FB46-8D3E-AB51A3BA84B3}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62A75C1-FFB3-A649-B3DD-A2FFAA6820B5}">
   <dimension ref="A1:K355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5905,7 +5989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19A0243-1058-594D-AF94-4FF1EBCCFA95}">
   <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6297,7 +6381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08F483A4-8058-DB4E-A46F-535DD3F5F342}">
   <dimension ref="A1:K355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10974,7 +11058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9374F8-5EC0-2B4D-B147-6130FD66FA7B}">
   <dimension ref="A1:N355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E2749-1D7C-E649-94BF-0F78D1572307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6BEBA3-BD80-9648-AC6A-9A084A5D28D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="880" windowWidth="14900" windowHeight="17220" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="1520" yWindow="860" windowWidth="30240" windowHeight="17540" firstSheet="1" activeTab="4" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="6" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="326">
   <si>
     <t>DIABETES</t>
   </si>
@@ -1009,6 +1009,15 @@
   </si>
   <si>
     <t>original keywords list plus additional keywords with group titles to match ICD logic</t>
+  </si>
+  <si>
+    <t>suicide</t>
+  </si>
+  <si>
+    <t>HOMICIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">homicide </t>
   </si>
 </sst>
 </file>
@@ -11060,7 +11069,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9374F8-5EC0-2B4D-B147-6130FD66FA7B}">
-  <dimension ref="A1:N355"/>
+  <dimension ref="A1:L355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="21.5" customWidth="1"/>
@@ -11070,13 +11079,11 @@
     <col min="7" max="7" width="24.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.83203125" customWidth="1"/>
     <col min="9" max="9" width="33.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
-    <col min="11" max="11" width="11.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>220</v>
       </c>
@@ -11105,20 +11112,14 @@
         <v>312</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>226</v>
+        <v>18</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="N1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>219</v>
       </c>
@@ -11147,20 +11148,14 @@
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>213</v>
       </c>
@@ -11189,20 +11184,14 @@
         <v>216</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>209</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
@@ -11231,18 +11220,14 @@
         <v>204</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>202</v>
       </c>
@@ -11270,14 +11255,10 @@
       <c r="I5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K5" s="1"/>
+      <c r="J5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>196</v>
       </c>
@@ -11303,14 +11284,10 @@
       <c r="I6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="K6" s="1"/>
+      <c r="J6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>192</v>
       </c>
@@ -11334,14 +11311,10 @@
       <c r="I7" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K7" s="1"/>
+      <c r="J7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>188</v>
       </c>
@@ -11365,14 +11338,10 @@
       <c r="I8" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K8" s="1"/>
+      <c r="J8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>185</v>
       </c>
@@ -11393,14 +11362,10 @@
       <c r="I9" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="K9" s="1"/>
+      <c r="J9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>179</v>
       </c>
@@ -11425,11 +11390,9 @@
         <v>46</v>
       </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>176</v>
       </c>
@@ -11454,11 +11417,9 @@
         <v>11</v>
       </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>86</v>
       </c>
@@ -11466,7 +11427,9 @@
       <c r="C12" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>305</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>133</v>
       </c>
@@ -11481,11 +11444,9 @@
         <v>63</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>172</v>
       </c>
@@ -11493,7 +11454,9 @@
       <c r="C13" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>323</v>
+      </c>
       <c r="E13" s="1" t="s">
         <v>131</v>
       </c>
@@ -11508,11 +11471,9 @@
         <v>27</v>
       </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>168</v>
       </c>
@@ -11535,11 +11496,9 @@
         <v>162</v>
       </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
@@ -11548,7 +11507,9 @@
         <v>159</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>324</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>2</v>
       </c>
@@ -11560,11 +11521,9 @@
         <v>144</v>
       </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>161</v>
       </c>
@@ -11573,7 +11532,9 @@
         <v>228</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>137</v>
       </c>
@@ -11585,11 +11546,9 @@
         <v>157</v>
       </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
@@ -11608,11 +11567,9 @@
         <v>35</v>
       </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>154</v>
       </c>
@@ -11631,11 +11588,9 @@
         <v>16</v>
       </c>
       <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>153</v>
       </c>
@@ -11654,11 +11609,9 @@
         <v>150</v>
       </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -11677,11 +11630,9 @@
         <v>148</v>
       </c>
       <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-      <c r="N20" s="1"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>147</v>
       </c>
@@ -11697,11 +11648,9 @@
         <v>36</v>
       </c>
       <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
-      <c r="N21" s="1"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>143</v>
       </c>
@@ -11717,11 +11666,9 @@
         <v>139</v>
       </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="N22" s="1"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>140</v>
       </c>
@@ -11737,11 +11684,9 @@
         <v>135</v>
       </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-      <c r="N23" s="1"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>138</v>
       </c>
@@ -11757,11 +11702,9 @@
         <v>49</v>
       </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="N24" s="1"/>
-    </row>
-    <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>134</v>
       </c>
@@ -11777,11 +11720,9 @@
         <v>129</v>
       </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
       <c r="L25" s="1"/>
-      <c r="N25" s="1"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>132</v>
       </c>
@@ -11797,11 +11738,9 @@
         <v>125</v>
       </c>
       <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
-      <c r="N26" s="1"/>
-    </row>
-    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>128</v>
       </c>
@@ -11818,11 +11757,9 @@
         <v>122</v>
       </c>
       <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
       <c r="L27" s="1"/>
-      <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>124</v>
       </c>
@@ -11838,11 +11775,9 @@
         <v>39</v>
       </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>121</v>
       </c>
@@ -11858,11 +11793,9 @@
         <v>117</v>
       </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
       <c r="L29" s="1"/>
-      <c r="N29" s="1"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>119</v>
       </c>
@@ -11878,11 +11811,9 @@
         <v>0</v>
       </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>118</v>
       </c>
@@ -11898,11 +11829,9 @@
         <v>112</v>
       </c>
       <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
       <c r="L31" s="1"/>
-      <c r="N31" s="1"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>116</v>
       </c>
@@ -11918,11 +11847,9 @@
         <v>40</v>
       </c>
       <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
       <c r="L32" s="1"/>
-      <c r="N32" s="1"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>114</v>
       </c>
@@ -11936,11 +11863,9 @@
         <v>110</v>
       </c>
       <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
       <c r="L33" s="1"/>
-      <c r="N33" s="1"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>111</v>
       </c>
@@ -11955,11 +11880,9 @@
         <v>58</v>
       </c>
       <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
       <c r="L34" s="1"/>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>109</v>
       </c>
@@ -11974,11 +11897,9 @@
         <v>55</v>
       </c>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>108</v>
       </c>
@@ -11993,11 +11914,9 @@
         <v>106</v>
       </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
       <c r="L36" s="1"/>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>107</v>
       </c>
@@ -12012,11 +11931,9 @@
         <v>104</v>
       </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>105</v>
       </c>
@@ -12031,11 +11948,9 @@
         <v>102</v>
       </c>
       <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
       <c r="L38" s="1"/>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>227</v>
       </c>
@@ -12050,11 +11965,9 @@
         <v>100</v>
       </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
-      <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>88</v>
       </c>
@@ -12069,11 +11982,9 @@
         <v>37</v>
       </c>
       <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
       <c r="L40" s="1"/>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>103</v>
       </c>
@@ -12088,11 +11999,9 @@
         <v>97</v>
       </c>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
       <c r="L41" s="1"/>
-      <c r="N41" s="1"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>101</v>
       </c>
@@ -12107,11 +12016,9 @@
         <v>95</v>
       </c>
       <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
       <c r="L42" s="1"/>
-      <c r="N42" s="1"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>99</v>
       </c>
@@ -12126,11 +12033,9 @@
         <v>93</v>
       </c>
       <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
       <c r="L43" s="1"/>
-      <c r="N43" s="1"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>98</v>
       </c>
@@ -12145,11 +12050,9 @@
         <v>59</v>
       </c>
       <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
       <c r="L44" s="1"/>
-      <c r="N44" s="1"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>96</v>
       </c>
@@ -12164,10 +12067,8 @@
         <v>33</v>
       </c>
       <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-    </row>
-    <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>94</v>
       </c>
@@ -12182,10 +12083,8 @@
         <v>89</v>
       </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>92</v>
       </c>
@@ -12200,10 +12099,8 @@
         <v>87</v>
       </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>91</v>
       </c>
@@ -12218,10 +12115,8 @@
         <v>17</v>
       </c>
       <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-    </row>
-    <row r="49" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>90</v>
       </c>
@@ -12236,10 +12131,8 @@
         <v>12</v>
       </c>
       <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>229</v>
       </c>
@@ -12254,10 +12147,8 @@
         <v>66</v>
       </c>
       <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>234</v>
       </c>
@@ -12271,10 +12162,8 @@
         <v>84</v>
       </c>
       <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>235</v>
       </c>
@@ -12289,10 +12178,8 @@
         <v>48</v>
       </c>
       <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>236</v>
       </c>
@@ -12306,10 +12193,8 @@
         <v>83</v>
       </c>
       <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>241</v>
       </c>
@@ -12323,10 +12208,8 @@
         <v>82</v>
       </c>
       <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>219</v>
       </c>
@@ -12341,10 +12224,8 @@
         <v>81</v>
       </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-    </row>
-    <row r="56" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>213</v>
       </c>
@@ -12359,10 +12240,8 @@
         <v>80</v>
       </c>
       <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>188</v>
       </c>
@@ -12377,10 +12256,8 @@
         <v>79</v>
       </c>
       <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>185</v>
       </c>
@@ -12395,10 +12272,8 @@
         <v>10</v>
       </c>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-    </row>
-    <row r="59" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>179</v>
       </c>
@@ -12413,10 +12288,8 @@
         <v>78</v>
       </c>
       <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>176</v>
       </c>
@@ -12431,10 +12304,8 @@
         <v>44</v>
       </c>
       <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>86</v>
       </c>
@@ -12449,10 +12320,8 @@
         <v>65</v>
       </c>
       <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>172</v>
       </c>
@@ -12467,10 +12336,8 @@
         <v>32</v>
       </c>
       <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>168</v>
       </c>
@@ -12485,10 +12352,8 @@
         <v>19</v>
       </c>
       <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-    </row>
-    <row r="64" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
@@ -12503,10 +12368,8 @@
         <v>77</v>
       </c>
       <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>161</v>
       </c>
@@ -12521,10 +12384,8 @@
         <v>38</v>
       </c>
       <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>156</v>
       </c>
@@ -12539,10 +12400,8 @@
         <v>52</v>
       </c>
       <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>154</v>
       </c>
@@ -12557,10 +12416,8 @@
         <v>64</v>
       </c>
       <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-    </row>
-    <row r="68" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>153</v>
       </c>
@@ -12575,10 +12432,8 @@
         <v>76</v>
       </c>
       <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>45</v>
       </c>
@@ -12593,10 +12448,8 @@
         <v>75</v>
       </c>
       <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
@@ -12611,10 +12464,8 @@
         <v>7</v>
       </c>
       <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>138</v>
       </c>
@@ -12629,10 +12480,8 @@
         <v>20</v>
       </c>
       <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>134</v>
       </c>
@@ -12647,10 +12496,8 @@
         <v>74</v>
       </c>
       <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>132</v>
       </c>
@@ -12665,10 +12512,8 @@
         <v>73</v>
       </c>
       <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-    </row>
-    <row r="74" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>128</v>
       </c>
@@ -12683,10 +12528,8 @@
         <v>57</v>
       </c>
       <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>124</v>
       </c>
@@ -12701,10 +12544,8 @@
         <v>72</v>
       </c>
       <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>121</v>
       </c>
@@ -12719,10 +12560,8 @@
         <v>60</v>
       </c>
       <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>119</v>
       </c>
@@ -12737,10 +12576,8 @@
         <v>62</v>
       </c>
       <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>118</v>
       </c>
@@ -12755,10 +12592,8 @@
         <v>26</v>
       </c>
       <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-    </row>
-    <row r="79" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>116</v>
       </c>
@@ -12773,10 +12608,8 @@
         <v>71</v>
       </c>
       <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>114</v>
       </c>
@@ -12791,10 +12624,8 @@
         <v>70</v>
       </c>
       <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>111</v>
       </c>
@@ -12809,10 +12640,8 @@
         <v>69</v>
       </c>
       <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
-    </row>
-    <row r="82" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -12827,10 +12656,8 @@
         <v>68</v>
       </c>
       <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>108</v>
       </c>
@@ -12845,10 +12672,8 @@
         <v>67</v>
       </c>
       <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>107</v>
       </c>
@@ -12863,10 +12688,8 @@
         <v>30</v>
       </c>
       <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
-      <c r="L84" s="1"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>105</v>
       </c>
@@ -12881,10 +12704,8 @@
         <v>237</v>
       </c>
       <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
-      <c r="L85" s="1"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>227</v>
       </c>
@@ -12899,10 +12720,8 @@
         <v>238</v>
       </c>
       <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -12917,10 +12736,8 @@
         <v>239</v>
       </c>
       <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>103</v>
       </c>
@@ -12935,10 +12752,8 @@
         <v>240</v>
       </c>
       <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>101</v>
       </c>
@@ -12953,10 +12768,8 @@
         <v>242</v>
       </c>
       <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>99</v>
       </c>
@@ -12971,10 +12784,8 @@
         <v>243</v>
       </c>
       <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
@@ -12989,10 +12800,8 @@
         <v>244</v>
       </c>
       <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>96</v>
       </c>
@@ -13007,10 +12816,8 @@
         <v>245</v>
       </c>
       <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-      <c r="L92" s="1"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -13025,10 +12832,8 @@
         <v>247</v>
       </c>
       <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
-      <c r="L93" s="1"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -13043,10 +12848,8 @@
         <v>248</v>
       </c>
       <c r="J94" s="1"/>
-      <c r="K94" s="1"/>
-      <c r="L94" s="1"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>91</v>
       </c>
@@ -13061,10 +12864,8 @@
         <v>250</v>
       </c>
       <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-      <c r="L95" s="1"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>90</v>
       </c>
@@ -13079,10 +12880,8 @@
         <v>251</v>
       </c>
       <c r="J96" s="1"/>
-      <c r="K96" s="1"/>
-      <c r="L96" s="1"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>229</v>
       </c>
@@ -13097,10 +12896,8 @@
         <v>252</v>
       </c>
       <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
-      <c r="L97" s="1"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -13113,10 +12910,8 @@
         <v>253</v>
       </c>
       <c r="J98" s="1"/>
-      <c r="K98" s="1"/>
-      <c r="L98" s="1"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -13129,10 +12924,8 @@
         <v>254</v>
       </c>
       <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-      <c r="L99" s="1"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -13145,10 +12938,8 @@
         <v>255</v>
       </c>
       <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="1"/>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -13161,10 +12952,8 @@
         <v>256</v>
       </c>
       <c r="J101" s="1"/>
-      <c r="K101" s="1"/>
-      <c r="L101" s="1"/>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -13177,10 +12966,8 @@
         <v>257</v>
       </c>
       <c r="J102" s="1"/>
-      <c r="K102" s="1"/>
-      <c r="L102" s="1"/>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -13193,10 +12980,8 @@
         <v>258</v>
       </c>
       <c r="J103" s="1"/>
-      <c r="K103" s="1"/>
-      <c r="L103" s="1"/>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -13209,10 +12994,8 @@
         <v>259</v>
       </c>
       <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-      <c r="L104" s="1"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -13225,10 +13008,8 @@
         <v>260</v>
       </c>
       <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-      <c r="L105" s="1"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -13241,10 +13022,8 @@
         <v>261</v>
       </c>
       <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
-      <c r="L106" s="1"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -13257,10 +13036,8 @@
         <v>264</v>
       </c>
       <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -13273,10 +13050,8 @@
         <v>265</v>
       </c>
       <c r="J108" s="1"/>
-      <c r="K108" s="1"/>
-      <c r="L108" s="1"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -13289,10 +13064,8 @@
         <v>266</v>
       </c>
       <c r="J109" s="1"/>
-      <c r="K109" s="1"/>
-      <c r="L109" s="1"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -13305,10 +13078,8 @@
         <v>267</v>
       </c>
       <c r="J110" s="1"/>
-      <c r="K110" s="1"/>
-      <c r="L110" s="1"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -13321,10 +13092,8 @@
         <v>268</v>
       </c>
       <c r="J111" s="1"/>
-      <c r="K111" s="1"/>
-      <c r="L111" s="1"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -13337,10 +13106,8 @@
         <v>269</v>
       </c>
       <c r="J112" s="1"/>
-      <c r="K112" s="1"/>
-      <c r="L112" s="1"/>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -13353,10 +13120,8 @@
         <v>270</v>
       </c>
       <c r="J113" s="1"/>
-      <c r="K113" s="1"/>
-      <c r="L113" s="1"/>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -13369,10 +13134,8 @@
         <v>272</v>
       </c>
       <c r="J114" s="1"/>
-      <c r="K114" s="1"/>
-      <c r="L114" s="1"/>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -13385,10 +13148,8 @@
         <v>273</v>
       </c>
       <c r="J115" s="1"/>
-      <c r="K115" s="1"/>
-      <c r="L115" s="1"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -13401,10 +13162,8 @@
         <v>274</v>
       </c>
       <c r="J116" s="1"/>
-      <c r="K116" s="1"/>
-      <c r="L116" s="1"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -13417,10 +13176,8 @@
         <v>276</v>
       </c>
       <c r="J117" s="1"/>
-      <c r="K117" s="1"/>
-      <c r="L117" s="1"/>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -13433,10 +13190,8 @@
         <v>277</v>
       </c>
       <c r="J118" s="1"/>
-      <c r="K118" s="1"/>
-      <c r="L118" s="1"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -13449,10 +13204,8 @@
         <v>278</v>
       </c>
       <c r="J119" s="1"/>
-      <c r="K119" s="1"/>
-      <c r="L119" s="1"/>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -13465,10 +13218,8 @@
         <v>279</v>
       </c>
       <c r="J120" s="1"/>
-      <c r="K120" s="1"/>
-      <c r="L120" s="1"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -13481,10 +13232,8 @@
         <v>280</v>
       </c>
       <c r="J121" s="1"/>
-      <c r="K121" s="1"/>
-      <c r="L121" s="1"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -13497,10 +13246,8 @@
         <v>281</v>
       </c>
       <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -13513,10 +13260,8 @@
         <v>282</v>
       </c>
       <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-      <c r="L123" s="1"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -13529,10 +13274,8 @@
         <v>283</v>
       </c>
       <c r="J124" s="1"/>
-      <c r="K124" s="1"/>
-      <c r="L124" s="1"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -13545,10 +13288,8 @@
         <v>284</v>
       </c>
       <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-      <c r="L125" s="1"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -13561,10 +13302,8 @@
         <v>285</v>
       </c>
       <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -13577,10 +13316,8 @@
         <v>286</v>
       </c>
       <c r="J127" s="1"/>
-      <c r="K127" s="1"/>
-      <c r="L127" s="1"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -13593,10 +13330,8 @@
         <v>288</v>
       </c>
       <c r="J128" s="1"/>
-      <c r="K128" s="1"/>
-      <c r="L128" s="1"/>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -13609,10 +13344,8 @@
         <v>289</v>
       </c>
       <c r="J129" s="1"/>
-      <c r="K129" s="1"/>
-      <c r="L129" s="1"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -13625,10 +13358,8 @@
         <v>290</v>
       </c>
       <c r="J130" s="1"/>
-      <c r="K130" s="1"/>
-      <c r="L130" s="1"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -13641,10 +13372,8 @@
         <v>291</v>
       </c>
       <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
-      <c r="L131" s="1"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -13657,10 +13386,8 @@
         <v>292</v>
       </c>
       <c r="J132" s="1"/>
-      <c r="K132" s="1"/>
-      <c r="L132" s="1"/>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -13673,10 +13400,8 @@
         <v>293</v>
       </c>
       <c r="J133" s="1"/>
-      <c r="K133" s="1"/>
-      <c r="L133" s="1"/>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -13689,10 +13414,8 @@
         <v>294</v>
       </c>
       <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
-      <c r="L134" s="1"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -13705,10 +13428,8 @@
         <v>295</v>
       </c>
       <c r="J135" s="1"/>
-      <c r="K135" s="1"/>
-      <c r="L135" s="1"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -13721,10 +13442,8 @@
         <v>296</v>
       </c>
       <c r="J136" s="1"/>
-      <c r="K136" s="1"/>
-      <c r="L136" s="1"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -13737,10 +13456,8 @@
         <v>298</v>
       </c>
       <c r="J137" s="1"/>
-      <c r="K137" s="1"/>
-      <c r="L137" s="1"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -13753,10 +13470,8 @@
         <v>299</v>
       </c>
       <c r="J138" s="1"/>
-      <c r="K138" s="1"/>
-      <c r="L138" s="1"/>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -13769,10 +13484,8 @@
         <v>300</v>
       </c>
       <c r="J139" s="1"/>
-      <c r="K139" s="1"/>
-      <c r="L139" s="1"/>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -13785,10 +13498,8 @@
         <v>302</v>
       </c>
       <c r="J140" s="1"/>
-      <c r="K140" s="1"/>
-      <c r="L140" s="1"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -13801,10 +13512,8 @@
         <v>303</v>
       </c>
       <c r="J141" s="1"/>
-      <c r="K141" s="1"/>
-      <c r="L141" s="1"/>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -13817,10 +13526,8 @@
         <v>304</v>
       </c>
       <c r="J142" s="1"/>
-      <c r="K142" s="1"/>
-      <c r="L142" s="1"/>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -13831,10 +13538,8 @@
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
-      <c r="K143" s="1"/>
-      <c r="L143" s="1"/>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -13845,10 +13550,8 @@
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
-      <c r="K144" s="1"/>
-      <c r="L144" s="1"/>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -13859,10 +13562,8 @@
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
-      <c r="K145" s="1"/>
-      <c r="L145" s="1"/>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -13873,10 +13574,8 @@
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
-      <c r="K146" s="1"/>
-      <c r="L146" s="1"/>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -13887,10 +13586,8 @@
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
-      <c r="K147" s="1"/>
-      <c r="L147" s="1"/>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -13901,10 +13598,8 @@
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
-      <c r="K148" s="1"/>
-      <c r="L148" s="1"/>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -13915,10 +13610,8 @@
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
-      <c r="K149" s="1"/>
-      <c r="L149" s="1"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -13929,10 +13622,8 @@
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
-      <c r="K150" s="1"/>
-      <c r="L150" s="1"/>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -13943,10 +13634,8 @@
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
-      <c r="K151" s="1"/>
-      <c r="L151" s="1"/>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -13957,10 +13646,8 @@
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
-      <c r="K152" s="1"/>
-      <c r="L152" s="1"/>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -13971,10 +13658,8 @@
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
-      <c r="K153" s="1"/>
-      <c r="L153" s="1"/>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -13985,10 +13670,8 @@
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
       <c r="J154" s="1"/>
-      <c r="K154" s="1"/>
-      <c r="L154" s="1"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -13999,10 +13682,8 @@
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
-      <c r="K155" s="1"/>
-      <c r="L155" s="1"/>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -14013,10 +13694,8 @@
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
-      <c r="K156" s="1"/>
-      <c r="L156" s="1"/>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -14027,10 +13706,8 @@
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
-      <c r="K157" s="1"/>
-      <c r="L157" s="1"/>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -14041,10 +13718,8 @@
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
-      <c r="K158" s="1"/>
-      <c r="L158" s="1"/>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -14055,10 +13730,8 @@
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -14069,10 +13742,8 @@
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
-      <c r="K160" s="1"/>
-      <c r="L160" s="1"/>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -14083,10 +13754,8 @@
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
-      <c r="K161" s="1"/>
-      <c r="L161" s="1"/>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -14097,10 +13766,8 @@
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
-      <c r="K162" s="1"/>
-      <c r="L162" s="1"/>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -14111,10 +13778,8 @@
       <c r="H163" s="1"/>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
-      <c r="K163" s="1"/>
-      <c r="L163" s="1"/>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -14125,10 +13790,8 @@
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
-      <c r="K164" s="1"/>
-      <c r="L164" s="1"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -14139,10 +13802,8 @@
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
-      <c r="K165" s="1"/>
-      <c r="L165" s="1"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -14153,10 +13814,8 @@
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
-      <c r="K166" s="1"/>
-      <c r="L166" s="1"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -14167,10 +13826,8 @@
       <c r="H167" s="1"/>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
-      <c r="K167" s="1"/>
-      <c r="L167" s="1"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -14181,10 +13838,8 @@
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
-      <c r="K168" s="1"/>
-      <c r="L168" s="1"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -14195,10 +13850,8 @@
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
-      <c r="K169" s="1"/>
-      <c r="L169" s="1"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -14209,10 +13862,8 @@
       <c r="H170" s="1"/>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
-      <c r="K170" s="1"/>
-      <c r="L170" s="1"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -14223,10 +13874,8 @@
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
-      <c r="K171" s="1"/>
-      <c r="L171" s="1"/>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -14237,10 +13886,8 @@
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
-      <c r="K172" s="1"/>
-      <c r="L172" s="1"/>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -14251,10 +13898,8 @@
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
-      <c r="K173" s="1"/>
-      <c r="L173" s="1"/>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -14265,10 +13910,8 @@
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
-      <c r="K174" s="1"/>
-      <c r="L174" s="1"/>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -14279,10 +13922,8 @@
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
-      <c r="K175" s="1"/>
-      <c r="L175" s="1"/>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -14293,10 +13934,8 @@
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
       <c r="J176" s="1"/>
-      <c r="K176" s="1"/>
-      <c r="L176" s="1"/>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -14307,10 +13946,8 @@
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
       <c r="J177" s="1"/>
-      <c r="K177" s="1"/>
-      <c r="L177" s="1"/>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -14321,10 +13958,8 @@
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
       <c r="J178" s="1"/>
-      <c r="K178" s="1"/>
-      <c r="L178" s="1"/>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -14335,10 +13970,8 @@
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
       <c r="J179" s="1"/>
-      <c r="K179" s="1"/>
-      <c r="L179" s="1"/>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -14349,10 +13982,8 @@
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
       <c r="J180" s="1"/>
-      <c r="K180" s="1"/>
-      <c r="L180" s="1"/>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -14363,10 +13994,8 @@
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
       <c r="J181" s="1"/>
-      <c r="K181" s="1"/>
-      <c r="L181" s="1"/>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -14377,10 +14006,8 @@
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
       <c r="J182" s="1"/>
-      <c r="K182" s="1"/>
-      <c r="L182" s="1"/>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -14391,10 +14018,8 @@
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
       <c r="J183" s="1"/>
-      <c r="K183" s="1"/>
-      <c r="L183" s="1"/>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -14405,10 +14030,8 @@
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
       <c r="J184" s="1"/>
-      <c r="K184" s="1"/>
-      <c r="L184" s="1"/>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -14419,10 +14042,8 @@
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
       <c r="J185" s="1"/>
-      <c r="K185" s="1"/>
-      <c r="L185" s="1"/>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -14433,10 +14054,8 @@
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
       <c r="J186" s="1"/>
-      <c r="K186" s="1"/>
-      <c r="L186" s="1"/>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -14447,10 +14066,8 @@
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
-      <c r="K187" s="1"/>
-      <c r="L187" s="1"/>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -14461,10 +14078,8 @@
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
-      <c r="K188" s="1"/>
-      <c r="L188" s="1"/>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -14475,10 +14090,8 @@
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
-      <c r="K189" s="1"/>
-      <c r="L189" s="1"/>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -14489,10 +14102,8 @@
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
-      <c r="K190" s="1"/>
-      <c r="L190" s="1"/>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -14503,10 +14114,8 @@
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
       <c r="J191" s="1"/>
-      <c r="K191" s="1"/>
-      <c r="L191" s="1"/>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -14517,10 +14126,8 @@
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
-      <c r="K192" s="1"/>
-      <c r="L192" s="1"/>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -14531,10 +14138,8 @@
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
       <c r="J193" s="1"/>
-      <c r="K193" s="1"/>
-      <c r="L193" s="1"/>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -14545,10 +14150,8 @@
       <c r="H194" s="1"/>
       <c r="I194" s="1"/>
       <c r="J194" s="1"/>
-      <c r="K194" s="1"/>
-      <c r="L194" s="1"/>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -14559,10 +14162,8 @@
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
       <c r="J195" s="1"/>
-      <c r="K195" s="1"/>
-      <c r="L195" s="1"/>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -14573,10 +14174,8 @@
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
       <c r="J196" s="1"/>
-      <c r="K196" s="1"/>
-      <c r="L196" s="1"/>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -14587,10 +14186,8 @@
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
       <c r="J197" s="1"/>
-      <c r="K197" s="1"/>
-      <c r="L197" s="1"/>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -14601,10 +14198,8 @@
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
       <c r="J198" s="1"/>
-      <c r="K198" s="1"/>
-      <c r="L198" s="1"/>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -14615,10 +14210,8 @@
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
       <c r="J199" s="1"/>
-      <c r="K199" s="1"/>
-      <c r="L199" s="1"/>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -14629,10 +14222,8 @@
       <c r="H200" s="1"/>
       <c r="I200" s="1"/>
       <c r="J200" s="1"/>
-      <c r="K200" s="1"/>
-      <c r="L200" s="1"/>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -14643,10 +14234,8 @@
       <c r="H201" s="1"/>
       <c r="I201" s="1"/>
       <c r="J201" s="1"/>
-      <c r="K201" s="1"/>
-      <c r="L201" s="1"/>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -14657,10 +14246,8 @@
       <c r="H202" s="1"/>
       <c r="I202" s="1"/>
       <c r="J202" s="1"/>
-      <c r="K202" s="1"/>
-      <c r="L202" s="1"/>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -14671,10 +14258,8 @@
       <c r="H203" s="1"/>
       <c r="I203" s="1"/>
       <c r="J203" s="1"/>
-      <c r="K203" s="1"/>
-      <c r="L203" s="1"/>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -14685,10 +14270,8 @@
       <c r="H204" s="1"/>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
-      <c r="K204" s="1"/>
-      <c r="L204" s="1"/>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -14699,10 +14282,8 @@
       <c r="H205" s="1"/>
       <c r="I205" s="1"/>
       <c r="J205" s="1"/>
-      <c r="K205" s="1"/>
-      <c r="L205" s="1"/>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -14713,10 +14294,8 @@
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
       <c r="J206" s="1"/>
-      <c r="K206" s="1"/>
-      <c r="L206" s="1"/>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -14727,10 +14306,8 @@
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
       <c r="J207" s="1"/>
-      <c r="K207" s="1"/>
-      <c r="L207" s="1"/>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -14741,10 +14318,8 @@
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
       <c r="J208" s="1"/>
-      <c r="K208" s="1"/>
-      <c r="L208" s="1"/>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -14755,10 +14330,8 @@
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
       <c r="J209" s="1"/>
-      <c r="K209" s="1"/>
-      <c r="L209" s="1"/>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -14769,10 +14342,8 @@
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
       <c r="J210" s="1"/>
-      <c r="K210" s="1"/>
-      <c r="L210" s="1"/>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -14783,10 +14354,8 @@
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
       <c r="J211" s="1"/>
-      <c r="K211" s="1"/>
-      <c r="L211" s="1"/>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -14797,10 +14366,8 @@
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
       <c r="J212" s="1"/>
-      <c r="K212" s="1"/>
-      <c r="L212" s="1"/>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -14811,10 +14378,8 @@
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
       <c r="J213" s="1"/>
-      <c r="K213" s="1"/>
-      <c r="L213" s="1"/>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -14825,10 +14390,8 @@
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
       <c r="J214" s="1"/>
-      <c r="K214" s="1"/>
-      <c r="L214" s="1"/>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -14839,10 +14402,8 @@
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
       <c r="J215" s="1"/>
-      <c r="K215" s="1"/>
-      <c r="L215" s="1"/>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -14853,10 +14414,8 @@
       <c r="H216" s="1"/>
       <c r="I216" s="1"/>
       <c r="J216" s="1"/>
-      <c r="K216" s="1"/>
-      <c r="L216" s="1"/>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -14867,10 +14426,8 @@
       <c r="H217" s="1"/>
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
-      <c r="K217" s="1"/>
-      <c r="L217" s="1"/>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -14881,10 +14438,8 @@
       <c r="H218" s="1"/>
       <c r="I218" s="1"/>
       <c r="J218" s="1"/>
-      <c r="K218" s="1"/>
-      <c r="L218" s="1"/>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -14895,10 +14450,8 @@
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
       <c r="J219" s="1"/>
-      <c r="K219" s="1"/>
-      <c r="L219" s="1"/>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -14909,10 +14462,8 @@
       <c r="H220" s="1"/>
       <c r="I220" s="1"/>
       <c r="J220" s="1"/>
-      <c r="K220" s="1"/>
-      <c r="L220" s="1"/>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -14923,10 +14474,8 @@
       <c r="H221" s="1"/>
       <c r="I221" s="1"/>
       <c r="J221" s="1"/>
-      <c r="K221" s="1"/>
-      <c r="L221" s="1"/>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -14937,10 +14486,8 @@
       <c r="H222" s="1"/>
       <c r="I222" s="1"/>
       <c r="J222" s="1"/>
-      <c r="K222" s="1"/>
-      <c r="L222" s="1"/>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -14951,10 +14498,8 @@
       <c r="H223" s="1"/>
       <c r="I223" s="1"/>
       <c r="J223" s="1"/>
-      <c r="K223" s="1"/>
-      <c r="L223" s="1"/>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -14965,10 +14510,8 @@
       <c r="H224" s="1"/>
       <c r="I224" s="1"/>
       <c r="J224" s="1"/>
-      <c r="K224" s="1"/>
-      <c r="L224" s="1"/>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -14979,10 +14522,8 @@
       <c r="H225" s="1"/>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
-      <c r="K225" s="1"/>
-      <c r="L225" s="1"/>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -14993,10 +14534,8 @@
       <c r="H226" s="1"/>
       <c r="I226" s="1"/>
       <c r="J226" s="1"/>
-      <c r="K226" s="1"/>
-      <c r="L226" s="1"/>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -15007,10 +14546,8 @@
       <c r="H227" s="1"/>
       <c r="I227" s="1"/>
       <c r="J227" s="1"/>
-      <c r="K227" s="1"/>
-      <c r="L227" s="1"/>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -15021,10 +14558,8 @@
       <c r="H228" s="1"/>
       <c r="I228" s="1"/>
       <c r="J228" s="1"/>
-      <c r="K228" s="1"/>
-      <c r="L228" s="1"/>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -15035,10 +14570,8 @@
       <c r="H229" s="1"/>
       <c r="I229" s="1"/>
       <c r="J229" s="1"/>
-      <c r="K229" s="1"/>
-      <c r="L229" s="1"/>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -15049,10 +14582,8 @@
       <c r="H230" s="1"/>
       <c r="I230" s="1"/>
       <c r="J230" s="1"/>
-      <c r="K230" s="1"/>
-      <c r="L230" s="1"/>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -15063,10 +14594,8 @@
       <c r="H231" s="1"/>
       <c r="I231" s="1"/>
       <c r="J231" s="1"/>
-      <c r="K231" s="1"/>
-      <c r="L231" s="1"/>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -15077,10 +14606,8 @@
       <c r="H232" s="1"/>
       <c r="I232" s="1"/>
       <c r="J232" s="1"/>
-      <c r="K232" s="1"/>
-      <c r="L232" s="1"/>
-    </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -15091,10 +14618,8 @@
       <c r="H233" s="1"/>
       <c r="I233" s="1"/>
       <c r="J233" s="1"/>
-      <c r="K233" s="1"/>
-      <c r="L233" s="1"/>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -15105,10 +14630,8 @@
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
       <c r="J234" s="1"/>
-      <c r="K234" s="1"/>
-      <c r="L234" s="1"/>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -15119,10 +14642,8 @@
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
       <c r="J235" s="1"/>
-      <c r="K235" s="1"/>
-      <c r="L235" s="1"/>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -15133,10 +14654,8 @@
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
       <c r="J236" s="1"/>
-      <c r="K236" s="1"/>
-      <c r="L236" s="1"/>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -15147,10 +14666,8 @@
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
       <c r="J237" s="1"/>
-      <c r="K237" s="1"/>
-      <c r="L237" s="1"/>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -15161,10 +14678,8 @@
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
       <c r="J238" s="1"/>
-      <c r="K238" s="1"/>
-      <c r="L238" s="1"/>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -15175,10 +14690,8 @@
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
       <c r="J239" s="1"/>
-      <c r="K239" s="1"/>
-      <c r="L239" s="1"/>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -15189,10 +14702,8 @@
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
       <c r="J240" s="1"/>
-      <c r="K240" s="1"/>
-      <c r="L240" s="1"/>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -15203,10 +14714,8 @@
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
       <c r="J241" s="1"/>
-      <c r="K241" s="1"/>
-      <c r="L241" s="1"/>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -15217,10 +14726,8 @@
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
       <c r="J242" s="1"/>
-      <c r="K242" s="1"/>
-      <c r="L242" s="1"/>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -15231,10 +14738,8 @@
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
       <c r="J243" s="1"/>
-      <c r="K243" s="1"/>
-      <c r="L243" s="1"/>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -15245,10 +14750,8 @@
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
       <c r="J244" s="1"/>
-      <c r="K244" s="1"/>
-      <c r="L244" s="1"/>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -15259,10 +14762,8 @@
       <c r="H245" s="1"/>
       <c r="I245" s="1"/>
       <c r="J245" s="1"/>
-      <c r="K245" s="1"/>
-      <c r="L245" s="1"/>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -15273,10 +14774,8 @@
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
       <c r="J246" s="1"/>
-      <c r="K246" s="1"/>
-      <c r="L246" s="1"/>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -15287,10 +14786,8 @@
       <c r="H247" s="1"/>
       <c r="I247" s="1"/>
       <c r="J247" s="1"/>
-      <c r="K247" s="1"/>
-      <c r="L247" s="1"/>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -15301,10 +14798,8 @@
       <c r="H248" s="1"/>
       <c r="I248" s="1"/>
       <c r="J248" s="1"/>
-      <c r="K248" s="1"/>
-      <c r="L248" s="1"/>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -15315,10 +14810,8 @@
       <c r="H249" s="1"/>
       <c r="I249" s="1"/>
       <c r="J249" s="1"/>
-      <c r="K249" s="1"/>
-      <c r="L249" s="1"/>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -15329,10 +14822,8 @@
       <c r="H250" s="1"/>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
-      <c r="K250" s="1"/>
-      <c r="L250" s="1"/>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -15343,10 +14834,8 @@
       <c r="H251" s="1"/>
       <c r="I251" s="1"/>
       <c r="J251" s="1"/>
-      <c r="K251" s="1"/>
-      <c r="L251" s="1"/>
-    </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -15357,10 +14846,8 @@
       <c r="H252" s="1"/>
       <c r="I252" s="1"/>
       <c r="J252" s="1"/>
-      <c r="K252" s="1"/>
-      <c r="L252" s="1"/>
-    </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -15371,10 +14858,8 @@
       <c r="H253" s="1"/>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
-      <c r="K253" s="1"/>
-      <c r="L253" s="1"/>
-    </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -15385,10 +14870,8 @@
       <c r="H254" s="1"/>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
-      <c r="K254" s="1"/>
-      <c r="L254" s="1"/>
-    </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -15399,10 +14882,8 @@
       <c r="H255" s="1"/>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
-      <c r="K255" s="1"/>
-      <c r="L255" s="1"/>
-    </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -15413,10 +14894,8 @@
       <c r="H256" s="1"/>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
-      <c r="K256" s="1"/>
-      <c r="L256" s="1"/>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -15427,10 +14906,8 @@
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
-      <c r="K257" s="1"/>
-      <c r="L257" s="1"/>
-    </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -15441,10 +14918,8 @@
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
-      <c r="K258" s="1"/>
-      <c r="L258" s="1"/>
-    </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -15455,10 +14930,8 @@
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
-      <c r="K259" s="1"/>
-      <c r="L259" s="1"/>
-    </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -15469,10 +14942,8 @@
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
-      <c r="K260" s="1"/>
-      <c r="L260" s="1"/>
-    </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -15483,10 +14954,8 @@
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
-      <c r="K261" s="1"/>
-      <c r="L261" s="1"/>
-    </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -15497,10 +14966,8 @@
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
-      <c r="K262" s="1"/>
-      <c r="L262" s="1"/>
-    </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -15511,10 +14978,8 @@
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
       <c r="J263" s="1"/>
-      <c r="K263" s="1"/>
-      <c r="L263" s="1"/>
-    </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -15525,10 +14990,8 @@
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
       <c r="J264" s="1"/>
-      <c r="K264" s="1"/>
-      <c r="L264" s="1"/>
-    </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -15539,10 +15002,8 @@
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
       <c r="J265" s="1"/>
-      <c r="K265" s="1"/>
-      <c r="L265" s="1"/>
-    </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -15553,10 +15014,8 @@
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
       <c r="J266" s="1"/>
-      <c r="K266" s="1"/>
-      <c r="L266" s="1"/>
-    </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -15567,10 +15026,8 @@
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
       <c r="J267" s="1"/>
-      <c r="K267" s="1"/>
-      <c r="L267" s="1"/>
-    </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -15581,10 +15038,8 @@
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
       <c r="J268" s="1"/>
-      <c r="K268" s="1"/>
-      <c r="L268" s="1"/>
-    </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -15595,10 +15050,8 @@
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
       <c r="J269" s="1"/>
-      <c r="K269" s="1"/>
-      <c r="L269" s="1"/>
-    </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -15609,10 +15062,8 @@
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
       <c r="J270" s="1"/>
-      <c r="K270" s="1"/>
-      <c r="L270" s="1"/>
-    </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -15623,10 +15074,8 @@
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
       <c r="J271" s="1"/>
-      <c r="K271" s="1"/>
-      <c r="L271" s="1"/>
-    </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -15637,10 +15086,8 @@
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
       <c r="J272" s="1"/>
-      <c r="K272" s="1"/>
-      <c r="L272" s="1"/>
-    </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -15651,10 +15098,8 @@
       <c r="H273" s="1"/>
       <c r="I273" s="1"/>
       <c r="J273" s="1"/>
-      <c r="K273" s="1"/>
-      <c r="L273" s="1"/>
-    </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -15665,10 +15110,8 @@
       <c r="H274" s="1"/>
       <c r="I274" s="1"/>
       <c r="J274" s="1"/>
-      <c r="K274" s="1"/>
-      <c r="L274" s="1"/>
-    </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -15679,10 +15122,8 @@
       <c r="H275" s="1"/>
       <c r="I275" s="1"/>
       <c r="J275" s="1"/>
-      <c r="K275" s="1"/>
-      <c r="L275" s="1"/>
-    </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -15693,10 +15134,8 @@
       <c r="H276" s="1"/>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
-      <c r="K276" s="1"/>
-      <c r="L276" s="1"/>
-    </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -15707,10 +15146,8 @@
       <c r="H277" s="1"/>
       <c r="I277" s="1"/>
       <c r="J277" s="1"/>
-      <c r="K277" s="1"/>
-      <c r="L277" s="1"/>
-    </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -15721,10 +15158,8 @@
       <c r="H278" s="1"/>
       <c r="I278" s="1"/>
       <c r="J278" s="1"/>
-      <c r="K278" s="1"/>
-      <c r="L278" s="1"/>
-    </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -15735,10 +15170,8 @@
       <c r="H279" s="1"/>
       <c r="I279" s="1"/>
       <c r="J279" s="1"/>
-      <c r="K279" s="1"/>
-      <c r="L279" s="1"/>
-    </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -15749,10 +15182,8 @@
       <c r="H280" s="1"/>
       <c r="I280" s="1"/>
       <c r="J280" s="1"/>
-      <c r="K280" s="1"/>
-      <c r="L280" s="1"/>
-    </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -15763,10 +15194,8 @@
       <c r="H281" s="1"/>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
-      <c r="K281" s="1"/>
-      <c r="L281" s="1"/>
-    </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -15777,10 +15206,8 @@
       <c r="H282" s="1"/>
       <c r="I282" s="1"/>
       <c r="J282" s="1"/>
-      <c r="K282" s="1"/>
-      <c r="L282" s="1"/>
-    </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -15791,10 +15218,8 @@
       <c r="H283" s="1"/>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
-      <c r="K283" s="1"/>
-      <c r="L283" s="1"/>
-    </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -15805,10 +15230,8 @@
       <c r="H284" s="1"/>
       <c r="I284" s="1"/>
       <c r="J284" s="1"/>
-      <c r="K284" s="1"/>
-      <c r="L284" s="1"/>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -15819,10 +15242,8 @@
       <c r="H285" s="1"/>
       <c r="I285" s="1"/>
       <c r="J285" s="1"/>
-      <c r="K285" s="1"/>
-      <c r="L285" s="1"/>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -15833,10 +15254,8 @@
       <c r="H286" s="1"/>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
-      <c r="K286" s="1"/>
-      <c r="L286" s="1"/>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -15847,10 +15266,8 @@
       <c r="H287" s="1"/>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
-      <c r="K287" s="1"/>
-      <c r="L287" s="1"/>
-    </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -15861,10 +15278,8 @@
       <c r="H288" s="1"/>
       <c r="I288" s="1"/>
       <c r="J288" s="1"/>
-      <c r="K288" s="1"/>
-      <c r="L288" s="1"/>
-    </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -15875,10 +15290,8 @@
       <c r="H289" s="1"/>
       <c r="I289" s="1"/>
       <c r="J289" s="1"/>
-      <c r="K289" s="1"/>
-      <c r="L289" s="1"/>
-    </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -15889,10 +15302,8 @@
       <c r="H290" s="1"/>
       <c r="I290" s="1"/>
       <c r="J290" s="1"/>
-      <c r="K290" s="1"/>
-      <c r="L290" s="1"/>
-    </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -15903,10 +15314,8 @@
       <c r="H291" s="1"/>
       <c r="I291" s="1"/>
       <c r="J291" s="1"/>
-      <c r="K291" s="1"/>
-      <c r="L291" s="1"/>
-    </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -15917,10 +15326,8 @@
       <c r="H292" s="1"/>
       <c r="I292" s="1"/>
       <c r="J292" s="1"/>
-      <c r="K292" s="1"/>
-      <c r="L292" s="1"/>
-    </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -15931,10 +15338,8 @@
       <c r="H293" s="1"/>
       <c r="I293" s="1"/>
       <c r="J293" s="1"/>
-      <c r="K293" s="1"/>
-      <c r="L293" s="1"/>
-    </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -15945,10 +15350,8 @@
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
       <c r="J294" s="1"/>
-      <c r="K294" s="1"/>
-      <c r="L294" s="1"/>
-    </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -15959,10 +15362,8 @@
       <c r="H295" s="1"/>
       <c r="I295" s="1"/>
       <c r="J295" s="1"/>
-      <c r="K295" s="1"/>
-      <c r="L295" s="1"/>
-    </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -15973,10 +15374,8 @@
       <c r="H296" s="1"/>
       <c r="I296" s="1"/>
       <c r="J296" s="1"/>
-      <c r="K296" s="1"/>
-      <c r="L296" s="1"/>
-    </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -15987,10 +15386,8 @@
       <c r="H297" s="1"/>
       <c r="I297" s="1"/>
       <c r="J297" s="1"/>
-      <c r="K297" s="1"/>
-      <c r="L297" s="1"/>
-    </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -16001,10 +15398,8 @@
       <c r="H298" s="1"/>
       <c r="I298" s="1"/>
       <c r="J298" s="1"/>
-      <c r="K298" s="1"/>
-      <c r="L298" s="1"/>
-    </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -16015,10 +15410,8 @@
       <c r="H299" s="1"/>
       <c r="I299" s="1"/>
       <c r="J299" s="1"/>
-      <c r="K299" s="1"/>
-      <c r="L299" s="1"/>
-    </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -16029,10 +15422,8 @@
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
       <c r="J300" s="1"/>
-      <c r="K300" s="1"/>
-      <c r="L300" s="1"/>
-    </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -16043,10 +15434,8 @@
       <c r="H301" s="1"/>
       <c r="I301" s="1"/>
       <c r="J301" s="1"/>
-      <c r="K301" s="1"/>
-      <c r="L301" s="1"/>
-    </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -16057,10 +15446,8 @@
       <c r="H302" s="1"/>
       <c r="I302" s="1"/>
       <c r="J302" s="1"/>
-      <c r="K302" s="1"/>
-      <c r="L302" s="1"/>
-    </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -16071,10 +15458,8 @@
       <c r="H303" s="1"/>
       <c r="I303" s="1"/>
       <c r="J303" s="1"/>
-      <c r="K303" s="1"/>
-      <c r="L303" s="1"/>
-    </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -16085,10 +15470,8 @@
       <c r="H304" s="1"/>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
-      <c r="K304" s="1"/>
-      <c r="L304" s="1"/>
-    </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -16099,10 +15482,8 @@
       <c r="H305" s="1"/>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
-      <c r="K305" s="1"/>
-      <c r="L305" s="1"/>
-    </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -16113,10 +15494,8 @@
       <c r="H306" s="1"/>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
-      <c r="K306" s="1"/>
-      <c r="L306" s="1"/>
-    </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -16127,10 +15506,8 @@
       <c r="H307" s="1"/>
       <c r="I307" s="1"/>
       <c r="J307" s="1"/>
-      <c r="K307" s="1"/>
-      <c r="L307" s="1"/>
-    </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -16141,10 +15518,8 @@
       <c r="H308" s="1"/>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
-      <c r="K308" s="1"/>
-      <c r="L308" s="1"/>
-    </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -16155,10 +15530,8 @@
       <c r="H309" s="1"/>
       <c r="I309" s="1"/>
       <c r="J309" s="1"/>
-      <c r="K309" s="1"/>
-      <c r="L309" s="1"/>
-    </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -16169,10 +15542,8 @@
       <c r="H310" s="1"/>
       <c r="I310" s="1"/>
       <c r="J310" s="1"/>
-      <c r="K310" s="1"/>
-      <c r="L310" s="1"/>
-    </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -16183,10 +15554,8 @@
       <c r="H311" s="1"/>
       <c r="I311" s="1"/>
       <c r="J311" s="1"/>
-      <c r="K311" s="1"/>
-      <c r="L311" s="1"/>
-    </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -16197,10 +15566,8 @@
       <c r="H312" s="1"/>
       <c r="I312" s="1"/>
       <c r="J312" s="1"/>
-      <c r="K312" s="1"/>
-      <c r="L312" s="1"/>
-    </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -16211,10 +15578,8 @@
       <c r="H313" s="1"/>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
-      <c r="K313" s="1"/>
-      <c r="L313" s="1"/>
-    </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -16225,10 +15590,8 @@
       <c r="H314" s="1"/>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
-      <c r="K314" s="1"/>
-      <c r="L314" s="1"/>
-    </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -16239,10 +15602,8 @@
       <c r="H315" s="1"/>
       <c r="I315" s="1"/>
       <c r="J315" s="1"/>
-      <c r="K315" s="1"/>
-      <c r="L315" s="1"/>
-    </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -16253,10 +15614,8 @@
       <c r="H316" s="1"/>
       <c r="I316" s="1"/>
       <c r="J316" s="1"/>
-      <c r="K316" s="1"/>
-      <c r="L316" s="1"/>
-    </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -16267,10 +15626,8 @@
       <c r="H317" s="1"/>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
-      <c r="K317" s="1"/>
-      <c r="L317" s="1"/>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -16281,10 +15638,8 @@
       <c r="H318" s="1"/>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
-      <c r="K318" s="1"/>
-      <c r="L318" s="1"/>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -16295,10 +15650,8 @@
       <c r="H319" s="1"/>
       <c r="I319" s="1"/>
       <c r="J319" s="1"/>
-      <c r="K319" s="1"/>
-      <c r="L319" s="1"/>
-    </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -16309,10 +15662,8 @@
       <c r="H320" s="1"/>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
-      <c r="K320" s="1"/>
-      <c r="L320" s="1"/>
-    </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -16323,10 +15674,8 @@
       <c r="H321" s="1"/>
       <c r="I321" s="1"/>
       <c r="J321" s="1"/>
-      <c r="K321" s="1"/>
-      <c r="L321" s="1"/>
-    </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -16337,10 +15686,8 @@
       <c r="H322" s="1"/>
       <c r="I322" s="1"/>
       <c r="J322" s="1"/>
-      <c r="K322" s="1"/>
-      <c r="L322" s="1"/>
-    </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -16351,10 +15698,8 @@
       <c r="H323" s="1"/>
       <c r="I323" s="1"/>
       <c r="J323" s="1"/>
-      <c r="K323" s="1"/>
-      <c r="L323" s="1"/>
-    </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -16365,10 +15710,8 @@
       <c r="H324" s="1"/>
       <c r="I324" s="1"/>
       <c r="J324" s="1"/>
-      <c r="K324" s="1"/>
-      <c r="L324" s="1"/>
-    </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -16379,10 +15722,8 @@
       <c r="H325" s="1"/>
       <c r="I325" s="1"/>
       <c r="J325" s="1"/>
-      <c r="K325" s="1"/>
-      <c r="L325" s="1"/>
-    </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -16393,10 +15734,8 @@
       <c r="H326" s="1"/>
       <c r="I326" s="1"/>
       <c r="J326" s="1"/>
-      <c r="K326" s="1"/>
-      <c r="L326" s="1"/>
-    </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -16407,10 +15746,8 @@
       <c r="H327" s="1"/>
       <c r="I327" s="1"/>
       <c r="J327" s="1"/>
-      <c r="K327" s="1"/>
-      <c r="L327" s="1"/>
-    </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -16421,10 +15758,8 @@
       <c r="H328" s="1"/>
       <c r="I328" s="1"/>
       <c r="J328" s="1"/>
-      <c r="K328" s="1"/>
-      <c r="L328" s="1"/>
-    </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -16435,10 +15770,8 @@
       <c r="H329" s="1"/>
       <c r="I329" s="1"/>
       <c r="J329" s="1"/>
-      <c r="K329" s="1"/>
-      <c r="L329" s="1"/>
-    </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -16449,10 +15782,8 @@
       <c r="H330" s="1"/>
       <c r="I330" s="1"/>
       <c r="J330" s="1"/>
-      <c r="K330" s="1"/>
-      <c r="L330" s="1"/>
-    </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -16463,10 +15794,8 @@
       <c r="H331" s="1"/>
       <c r="I331" s="1"/>
       <c r="J331" s="1"/>
-      <c r="K331" s="1"/>
-      <c r="L331" s="1"/>
-    </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -16477,10 +15806,8 @@
       <c r="H332" s="1"/>
       <c r="I332" s="1"/>
       <c r="J332" s="1"/>
-      <c r="K332" s="1"/>
-      <c r="L332" s="1"/>
-    </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -16491,10 +15818,8 @@
       <c r="H333" s="1"/>
       <c r="I333" s="1"/>
       <c r="J333" s="1"/>
-      <c r="K333" s="1"/>
-      <c r="L333" s="1"/>
-    </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -16505,10 +15830,8 @@
       <c r="H334" s="1"/>
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
-      <c r="K334" s="1"/>
-      <c r="L334" s="1"/>
-    </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -16519,10 +15842,8 @@
       <c r="H335" s="1"/>
       <c r="I335" s="1"/>
       <c r="J335" s="1"/>
-      <c r="K335" s="1"/>
-      <c r="L335" s="1"/>
-    </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -16533,10 +15854,8 @@
       <c r="H336" s="1"/>
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
-      <c r="K336" s="1"/>
-      <c r="L336" s="1"/>
-    </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -16547,10 +15866,8 @@
       <c r="H337" s="1"/>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
-      <c r="K337" s="1"/>
-      <c r="L337" s="1"/>
-    </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -16561,10 +15878,8 @@
       <c r="H338" s="1"/>
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
-      <c r="K338" s="1"/>
-      <c r="L338" s="1"/>
-    </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -16575,10 +15890,8 @@
       <c r="H339" s="1"/>
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
-      <c r="K339" s="1"/>
-      <c r="L339" s="1"/>
-    </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -16589,10 +15902,8 @@
       <c r="H340" s="1"/>
       <c r="I340" s="1"/>
       <c r="J340" s="1"/>
-      <c r="K340" s="1"/>
-      <c r="L340" s="1"/>
-    </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -16603,10 +15914,8 @@
       <c r="H341" s="1"/>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
-      <c r="K341" s="1"/>
-      <c r="L341" s="1"/>
-    </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -16617,10 +15926,8 @@
       <c r="H342" s="1"/>
       <c r="I342" s="1"/>
       <c r="J342" s="1"/>
-      <c r="K342" s="1"/>
-      <c r="L342" s="1"/>
-    </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -16631,10 +15938,8 @@
       <c r="H343" s="1"/>
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
-      <c r="K343" s="1"/>
-      <c r="L343" s="1"/>
-    </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -16645,10 +15950,8 @@
       <c r="H344" s="1"/>
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
-      <c r="K344" s="1"/>
-      <c r="L344" s="1"/>
-    </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -16659,10 +15962,8 @@
       <c r="H345" s="1"/>
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
-      <c r="K345" s="1"/>
-      <c r="L345" s="1"/>
-    </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -16673,10 +15974,8 @@
       <c r="H346" s="1"/>
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
-      <c r="K346" s="1"/>
-      <c r="L346" s="1"/>
-    </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -16687,10 +15986,8 @@
       <c r="H347" s="1"/>
       <c r="I347" s="1"/>
       <c r="J347" s="1"/>
-      <c r="K347" s="1"/>
-      <c r="L347" s="1"/>
-    </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -16701,10 +15998,8 @@
       <c r="H348" s="1"/>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
-      <c r="K348" s="1"/>
-      <c r="L348" s="1"/>
-    </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -16714,10 +16009,8 @@
       <c r="H349" s="1"/>
       <c r="I349" s="1"/>
       <c r="J349" s="1"/>
-      <c r="K349" s="1"/>
-      <c r="L349" s="1"/>
-    </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -16727,10 +16020,8 @@
       <c r="H350" s="1"/>
       <c r="I350" s="1"/>
       <c r="J350" s="1"/>
-      <c r="K350" s="1"/>
-      <c r="L350" s="1"/>
-    </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -16740,10 +16031,8 @@
       <c r="H351" s="1"/>
       <c r="I351" s="1"/>
       <c r="J351" s="1"/>
-      <c r="K351" s="1"/>
-      <c r="L351" s="1"/>
-    </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -16752,10 +16041,8 @@
       <c r="G352" s="1"/>
       <c r="H352" s="1"/>
       <c r="J352" s="1"/>
-      <c r="K352" s="1"/>
-      <c r="L352" s="1"/>
-    </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -16764,10 +16051,8 @@
       <c r="G353" s="1"/>
       <c r="H353" s="1"/>
       <c r="J353" s="1"/>
-      <c r="K353" s="1"/>
-      <c r="L353" s="1"/>
-    </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -16776,10 +16061,8 @@
       <c r="G354" s="1"/>
       <c r="H354" s="1"/>
       <c r="J354" s="1"/>
-      <c r="K354" s="1"/>
-      <c r="L354" s="1"/>
-    </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -16788,8 +16071,6 @@
       <c r="G355" s="1"/>
       <c r="H355" s="1"/>
       <c r="J355" s="1"/>
-      <c r="K355" s="1"/>
-      <c r="L355" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6BEBA3-BD80-9648-AC6A-9A084A5D28D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07B9B60-EB7A-6D4F-9652-48DC32957816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="860" windowWidth="30240" windowHeight="17540" firstSheet="1" activeTab="4" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17540" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="6" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="additional keywords" sheetId="3" r:id="rId3"/>
     <sheet name="keywords_additional" sheetId="4" r:id="rId4"/>
     <sheet name="adapted_keywords" sheetId="5" r:id="rId5"/>
+    <sheet name="kw_icd_categories" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="350">
   <si>
     <t>DIABETES</t>
   </si>
@@ -1018,13 +1019,85 @@
   </si>
   <si>
     <t xml:space="preserve">homicide </t>
+  </si>
+  <si>
+    <t>CARDIOVASCULAR KEYWORDS</t>
+  </si>
+  <si>
+    <t>NEUROPSYCHIATRIC KEYWORDS</t>
+  </si>
+  <si>
+    <t>CANCERS KEYWORDS</t>
+  </si>
+  <si>
+    <t>RESPIRATORY KEWORDS</t>
+  </si>
+  <si>
+    <t>CEREBROVASCULAR ACCIDENT</t>
+  </si>
+  <si>
+    <t>SUBDURAL HEMATOMA</t>
+  </si>
+  <si>
+    <t>ACUTE MYELOID LEUKEMIA</t>
+  </si>
+  <si>
+    <t>CA OF ESOPHAGUS</t>
+  </si>
+  <si>
+    <t>CA OF LUNG</t>
+  </si>
+  <si>
+    <t>HEPATOCELLULAR CA</t>
+  </si>
+  <si>
+    <t>COMPLICATIONS OF MULTIPLE MELOMA</t>
+  </si>
+  <si>
+    <t>ACUTE RESPIRATORY FAILURE</t>
+  </si>
+  <si>
+    <t>ACUTE RESPIRATORY FAILURE WITH HYPOXIA</t>
+  </si>
+  <si>
+    <t>CHRONIC LOWER RESPIRATORY DISEASE</t>
+  </si>
+  <si>
+    <t>HYPOXIC RESPIRATORY FAILURE</t>
+  </si>
+  <si>
+    <t>IDIOPATHIC PULMONARY FIBROSIS</t>
+  </si>
+  <si>
+    <t>PULMONARY EDEMA</t>
+  </si>
+  <si>
+    <t>END STAGE RENAL DISEASE</t>
+  </si>
+  <si>
+    <t>LIVER FIALURE</t>
+  </si>
+  <si>
+    <t>CHRONIC ALCOHOL</t>
+  </si>
+  <si>
+    <t>HEMORRHAGIC SHOCK</t>
+  </si>
+  <si>
+    <t>NONCOMMUNICABLE DISEASE KEYWORDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEPATITIS </t>
+  </si>
+  <si>
+    <t>HEP C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1052,6 +1125,13 @@
       <name val="Lucida Grande"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1073,7 +1153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1086,6 +1166,11 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16075,4 +16160,6075 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEE812F-4599-D14A-8994-D04F411E7319}">
+  <dimension ref="A1:N355"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="24.83203125" customWidth="1"/>
+    <col min="10" max="10" width="35.33203125" customWidth="1"/>
+    <col min="11" max="11" width="37.6640625" customWidth="1"/>
+    <col min="12" max="12" width="42.1640625" style="7" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="23.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H2" t="s">
+        <v>270</v>
+      </c>
+      <c r="I2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" t="s">
+        <v>272</v>
+      </c>
+      <c r="J4" t="s">
+        <v>288</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H5" t="s">
+        <v>204</v>
+      </c>
+      <c r="I5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J5" t="s">
+        <v>187</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>261</v>
+      </c>
+      <c r="J6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" t="s">
+        <v>339</v>
+      </c>
+      <c r="I7" t="s">
+        <v>333</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" t="s">
+        <v>334</v>
+      </c>
+      <c r="J8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>250</v>
+      </c>
+      <c r="I9" t="s">
+        <v>257</v>
+      </c>
+      <c r="J9" t="s">
+        <v>330</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" t="s">
+        <v>280</v>
+      </c>
+      <c r="J10" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" t="s">
+        <v>264</v>
+      </c>
+      <c r="I11" t="s">
+        <v>298</v>
+      </c>
+      <c r="J11" t="s">
+        <v>243</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" t="s">
+        <v>340</v>
+      </c>
+      <c r="I12" t="s">
+        <v>162</v>
+      </c>
+      <c r="J12" t="s">
+        <v>282</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>129</v>
+      </c>
+      <c r="J14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" t="s">
+        <v>342</v>
+      </c>
+      <c r="I15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s">
+        <v>335</v>
+      </c>
+      <c r="J16" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
+        <v>239</v>
+      </c>
+      <c r="J17" t="s">
+        <v>266</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>269</v>
+      </c>
+      <c r="I18" t="s">
+        <v>238</v>
+      </c>
+      <c r="J18" t="s">
+        <v>265</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" t="s">
+        <v>278</v>
+      </c>
+      <c r="I19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" t="s">
+        <v>44</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" t="s">
+        <v>293</v>
+      </c>
+      <c r="I20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H21" t="s">
+        <v>237</v>
+      </c>
+      <c r="I21" t="s">
+        <v>260</v>
+      </c>
+      <c r="J21" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" t="s">
+        <v>240</v>
+      </c>
+      <c r="I22" t="s">
+        <v>252</v>
+      </c>
+      <c r="J22" t="s">
+        <v>57</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" t="s">
+        <v>68</v>
+      </c>
+      <c r="J24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" t="s">
+        <v>336</v>
+      </c>
+      <c r="J25" t="s">
+        <v>331</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M45" s="1"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M46" s="1"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M47" s="1"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M48" s="1"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M49" s="1"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M50" s="1"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="M51" s="1"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M52" s="1"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>236</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M53" s="1"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>241</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="M54" s="1"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M55" s="1"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M56" s="1"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M57" s="1"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M58" s="1"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M59" s="1"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="M60" s="1"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M61" s="1"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M62" s="1"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M63" s="1"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M64" s="1"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M65" s="1"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M66" s="1"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="M67" s="1"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="M68" s="1"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="M69" s="1"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="M70" s="1"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="1"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="1"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="1"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
+      <c r="K116" s="1"/>
+      <c r="L116" s="1"/>
+      <c r="M116" s="1"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="L118" s="1"/>
+      <c r="M118" s="1"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1"/>
+      <c r="L119" s="1"/>
+      <c r="M119" s="1"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+      <c r="K120" s="1"/>
+      <c r="L120" s="1"/>
+      <c r="M120" s="1"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="1"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="1"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="1"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="1"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+      <c r="K124" s="1"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="1"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1"/>
+      <c r="L125" s="1"/>
+      <c r="M125" s="1"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1"/>
+      <c r="L126" s="1"/>
+      <c r="M126" s="1"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+      <c r="K127" s="1"/>
+      <c r="L127" s="1"/>
+      <c r="M127" s="1"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+      <c r="L128" s="1"/>
+      <c r="M128" s="1"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+      <c r="L130" s="1"/>
+      <c r="M130" s="1"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="1"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="1"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+      <c r="K133" s="1"/>
+      <c r="L133" s="1"/>
+      <c r="M133" s="1"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="1"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
+      <c r="K135" s="1"/>
+      <c r="L135" s="1"/>
+      <c r="M135" s="1"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1"/>
+      <c r="L137" s="1"/>
+      <c r="M137" s="1"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
+      <c r="K138" s="1"/>
+      <c r="L138" s="1"/>
+      <c r="M138" s="1"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
+      <c r="K139" s="1"/>
+      <c r="L139" s="1"/>
+      <c r="M139" s="1"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
+      <c r="K140" s="1"/>
+      <c r="L140" s="1"/>
+      <c r="M140" s="1"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
+      <c r="K141" s="1"/>
+      <c r="L141" s="1"/>
+      <c r="M141" s="1"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
+      <c r="K142" s="1"/>
+      <c r="L142" s="1"/>
+      <c r="M142" s="1"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
+      <c r="E143" s="1"/>
+      <c r="F143" s="1"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
+      <c r="K143" s="1"/>
+      <c r="L143" s="1"/>
+      <c r="M143" s="1"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
+      <c r="K144" s="1"/>
+      <c r="L144" s="1"/>
+      <c r="M144" s="1"/>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="1"/>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1"/>
+      <c r="L145" s="1"/>
+      <c r="M145" s="1"/>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="1"/>
+      <c r="M146" s="1"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
+      <c r="F147" s="1"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
+      <c r="K147" s="1"/>
+      <c r="L147" s="1"/>
+      <c r="M147" s="1"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
+      <c r="K148" s="1"/>
+      <c r="L148" s="1"/>
+      <c r="M148" s="1"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1"/>
+      <c r="L149" s="1"/>
+      <c r="M149" s="1"/>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
+      <c r="K150" s="1"/>
+      <c r="L150" s="1"/>
+      <c r="M150" s="1"/>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
+      <c r="K151" s="1"/>
+      <c r="L151" s="1"/>
+      <c r="M151" s="1"/>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
+      <c r="K152" s="1"/>
+      <c r="L152" s="1"/>
+      <c r="M152" s="1"/>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
+      <c r="K153" s="1"/>
+      <c r="L153" s="1"/>
+      <c r="M153" s="1"/>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1"/>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
+      <c r="K154" s="1"/>
+      <c r="L154" s="1"/>
+      <c r="M154" s="1"/>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
+      <c r="K155" s="1"/>
+      <c r="L155" s="1"/>
+      <c r="M155" s="1"/>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
+      <c r="K156" s="1"/>
+      <c r="L156" s="1"/>
+      <c r="M156" s="1"/>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
+      <c r="K157" s="1"/>
+      <c r="L157" s="1"/>
+      <c r="M157" s="1"/>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A158" s="1"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="F158" s="1"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+      <c r="J158" s="1"/>
+      <c r="K158" s="1"/>
+      <c r="L158" s="1"/>
+      <c r="M158" s="1"/>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+      <c r="J159" s="1"/>
+      <c r="K159" s="1"/>
+      <c r="L159" s="1"/>
+      <c r="M159" s="1"/>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+      <c r="J162" s="1"/>
+      <c r="K162" s="1"/>
+      <c r="L162" s="1"/>
+      <c r="M162" s="1"/>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+      <c r="J163" s="1"/>
+      <c r="K163" s="1"/>
+      <c r="L163" s="1"/>
+      <c r="M163" s="1"/>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+      <c r="J164" s="1"/>
+      <c r="K164" s="1"/>
+      <c r="L164" s="1"/>
+      <c r="M164" s="1"/>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="K165" s="1"/>
+      <c r="L165" s="1"/>
+      <c r="M165" s="1"/>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+      <c r="J166" s="1"/>
+      <c r="K166" s="1"/>
+      <c r="L166" s="1"/>
+      <c r="M166" s="1"/>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="1"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+      <c r="J167" s="1"/>
+      <c r="K167" s="1"/>
+      <c r="L167" s="1"/>
+      <c r="M167" s="1"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
+      <c r="K168" s="1"/>
+      <c r="L168" s="1"/>
+      <c r="M168" s="1"/>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+      <c r="L169" s="1"/>
+      <c r="M169" s="1"/>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="K170" s="1"/>
+      <c r="L170" s="1"/>
+      <c r="M170" s="1"/>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="K171" s="1"/>
+      <c r="L171" s="1"/>
+      <c r="M171" s="1"/>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+      <c r="K172" s="1"/>
+      <c r="L172" s="1"/>
+      <c r="M172" s="1"/>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="K173" s="1"/>
+      <c r="L173" s="1"/>
+      <c r="M173" s="1"/>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="K174" s="1"/>
+      <c r="L174" s="1"/>
+      <c r="M174" s="1"/>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="1"/>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
+      <c r="L175" s="1"/>
+      <c r="M175" s="1"/>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+      <c r="K176" s="1"/>
+      <c r="L176" s="1"/>
+      <c r="M176" s="1"/>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+      <c r="E177" s="1"/>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+      <c r="J177" s="1"/>
+      <c r="K177" s="1"/>
+      <c r="L177" s="1"/>
+      <c r="M177" s="1"/>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="K178" s="1"/>
+      <c r="L178" s="1"/>
+      <c r="M178" s="1"/>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+      <c r="J179" s="1"/>
+      <c r="K179" s="1"/>
+      <c r="L179" s="1"/>
+      <c r="M179" s="1"/>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+      <c r="G180" s="1"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+      <c r="J180" s="1"/>
+      <c r="K180" s="1"/>
+      <c r="L180" s="1"/>
+      <c r="M180" s="1"/>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+      <c r="G181" s="1"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="K181" s="1"/>
+      <c r="L181" s="1"/>
+      <c r="M181" s="1"/>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="K182" s="1"/>
+      <c r="L182" s="1"/>
+      <c r="M182" s="1"/>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="1"/>
+      <c r="G183" s="1"/>
+      <c r="H183" s="1"/>
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+      <c r="K183" s="1"/>
+      <c r="L183" s="1"/>
+      <c r="M183" s="1"/>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
+      <c r="H184" s="1"/>
+      <c r="I184" s="1"/>
+      <c r="J184" s="1"/>
+      <c r="K184" s="1"/>
+      <c r="L184" s="1"/>
+      <c r="M184" s="1"/>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="1"/>
+      <c r="G185" s="1"/>
+      <c r="H185" s="1"/>
+      <c r="I185" s="1"/>
+      <c r="J185" s="1"/>
+      <c r="K185" s="1"/>
+      <c r="L185" s="1"/>
+      <c r="M185" s="1"/>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="1"/>
+      <c r="G186" s="1"/>
+      <c r="H186" s="1"/>
+      <c r="I186" s="1"/>
+      <c r="J186" s="1"/>
+      <c r="K186" s="1"/>
+      <c r="L186" s="1"/>
+      <c r="M186" s="1"/>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="1"/>
+      <c r="G187" s="1"/>
+      <c r="H187" s="1"/>
+      <c r="I187" s="1"/>
+      <c r="J187" s="1"/>
+      <c r="K187" s="1"/>
+      <c r="L187" s="1"/>
+      <c r="M187" s="1"/>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+      <c r="L188" s="1"/>
+      <c r="M188" s="1"/>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
+      <c r="L189" s="1"/>
+      <c r="M189" s="1"/>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+      <c r="K190" s="1"/>
+      <c r="L190" s="1"/>
+      <c r="M190" s="1"/>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+      <c r="K191" s="1"/>
+      <c r="L191" s="1"/>
+      <c r="M191" s="1"/>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+      <c r="J192" s="1"/>
+      <c r="K192" s="1"/>
+      <c r="L192" s="1"/>
+      <c r="M192" s="1"/>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+      <c r="J193" s="1"/>
+      <c r="K193" s="1"/>
+      <c r="L193" s="1"/>
+      <c r="M193" s="1"/>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+      <c r="J194" s="1"/>
+      <c r="K194" s="1"/>
+      <c r="L194" s="1"/>
+      <c r="M194" s="1"/>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195" s="1"/>
+      <c r="K195" s="1"/>
+      <c r="L195" s="1"/>
+      <c r="M195" s="1"/>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+      <c r="F196" s="1"/>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1"/>
+      <c r="I196" s="1"/>
+      <c r="J196" s="1"/>
+      <c r="K196" s="1"/>
+      <c r="L196" s="1"/>
+      <c r="M196" s="1"/>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1"/>
+      <c r="F197" s="1"/>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+      <c r="J197" s="1"/>
+      <c r="K197" s="1"/>
+      <c r="L197" s="1"/>
+      <c r="M197" s="1"/>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+      <c r="F198" s="1"/>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+      <c r="J198" s="1"/>
+      <c r="K198" s="1"/>
+      <c r="L198" s="1"/>
+      <c r="M198" s="1"/>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+      <c r="J199" s="1"/>
+      <c r="K199" s="1"/>
+      <c r="L199" s="1"/>
+      <c r="M199" s="1"/>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
+      <c r="E200" s="1"/>
+      <c r="F200" s="1"/>
+      <c r="G200" s="1"/>
+      <c r="H200" s="1"/>
+      <c r="I200" s="1"/>
+      <c r="J200" s="1"/>
+      <c r="K200" s="1"/>
+      <c r="L200" s="1"/>
+      <c r="M200" s="1"/>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+      <c r="F201" s="1"/>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+      <c r="J201" s="1"/>
+      <c r="K201" s="1"/>
+      <c r="L201" s="1"/>
+      <c r="M201" s="1"/>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="1"/>
+      <c r="F202" s="1"/>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1"/>
+      <c r="I202" s="1"/>
+      <c r="J202" s="1"/>
+      <c r="K202" s="1"/>
+      <c r="L202" s="1"/>
+      <c r="M202" s="1"/>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+      <c r="E203" s="1"/>
+      <c r="F203" s="1"/>
+      <c r="G203" s="1"/>
+      <c r="H203" s="1"/>
+      <c r="I203" s="1"/>
+      <c r="J203" s="1"/>
+      <c r="K203" s="1"/>
+      <c r="L203" s="1"/>
+      <c r="M203" s="1"/>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+      <c r="E204" s="1"/>
+      <c r="F204" s="1"/>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1"/>
+      <c r="J204" s="1"/>
+      <c r="K204" s="1"/>
+      <c r="L204" s="1"/>
+      <c r="M204" s="1"/>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+      <c r="E205" s="1"/>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1"/>
+      <c r="H205" s="1"/>
+      <c r="I205" s="1"/>
+      <c r="J205" s="1"/>
+      <c r="K205" s="1"/>
+      <c r="L205" s="1"/>
+      <c r="M205" s="1"/>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="1"/>
+      <c r="F206" s="1"/>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+      <c r="I206" s="1"/>
+      <c r="J206" s="1"/>
+      <c r="K206" s="1"/>
+      <c r="L206" s="1"/>
+      <c r="M206" s="1"/>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+      <c r="E207" s="1"/>
+      <c r="F207" s="1"/>
+      <c r="G207" s="1"/>
+      <c r="H207" s="1"/>
+      <c r="I207" s="1"/>
+      <c r="J207" s="1"/>
+      <c r="K207" s="1"/>
+      <c r="L207" s="1"/>
+      <c r="M207" s="1"/>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
+      <c r="E208" s="1"/>
+      <c r="F208" s="1"/>
+      <c r="G208" s="1"/>
+      <c r="H208" s="1"/>
+      <c r="I208" s="1"/>
+      <c r="J208" s="1"/>
+      <c r="K208" s="1"/>
+      <c r="L208" s="1"/>
+      <c r="M208" s="1"/>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
+      <c r="E209" s="1"/>
+      <c r="F209" s="1"/>
+      <c r="G209" s="1"/>
+      <c r="H209" s="1"/>
+      <c r="I209" s="1"/>
+      <c r="J209" s="1"/>
+      <c r="K209" s="1"/>
+      <c r="L209" s="1"/>
+      <c r="M209" s="1"/>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+      <c r="E210" s="1"/>
+      <c r="F210" s="1"/>
+      <c r="G210" s="1"/>
+      <c r="H210" s="1"/>
+      <c r="I210" s="1"/>
+      <c r="J210" s="1"/>
+      <c r="K210" s="1"/>
+      <c r="L210" s="1"/>
+      <c r="M210" s="1"/>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+      <c r="E211" s="1"/>
+      <c r="F211" s="1"/>
+      <c r="G211" s="1"/>
+      <c r="H211" s="1"/>
+      <c r="I211" s="1"/>
+      <c r="J211" s="1"/>
+      <c r="K211" s="1"/>
+      <c r="L211" s="1"/>
+      <c r="M211" s="1"/>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+      <c r="E212" s="1"/>
+      <c r="F212" s="1"/>
+      <c r="G212" s="1"/>
+      <c r="H212" s="1"/>
+      <c r="I212" s="1"/>
+      <c r="J212" s="1"/>
+      <c r="K212" s="1"/>
+      <c r="L212" s="1"/>
+      <c r="M212" s="1"/>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A213" s="1"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
+      <c r="E213" s="1"/>
+      <c r="F213" s="1"/>
+      <c r="G213" s="1"/>
+      <c r="H213" s="1"/>
+      <c r="I213" s="1"/>
+      <c r="J213" s="1"/>
+      <c r="K213" s="1"/>
+      <c r="L213" s="1"/>
+      <c r="M213" s="1"/>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="1"/>
+      <c r="F214" s="1"/>
+      <c r="G214" s="1"/>
+      <c r="H214" s="1"/>
+      <c r="I214" s="1"/>
+      <c r="J214" s="1"/>
+      <c r="K214" s="1"/>
+      <c r="L214" s="1"/>
+      <c r="M214" s="1"/>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A215" s="1"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
+      <c r="E215" s="1"/>
+      <c r="F215" s="1"/>
+      <c r="G215" s="1"/>
+      <c r="H215" s="1"/>
+      <c r="I215" s="1"/>
+      <c r="J215" s="1"/>
+      <c r="K215" s="1"/>
+      <c r="L215" s="1"/>
+      <c r="M215" s="1"/>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+      <c r="E216" s="1"/>
+      <c r="F216" s="1"/>
+      <c r="G216" s="1"/>
+      <c r="H216" s="1"/>
+      <c r="I216" s="1"/>
+      <c r="J216" s="1"/>
+      <c r="K216" s="1"/>
+      <c r="L216" s="1"/>
+      <c r="M216" s="1"/>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
+      <c r="E217" s="1"/>
+      <c r="F217" s="1"/>
+      <c r="G217" s="1"/>
+      <c r="H217" s="1"/>
+      <c r="I217" s="1"/>
+      <c r="J217" s="1"/>
+      <c r="K217" s="1"/>
+      <c r="L217" s="1"/>
+      <c r="M217" s="1"/>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
+      <c r="E218" s="1"/>
+      <c r="F218" s="1"/>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1"/>
+      <c r="I218" s="1"/>
+      <c r="J218" s="1"/>
+      <c r="K218" s="1"/>
+      <c r="L218" s="1"/>
+      <c r="M218" s="1"/>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+      <c r="K219" s="1"/>
+      <c r="L219" s="1"/>
+      <c r="M219" s="1"/>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
+      <c r="E220" s="1"/>
+      <c r="F220" s="1"/>
+      <c r="G220" s="1"/>
+      <c r="H220" s="1"/>
+      <c r="I220" s="1"/>
+      <c r="J220" s="1"/>
+      <c r="K220" s="1"/>
+      <c r="L220" s="1"/>
+      <c r="M220" s="1"/>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+      <c r="J221" s="1"/>
+      <c r="K221" s="1"/>
+      <c r="L221" s="1"/>
+      <c r="M221" s="1"/>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
+      <c r="E222" s="1"/>
+      <c r="F222" s="1"/>
+      <c r="G222" s="1"/>
+      <c r="H222" s="1"/>
+      <c r="I222" s="1"/>
+      <c r="J222" s="1"/>
+      <c r="K222" s="1"/>
+      <c r="L222" s="1"/>
+      <c r="M222" s="1"/>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+      <c r="E223" s="1"/>
+      <c r="F223" s="1"/>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
+      <c r="J223" s="1"/>
+      <c r="K223" s="1"/>
+      <c r="L223" s="1"/>
+      <c r="M223" s="1"/>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A224" s="1"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+      <c r="E224" s="1"/>
+      <c r="F224" s="1"/>
+      <c r="G224" s="1"/>
+      <c r="H224" s="1"/>
+      <c r="I224" s="1"/>
+      <c r="J224" s="1"/>
+      <c r="K224" s="1"/>
+      <c r="L224" s="1"/>
+      <c r="M224" s="1"/>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
+      <c r="E225" s="1"/>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1"/>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+      <c r="J225" s="1"/>
+      <c r="K225" s="1"/>
+      <c r="L225" s="1"/>
+      <c r="M225" s="1"/>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
+      <c r="E226" s="1"/>
+      <c r="F226" s="1"/>
+      <c r="G226" s="1"/>
+      <c r="H226" s="1"/>
+      <c r="I226" s="1"/>
+      <c r="J226" s="1"/>
+      <c r="K226" s="1"/>
+      <c r="L226" s="1"/>
+      <c r="M226" s="1"/>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
+      <c r="E227" s="1"/>
+      <c r="F227" s="1"/>
+      <c r="G227" s="1"/>
+      <c r="H227" s="1"/>
+      <c r="I227" s="1"/>
+      <c r="J227" s="1"/>
+      <c r="K227" s="1"/>
+      <c r="L227" s="1"/>
+      <c r="M227" s="1"/>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1"/>
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+      <c r="J228" s="1"/>
+      <c r="K228" s="1"/>
+      <c r="L228" s="1"/>
+      <c r="M228" s="1"/>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
+      <c r="E229" s="1"/>
+      <c r="F229" s="1"/>
+      <c r="G229" s="1"/>
+      <c r="H229" s="1"/>
+      <c r="I229" s="1"/>
+      <c r="J229" s="1"/>
+      <c r="K229" s="1"/>
+      <c r="L229" s="1"/>
+      <c r="M229" s="1"/>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
+      <c r="E230" s="1"/>
+      <c r="F230" s="1"/>
+      <c r="G230" s="1"/>
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
+      <c r="J230" s="1"/>
+      <c r="K230" s="1"/>
+      <c r="L230" s="1"/>
+      <c r="M230" s="1"/>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+      <c r="I231" s="1"/>
+      <c r="J231" s="1"/>
+      <c r="K231" s="1"/>
+      <c r="L231" s="1"/>
+      <c r="M231" s="1"/>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+      <c r="E232" s="1"/>
+      <c r="F232" s="1"/>
+      <c r="G232" s="1"/>
+      <c r="H232" s="1"/>
+      <c r="I232" s="1"/>
+      <c r="J232" s="1"/>
+      <c r="K232" s="1"/>
+      <c r="L232" s="1"/>
+      <c r="M232" s="1"/>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+      <c r="E233" s="1"/>
+      <c r="F233" s="1"/>
+      <c r="G233" s="1"/>
+      <c r="H233" s="1"/>
+      <c r="I233" s="1"/>
+      <c r="J233" s="1"/>
+      <c r="K233" s="1"/>
+      <c r="L233" s="1"/>
+      <c r="M233" s="1"/>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1"/>
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+      <c r="J234" s="1"/>
+      <c r="K234" s="1"/>
+      <c r="L234" s="1"/>
+      <c r="M234" s="1"/>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+      <c r="J235" s="1"/>
+      <c r="K235" s="1"/>
+      <c r="L235" s="1"/>
+      <c r="M235" s="1"/>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+      <c r="F236" s="1"/>
+      <c r="G236" s="1"/>
+      <c r="H236" s="1"/>
+      <c r="I236" s="1"/>
+      <c r="J236" s="1"/>
+      <c r="K236" s="1"/>
+      <c r="L236" s="1"/>
+      <c r="M236" s="1"/>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+      <c r="J237" s="1"/>
+      <c r="K237" s="1"/>
+      <c r="L237" s="1"/>
+      <c r="M237" s="1"/>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="K238" s="1"/>
+      <c r="L238" s="1"/>
+      <c r="M238" s="1"/>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
+      <c r="K239" s="1"/>
+      <c r="L239" s="1"/>
+      <c r="M239" s="1"/>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+      <c r="F240" s="1"/>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+      <c r="J240" s="1"/>
+      <c r="K240" s="1"/>
+      <c r="L240" s="1"/>
+      <c r="M240" s="1"/>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+      <c r="F241" s="1"/>
+      <c r="G241" s="1"/>
+      <c r="H241" s="1"/>
+      <c r="I241" s="1"/>
+      <c r="J241" s="1"/>
+      <c r="K241" s="1"/>
+      <c r="L241" s="1"/>
+      <c r="M241" s="1"/>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+      <c r="E242" s="1"/>
+      <c r="F242" s="1"/>
+      <c r="G242" s="1"/>
+      <c r="H242" s="1"/>
+      <c r="I242" s="1"/>
+      <c r="J242" s="1"/>
+      <c r="K242" s="1"/>
+      <c r="L242" s="1"/>
+      <c r="M242" s="1"/>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1"/>
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+      <c r="J243" s="1"/>
+      <c r="K243" s="1"/>
+      <c r="L243" s="1"/>
+      <c r="M243" s="1"/>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
+      <c r="G244" s="1"/>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1"/>
+      <c r="J244" s="1"/>
+      <c r="K244" s="1"/>
+      <c r="L244" s="1"/>
+      <c r="M244" s="1"/>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+      <c r="E245" s="1"/>
+      <c r="F245" s="1"/>
+      <c r="G245" s="1"/>
+      <c r="H245" s="1"/>
+      <c r="I245" s="1"/>
+      <c r="J245" s="1"/>
+      <c r="K245" s="1"/>
+      <c r="L245" s="1"/>
+      <c r="M245" s="1"/>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+      <c r="E246" s="1"/>
+      <c r="F246" s="1"/>
+      <c r="G246" s="1"/>
+      <c r="H246" s="1"/>
+      <c r="I246" s="1"/>
+      <c r="J246" s="1"/>
+      <c r="K246" s="1"/>
+      <c r="L246" s="1"/>
+      <c r="M246" s="1"/>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+      <c r="E247" s="1"/>
+      <c r="F247" s="1"/>
+      <c r="G247" s="1"/>
+      <c r="H247" s="1"/>
+      <c r="I247" s="1"/>
+      <c r="J247" s="1"/>
+      <c r="K247" s="1"/>
+      <c r="L247" s="1"/>
+      <c r="M247" s="1"/>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A248" s="1"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+      <c r="F248" s="1"/>
+      <c r="G248" s="1"/>
+      <c r="H248" s="1"/>
+      <c r="I248" s="1"/>
+      <c r="J248" s="1"/>
+      <c r="K248" s="1"/>
+      <c r="L248" s="1"/>
+      <c r="M248" s="1"/>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
+      <c r="G249" s="1"/>
+      <c r="H249" s="1"/>
+      <c r="I249" s="1"/>
+      <c r="J249" s="1"/>
+      <c r="K249" s="1"/>
+      <c r="L249" s="1"/>
+      <c r="M249" s="1"/>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
+      <c r="G250" s="1"/>
+      <c r="H250" s="1"/>
+      <c r="I250" s="1"/>
+      <c r="J250" s="1"/>
+      <c r="K250" s="1"/>
+      <c r="L250" s="1"/>
+      <c r="M250" s="1"/>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
+      <c r="E251" s="1"/>
+      <c r="F251" s="1"/>
+      <c r="G251" s="1"/>
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
+      <c r="J251" s="1"/>
+      <c r="K251" s="1"/>
+      <c r="L251" s="1"/>
+      <c r="M251" s="1"/>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+      <c r="F252" s="1"/>
+      <c r="G252" s="1"/>
+      <c r="H252" s="1"/>
+      <c r="I252" s="1"/>
+      <c r="J252" s="1"/>
+      <c r="K252" s="1"/>
+      <c r="L252" s="1"/>
+      <c r="M252" s="1"/>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1"/>
+      <c r="F253" s="1"/>
+      <c r="G253" s="1"/>
+      <c r="H253" s="1"/>
+      <c r="I253" s="1"/>
+      <c r="J253" s="1"/>
+      <c r="K253" s="1"/>
+      <c r="L253" s="1"/>
+      <c r="M253" s="1"/>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+      <c r="F254" s="1"/>
+      <c r="G254" s="1"/>
+      <c r="H254" s="1"/>
+      <c r="I254" s="1"/>
+      <c r="J254" s="1"/>
+      <c r="K254" s="1"/>
+      <c r="L254" s="1"/>
+      <c r="M254" s="1"/>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
+      <c r="E255" s="1"/>
+      <c r="F255" s="1"/>
+      <c r="G255" s="1"/>
+      <c r="H255" s="1"/>
+      <c r="I255" s="1"/>
+      <c r="J255" s="1"/>
+      <c r="K255" s="1"/>
+      <c r="L255" s="1"/>
+      <c r="M255" s="1"/>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
+      <c r="G256" s="1"/>
+      <c r="H256" s="1"/>
+      <c r="I256" s="1"/>
+      <c r="J256" s="1"/>
+      <c r="K256" s="1"/>
+      <c r="L256" s="1"/>
+      <c r="M256" s="1"/>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A257" s="1"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
+      <c r="E257" s="1"/>
+      <c r="F257" s="1"/>
+      <c r="G257" s="1"/>
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+      <c r="J257" s="1"/>
+      <c r="K257" s="1"/>
+      <c r="L257" s="1"/>
+      <c r="M257" s="1"/>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
+      <c r="G258" s="1"/>
+      <c r="H258" s="1"/>
+      <c r="I258" s="1"/>
+      <c r="J258" s="1"/>
+      <c r="K258" s="1"/>
+      <c r="L258" s="1"/>
+      <c r="M258" s="1"/>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+      <c r="E259" s="1"/>
+      <c r="F259" s="1"/>
+      <c r="G259" s="1"/>
+      <c r="H259" s="1"/>
+      <c r="I259" s="1"/>
+      <c r="J259" s="1"/>
+      <c r="K259" s="1"/>
+      <c r="L259" s="1"/>
+      <c r="M259" s="1"/>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
+      <c r="E260" s="1"/>
+      <c r="F260" s="1"/>
+      <c r="G260" s="1"/>
+      <c r="H260" s="1"/>
+      <c r="I260" s="1"/>
+      <c r="J260" s="1"/>
+      <c r="K260" s="1"/>
+      <c r="L260" s="1"/>
+      <c r="M260" s="1"/>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
+      <c r="E261" s="1"/>
+      <c r="F261" s="1"/>
+      <c r="G261" s="1"/>
+      <c r="H261" s="1"/>
+      <c r="I261" s="1"/>
+      <c r="J261" s="1"/>
+      <c r="K261" s="1"/>
+      <c r="L261" s="1"/>
+      <c r="M261" s="1"/>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
+      <c r="E262" s="1"/>
+      <c r="F262" s="1"/>
+      <c r="G262" s="1"/>
+      <c r="H262" s="1"/>
+      <c r="I262" s="1"/>
+      <c r="J262" s="1"/>
+      <c r="K262" s="1"/>
+      <c r="L262" s="1"/>
+      <c r="M262" s="1"/>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+      <c r="E263" s="1"/>
+      <c r="F263" s="1"/>
+      <c r="G263" s="1"/>
+      <c r="H263" s="1"/>
+      <c r="I263" s="1"/>
+      <c r="J263" s="1"/>
+      <c r="K263" s="1"/>
+      <c r="L263" s="1"/>
+      <c r="M263" s="1"/>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A264" s="1"/>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
+      <c r="E264" s="1"/>
+      <c r="F264" s="1"/>
+      <c r="G264" s="1"/>
+      <c r="H264" s="1"/>
+      <c r="I264" s="1"/>
+      <c r="J264" s="1"/>
+      <c r="K264" s="1"/>
+      <c r="L264" s="1"/>
+      <c r="M264" s="1"/>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A265" s="1"/>
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
+      <c r="E265" s="1"/>
+      <c r="F265" s="1"/>
+      <c r="G265" s="1"/>
+      <c r="H265" s="1"/>
+      <c r="I265" s="1"/>
+      <c r="J265" s="1"/>
+      <c r="K265" s="1"/>
+      <c r="L265" s="1"/>
+      <c r="M265" s="1"/>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A266" s="1"/>
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
+      <c r="E266" s="1"/>
+      <c r="F266" s="1"/>
+      <c r="G266" s="1"/>
+      <c r="H266" s="1"/>
+      <c r="I266" s="1"/>
+      <c r="J266" s="1"/>
+      <c r="K266" s="1"/>
+      <c r="L266" s="1"/>
+      <c r="M266" s="1"/>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A267" s="1"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
+      <c r="E267" s="1"/>
+      <c r="F267" s="1"/>
+      <c r="G267" s="1"/>
+      <c r="H267" s="1"/>
+      <c r="I267" s="1"/>
+      <c r="J267" s="1"/>
+      <c r="K267" s="1"/>
+      <c r="L267" s="1"/>
+      <c r="M267" s="1"/>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A268" s="1"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
+      <c r="E268" s="1"/>
+      <c r="F268" s="1"/>
+      <c r="G268" s="1"/>
+      <c r="H268" s="1"/>
+      <c r="I268" s="1"/>
+      <c r="J268" s="1"/>
+      <c r="K268" s="1"/>
+      <c r="L268" s="1"/>
+      <c r="M268" s="1"/>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A269" s="1"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
+      <c r="E269" s="1"/>
+      <c r="F269" s="1"/>
+      <c r="G269" s="1"/>
+      <c r="H269" s="1"/>
+      <c r="I269" s="1"/>
+      <c r="J269" s="1"/>
+      <c r="K269" s="1"/>
+      <c r="L269" s="1"/>
+      <c r="M269" s="1"/>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A270" s="1"/>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
+      <c r="E270" s="1"/>
+      <c r="F270" s="1"/>
+      <c r="G270" s="1"/>
+      <c r="H270" s="1"/>
+      <c r="I270" s="1"/>
+      <c r="J270" s="1"/>
+      <c r="K270" s="1"/>
+      <c r="L270" s="1"/>
+      <c r="M270" s="1"/>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A271" s="1"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+      <c r="E271" s="1"/>
+      <c r="F271" s="1"/>
+      <c r="G271" s="1"/>
+      <c r="H271" s="1"/>
+      <c r="I271" s="1"/>
+      <c r="J271" s="1"/>
+      <c r="K271" s="1"/>
+      <c r="L271" s="1"/>
+      <c r="M271" s="1"/>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A272" s="1"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+      <c r="E272" s="1"/>
+      <c r="F272" s="1"/>
+      <c r="G272" s="1"/>
+      <c r="H272" s="1"/>
+      <c r="I272" s="1"/>
+      <c r="J272" s="1"/>
+      <c r="K272" s="1"/>
+      <c r="L272" s="1"/>
+      <c r="M272" s="1"/>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A273" s="1"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+      <c r="E273" s="1"/>
+      <c r="F273" s="1"/>
+      <c r="G273" s="1"/>
+      <c r="H273" s="1"/>
+      <c r="I273" s="1"/>
+      <c r="J273" s="1"/>
+      <c r="K273" s="1"/>
+      <c r="L273" s="1"/>
+      <c r="M273" s="1"/>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A274" s="1"/>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
+      <c r="E274" s="1"/>
+      <c r="F274" s="1"/>
+      <c r="G274" s="1"/>
+      <c r="H274" s="1"/>
+      <c r="I274" s="1"/>
+      <c r="J274" s="1"/>
+      <c r="K274" s="1"/>
+      <c r="L274" s="1"/>
+      <c r="M274" s="1"/>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A275" s="1"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+      <c r="E275" s="1"/>
+      <c r="F275" s="1"/>
+      <c r="G275" s="1"/>
+      <c r="H275" s="1"/>
+      <c r="I275" s="1"/>
+      <c r="J275" s="1"/>
+      <c r="K275" s="1"/>
+      <c r="L275" s="1"/>
+      <c r="M275" s="1"/>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A276" s="1"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+      <c r="E276" s="1"/>
+      <c r="F276" s="1"/>
+      <c r="G276" s="1"/>
+      <c r="H276" s="1"/>
+      <c r="I276" s="1"/>
+      <c r="J276" s="1"/>
+      <c r="K276" s="1"/>
+      <c r="L276" s="1"/>
+      <c r="M276" s="1"/>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A277" s="1"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+      <c r="E277" s="1"/>
+      <c r="F277" s="1"/>
+      <c r="G277" s="1"/>
+      <c r="H277" s="1"/>
+      <c r="I277" s="1"/>
+      <c r="J277" s="1"/>
+      <c r="K277" s="1"/>
+      <c r="L277" s="1"/>
+      <c r="M277" s="1"/>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A278" s="1"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+      <c r="E278" s="1"/>
+      <c r="F278" s="1"/>
+      <c r="G278" s="1"/>
+      <c r="H278" s="1"/>
+      <c r="I278" s="1"/>
+      <c r="J278" s="1"/>
+      <c r="K278" s="1"/>
+      <c r="L278" s="1"/>
+      <c r="M278" s="1"/>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A279" s="1"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
+      <c r="G279" s="1"/>
+      <c r="H279" s="1"/>
+      <c r="I279" s="1"/>
+      <c r="J279" s="1"/>
+      <c r="K279" s="1"/>
+      <c r="L279" s="1"/>
+      <c r="M279" s="1"/>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A280" s="1"/>
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
+      <c r="E280" s="1"/>
+      <c r="F280" s="1"/>
+      <c r="G280" s="1"/>
+      <c r="H280" s="1"/>
+      <c r="I280" s="1"/>
+      <c r="J280" s="1"/>
+      <c r="K280" s="1"/>
+      <c r="L280" s="1"/>
+      <c r="M280" s="1"/>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A281" s="1"/>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
+      <c r="E281" s="1"/>
+      <c r="F281" s="1"/>
+      <c r="G281" s="1"/>
+      <c r="H281" s="1"/>
+      <c r="I281" s="1"/>
+      <c r="J281" s="1"/>
+      <c r="K281" s="1"/>
+      <c r="L281" s="1"/>
+      <c r="M281" s="1"/>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A282" s="1"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
+      <c r="E282" s="1"/>
+      <c r="F282" s="1"/>
+      <c r="G282" s="1"/>
+      <c r="H282" s="1"/>
+      <c r="I282" s="1"/>
+      <c r="J282" s="1"/>
+      <c r="K282" s="1"/>
+      <c r="L282" s="1"/>
+      <c r="M282" s="1"/>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A283" s="1"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
+      <c r="E283" s="1"/>
+      <c r="F283" s="1"/>
+      <c r="G283" s="1"/>
+      <c r="H283" s="1"/>
+      <c r="I283" s="1"/>
+      <c r="J283" s="1"/>
+      <c r="K283" s="1"/>
+      <c r="L283" s="1"/>
+      <c r="M283" s="1"/>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A284" s="1"/>
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
+      <c r="E284" s="1"/>
+      <c r="F284" s="1"/>
+      <c r="G284" s="1"/>
+      <c r="H284" s="1"/>
+      <c r="I284" s="1"/>
+      <c r="J284" s="1"/>
+      <c r="K284" s="1"/>
+      <c r="L284" s="1"/>
+      <c r="M284" s="1"/>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A285" s="1"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
+      <c r="E285" s="1"/>
+      <c r="F285" s="1"/>
+      <c r="G285" s="1"/>
+      <c r="H285" s="1"/>
+      <c r="I285" s="1"/>
+      <c r="J285" s="1"/>
+      <c r="K285" s="1"/>
+      <c r="L285" s="1"/>
+      <c r="M285" s="1"/>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A286" s="1"/>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
+      <c r="E286" s="1"/>
+      <c r="F286" s="1"/>
+      <c r="G286" s="1"/>
+      <c r="H286" s="1"/>
+      <c r="I286" s="1"/>
+      <c r="J286" s="1"/>
+      <c r="K286" s="1"/>
+      <c r="L286" s="1"/>
+      <c r="M286" s="1"/>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A287" s="1"/>
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
+      <c r="E287" s="1"/>
+      <c r="F287" s="1"/>
+      <c r="G287" s="1"/>
+      <c r="H287" s="1"/>
+      <c r="I287" s="1"/>
+      <c r="J287" s="1"/>
+      <c r="K287" s="1"/>
+      <c r="L287" s="1"/>
+      <c r="M287" s="1"/>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A288" s="1"/>
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
+      <c r="E288" s="1"/>
+      <c r="F288" s="1"/>
+      <c r="G288" s="1"/>
+      <c r="H288" s="1"/>
+      <c r="I288" s="1"/>
+      <c r="J288" s="1"/>
+      <c r="K288" s="1"/>
+      <c r="L288" s="1"/>
+      <c r="M288" s="1"/>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A289" s="1"/>
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
+      <c r="E289" s="1"/>
+      <c r="F289" s="1"/>
+      <c r="G289" s="1"/>
+      <c r="H289" s="1"/>
+      <c r="I289" s="1"/>
+      <c r="J289" s="1"/>
+      <c r="K289" s="1"/>
+      <c r="L289" s="1"/>
+      <c r="M289" s="1"/>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A290" s="1"/>
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
+      <c r="E290" s="1"/>
+      <c r="F290" s="1"/>
+      <c r="G290" s="1"/>
+      <c r="H290" s="1"/>
+      <c r="I290" s="1"/>
+      <c r="J290" s="1"/>
+      <c r="K290" s="1"/>
+      <c r="L290" s="1"/>
+      <c r="M290" s="1"/>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A291" s="1"/>
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
+      <c r="E291" s="1"/>
+      <c r="F291" s="1"/>
+      <c r="G291" s="1"/>
+      <c r="H291" s="1"/>
+      <c r="I291" s="1"/>
+      <c r="J291" s="1"/>
+      <c r="K291" s="1"/>
+      <c r="L291" s="1"/>
+      <c r="M291" s="1"/>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A292" s="1"/>
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
+      <c r="E292" s="1"/>
+      <c r="F292" s="1"/>
+      <c r="G292" s="1"/>
+      <c r="H292" s="1"/>
+      <c r="I292" s="1"/>
+      <c r="J292" s="1"/>
+      <c r="K292" s="1"/>
+      <c r="L292" s="1"/>
+      <c r="M292" s="1"/>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A293" s="1"/>
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
+      <c r="E293" s="1"/>
+      <c r="F293" s="1"/>
+      <c r="G293" s="1"/>
+      <c r="H293" s="1"/>
+      <c r="I293" s="1"/>
+      <c r="J293" s="1"/>
+      <c r="K293" s="1"/>
+      <c r="L293" s="1"/>
+      <c r="M293" s="1"/>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A294" s="1"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
+      <c r="E294" s="1"/>
+      <c r="F294" s="1"/>
+      <c r="G294" s="1"/>
+      <c r="H294" s="1"/>
+      <c r="I294" s="1"/>
+      <c r="J294" s="1"/>
+      <c r="K294" s="1"/>
+      <c r="L294" s="1"/>
+      <c r="M294" s="1"/>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A295" s="1"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
+      <c r="E295" s="1"/>
+      <c r="F295" s="1"/>
+      <c r="G295" s="1"/>
+      <c r="H295" s="1"/>
+      <c r="I295" s="1"/>
+      <c r="J295" s="1"/>
+      <c r="K295" s="1"/>
+      <c r="L295" s="1"/>
+      <c r="M295" s="1"/>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A296" s="1"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="1"/>
+      <c r="E296" s="1"/>
+      <c r="F296" s="1"/>
+      <c r="G296" s="1"/>
+      <c r="H296" s="1"/>
+      <c r="I296" s="1"/>
+      <c r="J296" s="1"/>
+      <c r="K296" s="1"/>
+      <c r="L296" s="1"/>
+      <c r="M296" s="1"/>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A297" s="1"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="1"/>
+      <c r="E297" s="1"/>
+      <c r="F297" s="1"/>
+      <c r="G297" s="1"/>
+      <c r="H297" s="1"/>
+      <c r="I297" s="1"/>
+      <c r="J297" s="1"/>
+      <c r="K297" s="1"/>
+      <c r="L297" s="1"/>
+      <c r="M297" s="1"/>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A298" s="1"/>
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="1"/>
+      <c r="E298" s="1"/>
+      <c r="F298" s="1"/>
+      <c r="G298" s="1"/>
+      <c r="H298" s="1"/>
+      <c r="I298" s="1"/>
+      <c r="J298" s="1"/>
+      <c r="K298" s="1"/>
+      <c r="L298" s="1"/>
+      <c r="M298" s="1"/>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A299" s="1"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
+      <c r="E299" s="1"/>
+      <c r="F299" s="1"/>
+      <c r="G299" s="1"/>
+      <c r="H299" s="1"/>
+      <c r="I299" s="1"/>
+      <c r="J299" s="1"/>
+      <c r="K299" s="1"/>
+      <c r="L299" s="1"/>
+      <c r="M299" s="1"/>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A300" s="1"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="1"/>
+      <c r="E300" s="1"/>
+      <c r="F300" s="1"/>
+      <c r="G300" s="1"/>
+      <c r="H300" s="1"/>
+      <c r="I300" s="1"/>
+      <c r="J300" s="1"/>
+      <c r="K300" s="1"/>
+      <c r="L300" s="1"/>
+      <c r="M300" s="1"/>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A301" s="1"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="1"/>
+      <c r="E301" s="1"/>
+      <c r="F301" s="1"/>
+      <c r="G301" s="1"/>
+      <c r="H301" s="1"/>
+      <c r="I301" s="1"/>
+      <c r="J301" s="1"/>
+      <c r="K301" s="1"/>
+      <c r="L301" s="1"/>
+      <c r="M301" s="1"/>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A302" s="1"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="1"/>
+      <c r="E302" s="1"/>
+      <c r="F302" s="1"/>
+      <c r="G302" s="1"/>
+      <c r="H302" s="1"/>
+      <c r="I302" s="1"/>
+      <c r="J302" s="1"/>
+      <c r="K302" s="1"/>
+      <c r="L302" s="1"/>
+      <c r="M302" s="1"/>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A303" s="1"/>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="1"/>
+      <c r="E303" s="1"/>
+      <c r="F303" s="1"/>
+      <c r="G303" s="1"/>
+      <c r="H303" s="1"/>
+      <c r="I303" s="1"/>
+      <c r="J303" s="1"/>
+      <c r="K303" s="1"/>
+      <c r="L303" s="1"/>
+      <c r="M303" s="1"/>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A304" s="1"/>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="1"/>
+      <c r="E304" s="1"/>
+      <c r="F304" s="1"/>
+      <c r="G304" s="1"/>
+      <c r="H304" s="1"/>
+      <c r="I304" s="1"/>
+      <c r="J304" s="1"/>
+      <c r="K304" s="1"/>
+      <c r="L304" s="1"/>
+      <c r="M304" s="1"/>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A305" s="1"/>
+      <c r="B305" s="1"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="1"/>
+      <c r="E305" s="1"/>
+      <c r="F305" s="1"/>
+      <c r="G305" s="1"/>
+      <c r="H305" s="1"/>
+      <c r="I305" s="1"/>
+      <c r="J305" s="1"/>
+      <c r="K305" s="1"/>
+      <c r="L305" s="1"/>
+      <c r="M305" s="1"/>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A306" s="1"/>
+      <c r="B306" s="1"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="1"/>
+      <c r="E306" s="1"/>
+      <c r="F306" s="1"/>
+      <c r="G306" s="1"/>
+      <c r="H306" s="1"/>
+      <c r="I306" s="1"/>
+      <c r="J306" s="1"/>
+      <c r="K306" s="1"/>
+      <c r="L306" s="1"/>
+      <c r="M306" s="1"/>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A307" s="1"/>
+      <c r="B307" s="1"/>
+      <c r="C307" s="1"/>
+      <c r="D307" s="1"/>
+      <c r="E307" s="1"/>
+      <c r="F307" s="1"/>
+      <c r="G307" s="1"/>
+      <c r="H307" s="1"/>
+      <c r="I307" s="1"/>
+      <c r="J307" s="1"/>
+      <c r="K307" s="1"/>
+      <c r="L307" s="1"/>
+      <c r="M307" s="1"/>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A308" s="1"/>
+      <c r="B308" s="1"/>
+      <c r="C308" s="1"/>
+      <c r="D308" s="1"/>
+      <c r="E308" s="1"/>
+      <c r="F308" s="1"/>
+      <c r="G308" s="1"/>
+      <c r="H308" s="1"/>
+      <c r="I308" s="1"/>
+      <c r="J308" s="1"/>
+      <c r="K308" s="1"/>
+      <c r="L308" s="1"/>
+      <c r="M308" s="1"/>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A309" s="1"/>
+      <c r="B309" s="1"/>
+      <c r="C309" s="1"/>
+      <c r="D309" s="1"/>
+      <c r="E309" s="1"/>
+      <c r="F309" s="1"/>
+      <c r="G309" s="1"/>
+      <c r="H309" s="1"/>
+      <c r="I309" s="1"/>
+      <c r="J309" s="1"/>
+      <c r="K309" s="1"/>
+      <c r="L309" s="1"/>
+      <c r="M309" s="1"/>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A310" s="1"/>
+      <c r="B310" s="1"/>
+      <c r="C310" s="1"/>
+      <c r="D310" s="1"/>
+      <c r="E310" s="1"/>
+      <c r="F310" s="1"/>
+      <c r="G310" s="1"/>
+      <c r="H310" s="1"/>
+      <c r="I310" s="1"/>
+      <c r="J310" s="1"/>
+      <c r="K310" s="1"/>
+      <c r="L310" s="1"/>
+      <c r="M310" s="1"/>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A311" s="1"/>
+      <c r="B311" s="1"/>
+      <c r="C311" s="1"/>
+      <c r="D311" s="1"/>
+      <c r="E311" s="1"/>
+      <c r="F311" s="1"/>
+      <c r="G311" s="1"/>
+      <c r="H311" s="1"/>
+      <c r="I311" s="1"/>
+      <c r="J311" s="1"/>
+      <c r="K311" s="1"/>
+      <c r="L311" s="1"/>
+      <c r="M311" s="1"/>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A312" s="1"/>
+      <c r="B312" s="1"/>
+      <c r="C312" s="1"/>
+      <c r="D312" s="1"/>
+      <c r="E312" s="1"/>
+      <c r="F312" s="1"/>
+      <c r="G312" s="1"/>
+      <c r="H312" s="1"/>
+      <c r="I312" s="1"/>
+      <c r="J312" s="1"/>
+      <c r="K312" s="1"/>
+      <c r="L312" s="1"/>
+      <c r="M312" s="1"/>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A313" s="1"/>
+      <c r="B313" s="1"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
+      <c r="E313" s="1"/>
+      <c r="F313" s="1"/>
+      <c r="G313" s="1"/>
+      <c r="H313" s="1"/>
+      <c r="I313" s="1"/>
+      <c r="J313" s="1"/>
+      <c r="K313" s="1"/>
+      <c r="L313" s="1"/>
+      <c r="M313" s="1"/>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A314" s="1"/>
+      <c r="B314" s="1"/>
+      <c r="C314" s="1"/>
+      <c r="D314" s="1"/>
+      <c r="E314" s="1"/>
+      <c r="F314" s="1"/>
+      <c r="G314" s="1"/>
+      <c r="H314" s="1"/>
+      <c r="I314" s="1"/>
+      <c r="J314" s="1"/>
+      <c r="K314" s="1"/>
+      <c r="L314" s="1"/>
+      <c r="M314" s="1"/>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A315" s="1"/>
+      <c r="B315" s="1"/>
+      <c r="C315" s="1"/>
+      <c r="D315" s="1"/>
+      <c r="E315" s="1"/>
+      <c r="F315" s="1"/>
+      <c r="G315" s="1"/>
+      <c r="H315" s="1"/>
+      <c r="I315" s="1"/>
+      <c r="J315" s="1"/>
+      <c r="K315" s="1"/>
+      <c r="L315" s="1"/>
+      <c r="M315" s="1"/>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A316" s="1"/>
+      <c r="B316" s="1"/>
+      <c r="C316" s="1"/>
+      <c r="D316" s="1"/>
+      <c r="E316" s="1"/>
+      <c r="F316" s="1"/>
+      <c r="G316" s="1"/>
+      <c r="H316" s="1"/>
+      <c r="I316" s="1"/>
+      <c r="J316" s="1"/>
+      <c r="K316" s="1"/>
+      <c r="L316" s="1"/>
+      <c r="M316" s="1"/>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A317" s="1"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1"/>
+      <c r="E317" s="1"/>
+      <c r="F317" s="1"/>
+      <c r="G317" s="1"/>
+      <c r="H317" s="1"/>
+      <c r="I317" s="1"/>
+      <c r="J317" s="1"/>
+      <c r="K317" s="1"/>
+      <c r="L317" s="1"/>
+      <c r="M317" s="1"/>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A318" s="1"/>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
+      <c r="D318" s="1"/>
+      <c r="E318" s="1"/>
+      <c r="F318" s="1"/>
+      <c r="G318" s="1"/>
+      <c r="H318" s="1"/>
+      <c r="I318" s="1"/>
+      <c r="J318" s="1"/>
+      <c r="K318" s="1"/>
+      <c r="L318" s="1"/>
+      <c r="M318" s="1"/>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A319" s="1"/>
+      <c r="B319" s="1"/>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1"/>
+      <c r="E319" s="1"/>
+      <c r="F319" s="1"/>
+      <c r="G319" s="1"/>
+      <c r="H319" s="1"/>
+      <c r="I319" s="1"/>
+      <c r="J319" s="1"/>
+      <c r="K319" s="1"/>
+      <c r="L319" s="1"/>
+      <c r="M319" s="1"/>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A320" s="1"/>
+      <c r="B320" s="1"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
+      <c r="E320" s="1"/>
+      <c r="F320" s="1"/>
+      <c r="G320" s="1"/>
+      <c r="H320" s="1"/>
+      <c r="I320" s="1"/>
+      <c r="J320" s="1"/>
+      <c r="K320" s="1"/>
+      <c r="L320" s="1"/>
+      <c r="M320" s="1"/>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A321" s="1"/>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1"/>
+      <c r="E321" s="1"/>
+      <c r="F321" s="1"/>
+      <c r="G321" s="1"/>
+      <c r="H321" s="1"/>
+      <c r="I321" s="1"/>
+      <c r="J321" s="1"/>
+      <c r="K321" s="1"/>
+      <c r="L321" s="1"/>
+      <c r="M321" s="1"/>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A322" s="1"/>
+      <c r="B322" s="1"/>
+      <c r="C322" s="1"/>
+      <c r="D322" s="1"/>
+      <c r="E322" s="1"/>
+      <c r="F322" s="1"/>
+      <c r="G322" s="1"/>
+      <c r="H322" s="1"/>
+      <c r="I322" s="1"/>
+      <c r="J322" s="1"/>
+      <c r="K322" s="1"/>
+      <c r="L322" s="1"/>
+      <c r="M322" s="1"/>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A323" s="1"/>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1"/>
+      <c r="E323" s="1"/>
+      <c r="F323" s="1"/>
+      <c r="G323" s="1"/>
+      <c r="H323" s="1"/>
+      <c r="I323" s="1"/>
+      <c r="J323" s="1"/>
+      <c r="K323" s="1"/>
+      <c r="L323" s="1"/>
+      <c r="M323" s="1"/>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A324" s="1"/>
+      <c r="B324" s="1"/>
+      <c r="C324" s="1"/>
+      <c r="D324" s="1"/>
+      <c r="E324" s="1"/>
+      <c r="F324" s="1"/>
+      <c r="G324" s="1"/>
+      <c r="H324" s="1"/>
+      <c r="I324" s="1"/>
+      <c r="J324" s="1"/>
+      <c r="K324" s="1"/>
+      <c r="L324" s="1"/>
+      <c r="M324" s="1"/>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A325" s="1"/>
+      <c r="B325" s="1"/>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1"/>
+      <c r="E325" s="1"/>
+      <c r="F325" s="1"/>
+      <c r="G325" s="1"/>
+      <c r="H325" s="1"/>
+      <c r="I325" s="1"/>
+      <c r="J325" s="1"/>
+      <c r="K325" s="1"/>
+      <c r="L325" s="1"/>
+      <c r="M325" s="1"/>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A326" s="1"/>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
+      <c r="D326" s="1"/>
+      <c r="E326" s="1"/>
+      <c r="F326" s="1"/>
+      <c r="G326" s="1"/>
+      <c r="H326" s="1"/>
+      <c r="I326" s="1"/>
+      <c r="J326" s="1"/>
+      <c r="K326" s="1"/>
+      <c r="L326" s="1"/>
+      <c r="M326" s="1"/>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A327" s="1"/>
+      <c r="B327" s="1"/>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
+      <c r="E327" s="1"/>
+      <c r="F327" s="1"/>
+      <c r="G327" s="1"/>
+      <c r="H327" s="1"/>
+      <c r="I327" s="1"/>
+      <c r="J327" s="1"/>
+      <c r="K327" s="1"/>
+      <c r="L327" s="1"/>
+      <c r="M327" s="1"/>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A328" s="1"/>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
+      <c r="D328" s="1"/>
+      <c r="E328" s="1"/>
+      <c r="F328" s="1"/>
+      <c r="G328" s="1"/>
+      <c r="H328" s="1"/>
+      <c r="I328" s="1"/>
+      <c r="J328" s="1"/>
+      <c r="K328" s="1"/>
+      <c r="L328" s="1"/>
+      <c r="M328" s="1"/>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A329" s="1"/>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1"/>
+      <c r="E329" s="1"/>
+      <c r="F329" s="1"/>
+      <c r="G329" s="1"/>
+      <c r="H329" s="1"/>
+      <c r="I329" s="1"/>
+      <c r="J329" s="1"/>
+      <c r="K329" s="1"/>
+      <c r="L329" s="1"/>
+      <c r="M329" s="1"/>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A330" s="1"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
+      <c r="D330" s="1"/>
+      <c r="E330" s="1"/>
+      <c r="F330" s="1"/>
+      <c r="G330" s="1"/>
+      <c r="H330" s="1"/>
+      <c r="I330" s="1"/>
+      <c r="J330" s="1"/>
+      <c r="K330" s="1"/>
+      <c r="L330" s="1"/>
+      <c r="M330" s="1"/>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A331" s="1"/>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1"/>
+      <c r="E331" s="1"/>
+      <c r="F331" s="1"/>
+      <c r="G331" s="1"/>
+      <c r="H331" s="1"/>
+      <c r="I331" s="1"/>
+      <c r="J331" s="1"/>
+      <c r="K331" s="1"/>
+      <c r="L331" s="1"/>
+      <c r="M331" s="1"/>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A332" s="1"/>
+      <c r="B332" s="1"/>
+      <c r="C332" s="1"/>
+      <c r="D332" s="1"/>
+      <c r="E332" s="1"/>
+      <c r="F332" s="1"/>
+      <c r="G332" s="1"/>
+      <c r="H332" s="1"/>
+      <c r="I332" s="1"/>
+      <c r="J332" s="1"/>
+      <c r="K332" s="1"/>
+      <c r="L332" s="1"/>
+      <c r="M332" s="1"/>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A333" s="1"/>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1"/>
+      <c r="E333" s="1"/>
+      <c r="F333" s="1"/>
+      <c r="G333" s="1"/>
+      <c r="H333" s="1"/>
+      <c r="I333" s="1"/>
+      <c r="J333" s="1"/>
+      <c r="K333" s="1"/>
+      <c r="L333" s="1"/>
+      <c r="M333" s="1"/>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A334" s="1"/>
+      <c r="B334" s="1"/>
+      <c r="C334" s="1"/>
+      <c r="D334" s="1"/>
+      <c r="E334" s="1"/>
+      <c r="F334" s="1"/>
+      <c r="G334" s="1"/>
+      <c r="H334" s="1"/>
+      <c r="I334" s="1"/>
+      <c r="J334" s="1"/>
+      <c r="K334" s="1"/>
+      <c r="L334" s="1"/>
+      <c r="M334" s="1"/>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A335" s="1"/>
+      <c r="B335" s="1"/>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1"/>
+      <c r="E335" s="1"/>
+      <c r="F335" s="1"/>
+      <c r="G335" s="1"/>
+      <c r="H335" s="1"/>
+      <c r="I335" s="1"/>
+      <c r="J335" s="1"/>
+      <c r="K335" s="1"/>
+      <c r="L335" s="1"/>
+      <c r="M335" s="1"/>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A336" s="1"/>
+      <c r="B336" s="1"/>
+      <c r="C336" s="1"/>
+      <c r="D336" s="1"/>
+      <c r="E336" s="1"/>
+      <c r="F336" s="1"/>
+      <c r="G336" s="1"/>
+      <c r="H336" s="1"/>
+      <c r="I336" s="1"/>
+      <c r="J336" s="1"/>
+      <c r="K336" s="1"/>
+      <c r="L336" s="1"/>
+      <c r="M336" s="1"/>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A337" s="1"/>
+      <c r="B337" s="1"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1"/>
+      <c r="E337" s="1"/>
+      <c r="F337" s="1"/>
+      <c r="G337" s="1"/>
+      <c r="H337" s="1"/>
+      <c r="I337" s="1"/>
+      <c r="J337" s="1"/>
+      <c r="K337" s="1"/>
+      <c r="L337" s="1"/>
+      <c r="M337" s="1"/>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A338" s="1"/>
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
+      <c r="E338" s="1"/>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
+      <c r="H338" s="1"/>
+      <c r="I338" s="1"/>
+      <c r="J338" s="1"/>
+      <c r="K338" s="1"/>
+      <c r="L338" s="1"/>
+      <c r="M338" s="1"/>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A339" s="1"/>
+      <c r="B339" s="1"/>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1"/>
+      <c r="E339" s="1"/>
+      <c r="F339" s="1"/>
+      <c r="G339" s="1"/>
+      <c r="H339" s="1"/>
+      <c r="I339" s="1"/>
+      <c r="J339" s="1"/>
+      <c r="K339" s="1"/>
+      <c r="L339" s="1"/>
+      <c r="M339" s="1"/>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A340" s="1"/>
+      <c r="B340" s="1"/>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
+      <c r="E340" s="1"/>
+      <c r="F340" s="1"/>
+      <c r="G340" s="1"/>
+      <c r="H340" s="1"/>
+      <c r="I340" s="1"/>
+      <c r="J340" s="1"/>
+      <c r="K340" s="1"/>
+      <c r="L340" s="1"/>
+      <c r="M340" s="1"/>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A341" s="1"/>
+      <c r="B341" s="1"/>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1"/>
+      <c r="E341" s="1"/>
+      <c r="F341" s="1"/>
+      <c r="G341" s="1"/>
+      <c r="H341" s="1"/>
+      <c r="I341" s="1"/>
+      <c r="J341" s="1"/>
+      <c r="K341" s="1"/>
+      <c r="L341" s="1"/>
+      <c r="M341" s="1"/>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A342" s="1"/>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1"/>
+      <c r="E342" s="1"/>
+      <c r="F342" s="1"/>
+      <c r="G342" s="1"/>
+      <c r="H342" s="1"/>
+      <c r="I342" s="1"/>
+      <c r="J342" s="1"/>
+      <c r="K342" s="1"/>
+      <c r="L342" s="1"/>
+      <c r="M342" s="1"/>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A343" s="1"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1"/>
+      <c r="E343" s="1"/>
+      <c r="F343" s="1"/>
+      <c r="G343" s="1"/>
+      <c r="H343" s="1"/>
+      <c r="I343" s="1"/>
+      <c r="J343" s="1"/>
+      <c r="K343" s="1"/>
+      <c r="L343" s="1"/>
+      <c r="M343" s="1"/>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A344" s="1"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1"/>
+      <c r="E344" s="1"/>
+      <c r="F344" s="1"/>
+      <c r="G344" s="1"/>
+      <c r="H344" s="1"/>
+      <c r="I344" s="1"/>
+      <c r="J344" s="1"/>
+      <c r="K344" s="1"/>
+      <c r="L344" s="1"/>
+      <c r="M344" s="1"/>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A345" s="1"/>
+      <c r="B345" s="1"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1"/>
+      <c r="E345" s="1"/>
+      <c r="F345" s="1"/>
+      <c r="G345" s="1"/>
+      <c r="H345" s="1"/>
+      <c r="I345" s="1"/>
+      <c r="J345" s="1"/>
+      <c r="K345" s="1"/>
+      <c r="L345" s="1"/>
+      <c r="M345" s="1"/>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A346" s="1"/>
+      <c r="B346" s="1"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1"/>
+      <c r="E346" s="1"/>
+      <c r="F346" s="1"/>
+      <c r="G346" s="1"/>
+      <c r="H346" s="1"/>
+      <c r="I346" s="1"/>
+      <c r="J346" s="1"/>
+      <c r="K346" s="1"/>
+      <c r="L346" s="1"/>
+      <c r="M346" s="1"/>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A347" s="1"/>
+      <c r="B347" s="1"/>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1"/>
+      <c r="E347" s="1"/>
+      <c r="F347" s="1"/>
+      <c r="G347" s="1"/>
+      <c r="H347" s="1"/>
+      <c r="I347" s="1"/>
+      <c r="J347" s="1"/>
+      <c r="K347" s="1"/>
+      <c r="L347" s="1"/>
+      <c r="M347" s="1"/>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A348" s="1"/>
+      <c r="B348" s="1"/>
+      <c r="C348" s="1"/>
+      <c r="D348" s="1"/>
+      <c r="E348" s="1"/>
+      <c r="F348" s="1"/>
+      <c r="G348" s="1"/>
+      <c r="H348" s="1"/>
+      <c r="I348" s="1"/>
+      <c r="J348" s="1"/>
+      <c r="K348" s="1"/>
+      <c r="L348" s="1"/>
+      <c r="M348" s="1"/>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A349" s="1"/>
+      <c r="B349" s="1"/>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1"/>
+      <c r="E349" s="1"/>
+      <c r="G349" s="1"/>
+      <c r="H349" s="1"/>
+      <c r="I349" s="1"/>
+      <c r="J349" s="1"/>
+      <c r="K349" s="1"/>
+      <c r="L349" s="1"/>
+      <c r="M349" s="1"/>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A350" s="1"/>
+      <c r="B350" s="1"/>
+      <c r="C350" s="1"/>
+      <c r="D350" s="1"/>
+      <c r="E350" s="1"/>
+      <c r="G350" s="1"/>
+      <c r="H350" s="1"/>
+      <c r="I350" s="1"/>
+      <c r="J350" s="1"/>
+      <c r="K350" s="1"/>
+      <c r="L350" s="1"/>
+      <c r="M350" s="1"/>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A351" s="1"/>
+      <c r="B351" s="1"/>
+      <c r="C351" s="1"/>
+      <c r="D351" s="1"/>
+      <c r="E351" s="1"/>
+      <c r="G351" s="1"/>
+      <c r="H351" s="1"/>
+      <c r="I351" s="1"/>
+      <c r="J351" s="1"/>
+      <c r="K351" s="1"/>
+      <c r="L351" s="1"/>
+      <c r="M351" s="1"/>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A352" s="1"/>
+      <c r="B352" s="1"/>
+      <c r="C352" s="1"/>
+      <c r="D352" s="1"/>
+      <c r="E352" s="1"/>
+      <c r="G352" s="1"/>
+      <c r="H352" s="1"/>
+      <c r="I352" s="1"/>
+      <c r="J352" s="1"/>
+      <c r="K352" s="1"/>
+      <c r="M352" s="1"/>
+    </row>
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A353" s="1"/>
+      <c r="B353" s="1"/>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
+      <c r="E353" s="1"/>
+      <c r="G353" s="1"/>
+      <c r="H353" s="1"/>
+      <c r="I353" s="1"/>
+      <c r="J353" s="1"/>
+      <c r="K353" s="1"/>
+      <c r="M353" s="1"/>
+    </row>
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A354" s="1"/>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
+      <c r="E354" s="1"/>
+      <c r="G354" s="1"/>
+      <c r="H354" s="1"/>
+      <c r="I354" s="1"/>
+      <c r="J354" s="1"/>
+      <c r="K354" s="1"/>
+      <c r="M354" s="1"/>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A355" s="1"/>
+      <c r="B355" s="1"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="1"/>
+      <c r="E355" s="1"/>
+      <c r="G355" s="1"/>
+      <c r="I355" s="1"/>
+      <c r="J355" s="1"/>
+      <c r="K355" s="1"/>
+      <c r="M355" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/final_kw_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07B9B60-EB7A-6D4F-9652-48DC32957816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D079B0-C23E-874B-9DD4-31510045D17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17540" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="360">
   <si>
     <t>DIABETES</t>
   </si>
@@ -1030,12 +1030,6 @@
     <t>CANCERS KEYWORDS</t>
   </si>
   <si>
-    <t>RESPIRATORY KEWORDS</t>
-  </si>
-  <si>
-    <t>CEREBROVASCULAR ACCIDENT</t>
-  </si>
-  <si>
     <t>SUBDURAL HEMATOMA</t>
   </si>
   <si>
@@ -1091,6 +1085,42 @@
   </si>
   <si>
     <t>HEP C</t>
+  </si>
+  <si>
+    <t>RESPIRATORY KEYWORDS</t>
+  </si>
+  <si>
+    <t>INTERNAL KEYWORDS</t>
+  </si>
+  <si>
+    <t>NATURAL</t>
+  </si>
+  <si>
+    <t>ILLNESS</t>
+  </si>
+  <si>
+    <t>ACCIDENTAL KEYWORDS</t>
+  </si>
+  <si>
+    <t>ACCIDENT</t>
+  </si>
+  <si>
+    <t>ACCIDENTAL</t>
+  </si>
+  <si>
+    <t>UNINTENTIONAL</t>
+  </si>
+  <si>
+    <t>UNINTENDED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEREBRAL VASCULAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEREBRO VASCULAR </t>
+  </si>
+  <si>
+    <t>CEREBROVASCULAR</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1169,7 +1199,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -16164,24 +16193,25 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEE812F-4599-D14A-8994-D04F411E7319}">
-  <dimension ref="A1:N355"/>
+  <dimension ref="A1:O355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="22.1640625" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="24.83203125" customWidth="1"/>
-    <col min="10" max="10" width="35.33203125" customWidth="1"/>
-    <col min="11" max="11" width="37.6640625" customWidth="1"/>
-    <col min="12" max="12" width="42.1640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="7" max="7" width="36.6640625" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="35.33203125" customWidth="1"/>
+    <col min="10" max="10" width="37.6640625" customWidth="1"/>
+    <col min="11" max="12" width="42.1640625" customWidth="1"/>
     <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="23.33203125" customWidth="1"/>
+    <col min="14" max="14" width="16.33203125" customWidth="1"/>
+    <col min="15" max="15" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>220</v>
       </c>
@@ -16197,33 +16227,38 @@
       <c r="E1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>221</v>
+      <c r="F1" s="4" t="s">
+        <v>326</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="K1" s="4" t="s">
         <v>311</v>
       </c>
+      <c r="K1" s="6" t="s">
+        <v>345</v>
+      </c>
       <c r="L1" s="6" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="O1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>219</v>
       </c>
@@ -16237,35 +16272,40 @@
         <v>263</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>212</v>
+        <v>155</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
         <v>217</v>
       </c>
+      <c r="G2" t="s">
+        <v>270</v>
+      </c>
       <c r="H2" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="I2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J2" t="s">
         <v>242</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>216</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>353</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="N2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>213</v>
       </c>
@@ -16279,35 +16319,40 @@
         <v>271</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="1" t="s">
         <v>210</v>
       </c>
+      <c r="G3" t="s">
+        <v>335</v>
+      </c>
       <c r="H3" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="I3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J3" t="s">
         <v>244</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>198</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
@@ -16321,35 +16366,37 @@
         <v>287</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>175</v>
+        <v>51</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="G4" t="s">
+        <v>336</v>
+      </c>
       <c r="H4" t="s">
-        <v>338</v>
+        <v>272</v>
       </c>
       <c r="I4" t="s">
-        <v>272</v>
-      </c>
-      <c r="J4" t="s">
         <v>288</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>15</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>355</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>202</v>
       </c>
@@ -16363,33 +16410,35 @@
         <v>246</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>155</v>
+        <v>324</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H5" t="s">
+        <v>330</v>
+      </c>
+      <c r="I5" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="H5" t="s">
-        <v>204</v>
-      </c>
-      <c r="I5" t="s">
-        <v>332</v>
-      </c>
-      <c r="J5" t="s">
-        <v>187</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>196</v>
       </c>
@@ -16403,33 +16452,33 @@
         <v>249</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>152</v>
+        <v>325</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I6" t="s">
+        <v>181</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" t="s">
-        <v>261</v>
-      </c>
-      <c r="J6" t="s">
-        <v>181</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>192</v>
       </c>
@@ -16440,34 +16489,32 @@
       <c r="D7" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7" t="s">
+        <v>337</v>
+      </c>
+      <c r="H7" t="s">
+        <v>331</v>
+      </c>
+      <c r="I7" t="s">
+        <v>357</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H7" t="s">
-        <v>339</v>
-      </c>
-      <c r="I7" t="s">
-        <v>333</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>188</v>
       </c>
@@ -16478,32 +16525,30 @@
       <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>146</v>
-      </c>
+      <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G8" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" t="s">
+        <v>332</v>
+      </c>
+      <c r="I8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H8" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" t="s">
-        <v>334</v>
-      </c>
-      <c r="J8" t="s">
-        <v>150</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>185</v>
       </c>
@@ -16511,32 +16556,30 @@
       <c r="C9" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>142</v>
-      </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>250</v>
+      </c>
+      <c r="H9" t="s">
+        <v>257</v>
+      </c>
+      <c r="I9" t="s">
+        <v>359</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="L9" s="7"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I9" t="s">
-        <v>257</v>
-      </c>
-      <c r="J9" t="s">
-        <v>330</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>179</v>
       </c>
@@ -16545,34 +16588,32 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>280</v>
+      </c>
+      <c r="I10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="7"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>280</v>
-      </c>
-      <c r="J10" t="s">
-        <v>253</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>176</v>
       </c>
@@ -16581,34 +16622,32 @@
         <v>174</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>137</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G11" t="s">
+        <v>264</v>
+      </c>
+      <c r="H11" t="s">
+        <v>298</v>
+      </c>
+      <c r="I11" t="s">
+        <v>243</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="7"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11" t="s">
-        <v>264</v>
-      </c>
-      <c r="I11" t="s">
-        <v>298</v>
-      </c>
-      <c r="J11" t="s">
-        <v>243</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>86</v>
       </c>
@@ -16617,34 +16656,32 @@
         <v>170</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>133</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G12" t="s">
+        <v>338</v>
+      </c>
+      <c r="H12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" t="s">
+        <v>282</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="7"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" t="s">
-        <v>340</v>
-      </c>
-      <c r="I12" t="s">
-        <v>162</v>
-      </c>
-      <c r="J12" t="s">
-        <v>282</v>
-      </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>172</v>
       </c>
@@ -16652,35 +16689,31 @@
       <c r="C13" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>131</v>
-      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" t="s">
+        <v>339</v>
+      </c>
+      <c r="H13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="L13" s="7"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H13" t="s">
-        <v>341</v>
-      </c>
-      <c r="I13" t="s">
-        <v>157</v>
-      </c>
-      <c r="J13" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>168</v>
       </c>
@@ -16689,32 +16722,30 @@
         <v>164</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="1" t="s">
-        <v>127</v>
-      </c>
+      <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="7"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
@@ -16723,32 +16754,30 @@
         <v>159</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" t="s">
+        <v>340</v>
+      </c>
+      <c r="H15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="L15" s="7"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" t="s">
-        <v>342</v>
-      </c>
-      <c r="I15" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>161</v>
       </c>
@@ -16757,30 +16786,28 @@
         <v>228</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
-        <v>325</v>
-      </c>
+      <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" t="s">
+        <v>333</v>
+      </c>
+      <c r="I16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="7"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" t="s">
-        <v>335</v>
-      </c>
-      <c r="J16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -16791,26 +16818,26 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" t="s">
+        <v>239</v>
+      </c>
+      <c r="I17" t="s">
+        <v>266</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="7"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" t="s">
-        <v>239</v>
-      </c>
-      <c r="J17" t="s">
-        <v>266</v>
-      </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -16821,26 +16848,26 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>269</v>
+      </c>
+      <c r="H18" t="s">
+        <v>238</v>
+      </c>
+      <c r="I18" t="s">
+        <v>265</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="L18" s="7"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" t="s">
-        <v>269</v>
-      </c>
-      <c r="I18" t="s">
-        <v>238</v>
-      </c>
-      <c r="J18" t="s">
-        <v>265</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -16851,26 +16878,26 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" t="s">
+        <v>278</v>
+      </c>
+      <c r="H19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="7"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" t="s">
-        <v>278</v>
-      </c>
-      <c r="I19" t="s">
-        <v>80</v>
-      </c>
-      <c r="J19" t="s">
-        <v>44</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -16881,26 +16908,26 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" t="s">
+        <v>293</v>
+      </c>
+      <c r="H20" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="L20" s="7"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" t="s">
-        <v>293</v>
-      </c>
-      <c r="I20" t="s">
-        <v>79</v>
-      </c>
-      <c r="J20" t="s">
-        <v>65</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -16910,24 +16937,27 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="G21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>149</v>
       </c>
+      <c r="G21" t="s">
+        <v>237</v>
+      </c>
       <c r="H21" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="I21" t="s">
-        <v>260</v>
-      </c>
-      <c r="J21" t="s">
         <v>75</v>
       </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="8" t="s">
+      <c r="J21" s="1"/>
+      <c r="K21" s="7" t="s">
         <v>117</v>
       </c>
+      <c r="L21" s="7"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -16937,24 +16967,27 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="G22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>145</v>
       </c>
+      <c r="G22" t="s">
+        <v>240</v>
+      </c>
       <c r="H22" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="I22" t="s">
-        <v>252</v>
-      </c>
-      <c r="J22" t="s">
         <v>57</v>
       </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="8" t="s">
+      <c r="J22" s="1"/>
+      <c r="K22" s="7" t="s">
         <v>0</v>
       </c>
+      <c r="L22" s="7"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -16964,24 +16997,27 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="G23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>126</v>
       </c>
+      <c r="G23" t="s">
+        <v>69</v>
+      </c>
       <c r="H23" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I23" t="s">
-        <v>76</v>
-      </c>
-      <c r="J23" t="s">
         <v>60</v>
       </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="8" t="s">
+      <c r="J23" s="1"/>
+      <c r="K23" s="7" t="s">
         <v>112</v>
       </c>
+      <c r="L23" s="7"/>
       <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -16991,22 +17027,25 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="G24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" t="s">
+        <v>68</v>
+      </c>
       <c r="I24" t="s">
-        <v>68</v>
-      </c>
-      <c r="J24" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="8" t="s">
-        <v>343</v>
-      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="L24" s="7"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
+      <c r="N24" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -17016,22 +17055,25 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="G25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" t="s">
+        <v>334</v>
+      </c>
       <c r="I25" t="s">
-        <v>336</v>
-      </c>
-      <c r="J25" t="s">
-        <v>331</v>
-      </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="7" t="s">
         <v>110</v>
       </c>
+      <c r="L25" s="7"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
+      <c r="N25" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -17041,18 +17083,21 @@
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="G26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="8" t="s">
+      <c r="K26" s="7" t="s">
         <v>300</v>
       </c>
+      <c r="L26" s="7"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
@@ -17062,19 +17107,21 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>113</v>
       </c>
+      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="8" t="s">
+      <c r="K27" s="7" t="s">
         <v>55</v>
       </c>
+      <c r="L27" s="7"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -17083,19 +17130,21 @@
       <c r="B28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>136</v>
       </c>
+      <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="8" t="s">
+      <c r="K28" s="7" t="s">
         <v>106</v>
       </c>
+      <c r="L28" s="7"/>
       <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
+      <c r="N28" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -17104,19 +17153,21 @@
       <c r="B29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="8" t="s">
+      <c r="K29" s="7" t="s">
         <v>267</v>
       </c>
+      <c r="L29" s="7"/>
       <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -17125,19 +17176,21 @@
       <c r="B30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="8" t="s">
+      <c r="K30" s="7" t="s">
         <v>104</v>
       </c>
+      <c r="L30" s="7"/>
       <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
+      <c r="N30" s="1" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
@@ -17146,17 +17199,17 @@
       <c r="B31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>130</v>
       </c>
+      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="8" t="s">
+      <c r="K31" s="7" t="s">
         <v>102</v>
       </c>
+      <c r="L31" s="7"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
     </row>
@@ -17167,17 +17220,17 @@
       <c r="B32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>230</v>
       </c>
+      <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="8" t="s">
+      <c r="K32" s="7" t="s">
         <v>100</v>
       </c>
+      <c r="L32" s="7"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
@@ -17193,10 +17246,10 @@
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="8" t="s">
+      <c r="K33" s="7" t="s">
         <v>37</v>
       </c>
+      <c r="L33" s="7"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
@@ -17213,10 +17266,10 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="8" t="s">
+      <c r="K34" s="7" t="s">
         <v>97</v>
       </c>
+      <c r="L34" s="7"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
     </row>
@@ -17233,10 +17286,10 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="8" t="s">
+      <c r="K35" s="7" t="s">
         <v>274</v>
       </c>
+      <c r="L35" s="7"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
     </row>
@@ -17253,10 +17306,10 @@
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="8" t="s">
+      <c r="K36" s="7" t="s">
         <v>95</v>
       </c>
+      <c r="L36" s="7"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
@@ -17273,10 +17326,10 @@
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="8" t="s">
+      <c r="K37" s="7" t="s">
         <v>268</v>
       </c>
+      <c r="L37" s="7"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
@@ -17293,10 +17346,10 @@
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="8" t="s">
-        <v>346</v>
-      </c>
+      <c r="K38" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="L38" s="7"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
@@ -17313,10 +17366,10 @@
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="8" t="s">
+      <c r="K39" s="7" t="s">
         <v>283</v>
       </c>
+      <c r="L39" s="7"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
@@ -17333,10 +17386,10 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="8" t="s">
+      <c r="K40" s="7" t="s">
         <v>33</v>
       </c>
+      <c r="L40" s="7"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
@@ -17353,10 +17406,10 @@
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="8" t="s">
+      <c r="K41" s="7" t="s">
         <v>89</v>
       </c>
+      <c r="L41" s="7"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
@@ -17373,10 +17426,10 @@
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="8" t="s">
+      <c r="K42" s="7" t="s">
         <v>302</v>
       </c>
+      <c r="L42" s="7"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
@@ -17393,10 +17446,10 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="8" t="s">
+      <c r="K43" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="L43" s="7"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
@@ -17413,10 +17466,10 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="8" t="s">
+      <c r="K44" s="7" t="s">
         <v>256</v>
       </c>
+      <c r="L44" s="7"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
     </row>
@@ -17433,11 +17486,12 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="8" t="s">
+      <c r="K45" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="L45" s="7"/>
       <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -17452,11 +17506,12 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="8" t="s">
+      <c r="K46" s="7" t="s">
         <v>84</v>
       </c>
+      <c r="L46" s="7"/>
       <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
@@ -17471,11 +17526,12 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="8" t="s">
+      <c r="K47" s="7" t="s">
         <v>48</v>
       </c>
+      <c r="L47" s="7"/>
       <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -17490,13 +17546,14 @@
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="8" t="s">
+      <c r="K48" s="7" t="s">
         <v>83</v>
       </c>
+      <c r="L48" s="7"/>
       <c r="M48" s="1"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>90</v>
       </c>
@@ -17509,13 +17566,14 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="8" t="s">
+      <c r="K49" s="7" t="s">
         <v>82</v>
       </c>
+      <c r="L49" s="7"/>
       <c r="M49" s="1"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>229</v>
       </c>
@@ -17528,13 +17586,14 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="8" t="s">
+      <c r="K50" s="7" t="s">
         <v>81</v>
       </c>
+      <c r="L50" s="7"/>
       <c r="M50" s="1"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>234</v>
       </c>
@@ -17546,13 +17605,14 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="8" t="s">
-        <v>344</v>
-      </c>
+      <c r="K51" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="L51" s="7"/>
       <c r="M51" s="1"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>235</v>
       </c>
@@ -17565,13 +17625,14 @@
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="8" t="s">
+      <c r="K52" s="7" t="s">
         <v>10</v>
       </c>
+      <c r="L52" s="7"/>
       <c r="M52" s="1"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>236</v>
       </c>
@@ -17583,13 +17644,14 @@
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="8" t="s">
+      <c r="K53" s="7" t="s">
         <v>78</v>
       </c>
+      <c r="L53" s="7"/>
       <c r="M53" s="1"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>241</v>
       </c>
@@ -17601,13 +17663,14 @@
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="8" t="s">
+      <c r="K54" s="7" t="s">
         <v>303</v>
       </c>
+      <c r="L54" s="7"/>
       <c r="M54" s="1"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>219</v>
       </c>
@@ -17620,13 +17683,14 @@
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="8" t="s">
+      <c r="K55" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="L55" s="7"/>
       <c r="M55" s="1"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>213</v>
       </c>
@@ -17639,13 +17703,14 @@
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="8" t="s">
+      <c r="K56" s="7" t="s">
         <v>30</v>
       </c>
+      <c r="L56" s="7"/>
       <c r="M56" s="1"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>188</v>
       </c>
@@ -17658,13 +17723,14 @@
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="8" t="s">
+      <c r="K57" s="7" t="s">
         <v>32</v>
       </c>
+      <c r="L57" s="7"/>
       <c r="M57" s="1"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>185</v>
       </c>
@@ -17677,13 +17743,14 @@
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="8" t="s">
+      <c r="K58" s="7" t="s">
         <v>52</v>
       </c>
+      <c r="L58" s="7"/>
       <c r="M58" s="1"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>179</v>
       </c>
@@ -17696,13 +17763,14 @@
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="8" t="s">
+      <c r="K59" s="7" t="s">
         <v>64</v>
       </c>
+      <c r="L59" s="7"/>
       <c r="M59" s="1"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>176</v>
       </c>
@@ -17715,13 +17783,14 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="8" t="s">
+      <c r="K60" s="7" t="s">
         <v>7</v>
       </c>
+      <c r="L60" s="7"/>
       <c r="M60" s="1"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="1"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>86</v>
       </c>
@@ -17734,13 +17803,14 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="8" t="s">
+      <c r="K61" s="7" t="s">
         <v>20</v>
       </c>
+      <c r="L61" s="7"/>
       <c r="M61" s="1"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="1"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>172</v>
       </c>
@@ -17753,13 +17823,14 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="8" t="s">
+      <c r="K62" s="7" t="s">
         <v>74</v>
       </c>
+      <c r="L62" s="7"/>
       <c r="M62" s="1"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>168</v>
       </c>
@@ -17772,13 +17843,14 @@
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="8" t="s">
+      <c r="K63" s="7" t="s">
         <v>73</v>
       </c>
+      <c r="L63" s="7"/>
       <c r="M63" s="1"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
@@ -17791,13 +17863,14 @@
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="8" t="s">
+      <c r="K64" s="7" t="s">
         <v>72</v>
       </c>
+      <c r="L64" s="7"/>
       <c r="M64" s="1"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="1"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>161</v>
       </c>
@@ -17810,13 +17883,14 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="8" t="s">
+      <c r="K65" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="L65" s="7"/>
       <c r="M65" s="1"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>156</v>
       </c>
@@ -17829,13 +17903,14 @@
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="8" t="s">
+      <c r="K66" s="7" t="s">
         <v>71</v>
       </c>
+      <c r="L66" s="7"/>
       <c r="M66" s="1"/>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="1"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>154</v>
       </c>
@@ -17848,13 +17923,14 @@
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="8" t="s">
+      <c r="K67" s="7" t="s">
         <v>70</v>
       </c>
+      <c r="L67" s="7"/>
       <c r="M67" s="1"/>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="1"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>153</v>
       </c>
@@ -17867,13 +17943,14 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="8" t="s">
+      <c r="K68" s="7" t="s">
         <v>67</v>
       </c>
+      <c r="L68" s="7"/>
       <c r="M68" s="1"/>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="1"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>45</v>
       </c>
@@ -17886,13 +17963,14 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="8" t="s">
+      <c r="K69" s="7" t="s">
         <v>295</v>
       </c>
+      <c r="L69" s="7"/>
       <c r="M69" s="1"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="1"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
@@ -17905,13 +17983,14 @@
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="8" t="s">
+      <c r="K70" s="7" t="s">
         <v>281</v>
       </c>
+      <c r="L70" s="7"/>
       <c r="M70" s="1"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>138</v>
       </c>
@@ -17927,8 +18006,9 @@
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>134</v>
       </c>
@@ -17944,8 +18024,9 @@
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="1"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>132</v>
       </c>
@@ -17961,8 +18042,9 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="1"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>128</v>
       </c>
@@ -17975,11 +18057,12 @@
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
+      <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="1"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>124</v>
       </c>
@@ -17995,8 +18078,9 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>121</v>
       </c>
@@ -18012,8 +18096,9 @@
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>119</v>
       </c>
@@ -18029,8 +18114,9 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>118</v>
       </c>
@@ -18046,8 +18132,9 @@
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N78" s="1"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>116</v>
       </c>
@@ -18060,11 +18147,12 @@
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
+      <c r="K79" s="2"/>
       <c r="L79" s="2"/>
       <c r="M79" s="1"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N79" s="1"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>114</v>
       </c>
@@ -18080,8 +18168,9 @@
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>111</v>
       </c>
@@ -18097,8 +18186,9 @@
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="1"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -18111,11 +18201,12 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
+      <c r="K82" s="2"/>
       <c r="L82" s="2"/>
       <c r="M82" s="1"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="1"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>108</v>
       </c>
@@ -18131,8 +18222,9 @@
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>107</v>
       </c>
@@ -18148,8 +18240,9 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="1"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>105</v>
       </c>
@@ -18165,8 +18258,9 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="1"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>227</v>
       </c>
@@ -18182,8 +18276,9 @@
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -18199,8 +18294,9 @@
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="1"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>103</v>
       </c>
@@ -18216,8 +18312,9 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="1"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>101</v>
       </c>
@@ -18233,8 +18330,9 @@
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>99</v>
       </c>
@@ -18250,8 +18348,9 @@
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
@@ -18267,8 +18366,9 @@
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="1"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>96</v>
       </c>
@@ -18284,8 +18384,9 @@
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="1"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -18301,8 +18402,9 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="1"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -18318,8 +18420,9 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="1"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>91</v>
       </c>
@@ -18335,8 +18438,9 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="1"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>90</v>
       </c>
@@ -18352,8 +18456,9 @@
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="1"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>229</v>
       </c>
@@ -18369,8 +18474,9 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="1"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -18384,8 +18490,9 @@
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="1"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -18399,8 +18506,9 @@
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="1"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -18414,8 +18522,9 @@
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
       <c r="M100" s="1"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="1"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -18429,8 +18538,9 @@
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="1"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -18444,8 +18554,9 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N102" s="1"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -18459,8 +18570,9 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N103" s="1"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -18474,8 +18586,9 @@
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N104" s="1"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -18489,8 +18602,9 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N105" s="1"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -18504,8 +18618,9 @@
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N106" s="1"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -18519,8 +18634,9 @@
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N107" s="1"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -18534,8 +18650,9 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N108" s="1"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -18549,8 +18666,9 @@
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N109" s="1"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -18564,8 +18682,9 @@
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
       <c r="M110" s="1"/>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N110" s="1"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -18579,8 +18698,9 @@
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
       <c r="M111" s="1"/>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N111" s="1"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -18594,8 +18714,9 @@
       <c r="K112" s="1"/>
       <c r="L112" s="1"/>
       <c r="M112" s="1"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N112" s="1"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -18609,8 +18730,9 @@
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
       <c r="M113" s="1"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N113" s="1"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -18624,8 +18746,9 @@
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N114" s="1"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -18639,8 +18762,9 @@
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N115" s="1"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -18654,8 +18778,9 @@
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
       <c r="M116" s="1"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N116" s="1"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -18669,8 +18794,9 @@
       <c r="K117" s="1"/>
       <c r="L117" s="1"/>
       <c r="M117" s="1"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N117" s="1"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -18684,8 +18810,9 @@
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N118" s="1"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -18699,8 +18826,9 @@
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N119" s="1"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -18714,8 +18842,9 @@
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N120" s="1"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -18729,8 +18858,9 @@
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N121" s="1"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -18744,8 +18874,9 @@
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N122" s="1"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -18759,8 +18890,9 @@
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
       <c r="M123" s="1"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N123" s="1"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -18774,8 +18906,9 @@
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N124" s="1"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -18789,8 +18922,9 @@
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N125" s="1"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -18804,8 +18938,9 @@
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N126" s="1"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -18819,8 +18954,9 @@
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N127" s="1"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -18834,8 +18970,9 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="1"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N128" s="1"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -18849,8 +18986,9 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="1"/>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N129" s="1"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -18864,8 +19002,9 @@
       <c r="K130" s="1"/>
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N130" s="1"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -18879,8 +19018,9 @@
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N131" s="1"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -18894,8 +19034,9 @@
       <c r="K132" s="1"/>
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N132" s="1"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -18909,8 +19050,9 @@
       <c r="K133" s="1"/>
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N133" s="1"/>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -18924,8 +19066,9 @@
       <c r="K134" s="1"/>
       <c r="L134" s="1"/>
       <c r="M134" s="1"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N134" s="1"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -18939,8 +19082,9 @@
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="1"/>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N135" s="1"/>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -18954,8 +19098,9 @@
       <c r="K136" s="1"/>
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N136" s="1"/>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -18969,8 +19114,9 @@
       <c r="K137" s="1"/>
       <c r="L137" s="1"/>
       <c r="M137" s="1"/>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N137" s="1"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -18984,8 +19130,9 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="1"/>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N138" s="1"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -18999,8 +19146,9 @@
       <c r="K139" s="1"/>
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N139" s="1"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -19014,8 +19162,9 @@
       <c r="K140" s="1"/>
       <c r="L140" s="1"/>
       <c r="M140" s="1"/>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N140" s="1"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -19029,8 +19178,9 @@
       <c r="K141" s="1"/>
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N141" s="1"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -19044,8 +19194,9 @@
       <c r="K142" s="1"/>
       <c r="L142" s="1"/>
       <c r="M142" s="1"/>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N142" s="1"/>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -19059,8 +19210,9 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="1"/>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N143" s="1"/>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -19074,8 +19226,9 @@
       <c r="K144" s="1"/>
       <c r="L144" s="1"/>
       <c r="M144" s="1"/>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N144" s="1"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -19089,8 +19242,9 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N145" s="1"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -19104,8 +19258,9 @@
       <c r="K146" s="1"/>
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N146" s="1"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -19119,8 +19274,9 @@
       <c r="K147" s="1"/>
       <c r="L147" s="1"/>
       <c r="M147" s="1"/>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N147" s="1"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -19134,8 +19290,9 @@
       <c r="K148" s="1"/>
       <c r="L148" s="1"/>
       <c r="M148" s="1"/>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N148" s="1"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -19149,8 +19306,9 @@
       <c r="K149" s="1"/>
       <c r="L149" s="1"/>
       <c r="M149" s="1"/>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N149" s="1"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -19164,8 +19322,9 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="1"/>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N150" s="1"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -19179,8 +19338,9 @@
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N151" s="1"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -19194,8 +19354,9 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="1"/>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N152" s="1"/>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -19209,8 +19370,9 @@
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N153" s="1"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -19224,8 +19386,9 @@
       <c r="K154" s="1"/>
       <c r="L154" s="1"/>
       <c r="M154" s="1"/>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N154" s="1"/>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -19239,8 +19402,9 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="1"/>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N155" s="1"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -19254,8 +19418,9 @@
       <c r="K156" s="1"/>
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N156" s="1"/>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -19269,8 +19434,9 @@
       <c r="K157" s="1"/>
       <c r="L157" s="1"/>
       <c r="M157" s="1"/>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N157" s="1"/>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -19284,8 +19450,9 @@
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="1"/>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N158" s="1"/>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -19299,8 +19466,9 @@
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N159" s="1"/>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -19314,8 +19482,9 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N160" s="1"/>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -19329,8 +19498,9 @@
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N161" s="1"/>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -19344,8 +19514,9 @@
       <c r="K162" s="1"/>
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N162" s="1"/>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -19359,8 +19530,9 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N163" s="1"/>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -19374,8 +19546,9 @@
       <c r="K164" s="1"/>
       <c r="L164" s="1"/>
       <c r="M164" s="1"/>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N164" s="1"/>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -19389,8 +19562,9 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="1"/>
-    </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N165" s="1"/>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -19404,8 +19578,9 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="1"/>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N166" s="1"/>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -19419,8 +19594,9 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="1"/>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N167" s="1"/>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -19434,8 +19610,9 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="1"/>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N168" s="1"/>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -19449,8 +19626,9 @@
       <c r="K169" s="1"/>
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N169" s="1"/>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -19464,8 +19642,9 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="1"/>
-    </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N170" s="1"/>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -19479,8 +19658,9 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="1"/>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N171" s="1"/>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -19494,8 +19674,9 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="1"/>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N172" s="1"/>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -19509,8 +19690,9 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N173" s="1"/>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -19524,8 +19706,9 @@
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
       <c r="M174" s="1"/>
-    </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N174" s="1"/>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -19539,8 +19722,9 @@
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
       <c r="M175" s="1"/>
-    </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N175" s="1"/>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -19554,8 +19738,9 @@
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N176" s="1"/>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -19569,8 +19754,9 @@
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N177" s="1"/>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -19584,8 +19770,9 @@
       <c r="K178" s="1"/>
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N178" s="1"/>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -19599,8 +19786,9 @@
       <c r="K179" s="1"/>
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N179" s="1"/>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -19614,8 +19802,9 @@
       <c r="K180" s="1"/>
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N180" s="1"/>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -19629,8 +19818,9 @@
       <c r="K181" s="1"/>
       <c r="L181" s="1"/>
       <c r="M181" s="1"/>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N181" s="1"/>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -19644,8 +19834,9 @@
       <c r="K182" s="1"/>
       <c r="L182" s="1"/>
       <c r="M182" s="1"/>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N182" s="1"/>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -19659,8 +19850,9 @@
       <c r="K183" s="1"/>
       <c r="L183" s="1"/>
       <c r="M183" s="1"/>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N183" s="1"/>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -19674,8 +19866,9 @@
       <c r="K184" s="1"/>
       <c r="L184" s="1"/>
       <c r="M184" s="1"/>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N184" s="1"/>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -19689,8 +19882,9 @@
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
       <c r="M185" s="1"/>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N185" s="1"/>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -19704,8 +19898,9 @@
       <c r="K186" s="1"/>
       <c r="L186" s="1"/>
       <c r="M186" s="1"/>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N186" s="1"/>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -19719,8 +19914,9 @@
       <c r="K187" s="1"/>
       <c r="L187" s="1"/>
       <c r="M187" s="1"/>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N187" s="1"/>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -19734,8 +19930,9 @@
       <c r="K188" s="1"/>
       <c r="L188" s="1"/>
       <c r="M188" s="1"/>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N188" s="1"/>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -19749,8 +19946,9 @@
       <c r="K189" s="1"/>
       <c r="L189" s="1"/>
       <c r="M189" s="1"/>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N189" s="1"/>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -19764,8 +19962,9 @@
       <c r="K190" s="1"/>
       <c r="L190" s="1"/>
       <c r="M190" s="1"/>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N190" s="1"/>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -19779,8 +19978,9 @@
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
       <c r="M191" s="1"/>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N191" s="1"/>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -19794,8 +19994,9 @@
       <c r="K192" s="1"/>
       <c r="L192" s="1"/>
       <c r="M192" s="1"/>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N192" s="1"/>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -19809,8 +20010,9 @@
       <c r="K193" s="1"/>
       <c r="L193" s="1"/>
       <c r="M193" s="1"/>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N193" s="1"/>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -19824,8 +20026,9 @@
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
       <c r="M194" s="1"/>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N194" s="1"/>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -19839,8 +20042,9 @@
       <c r="K195" s="1"/>
       <c r="L195" s="1"/>
       <c r="M195" s="1"/>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N195" s="1"/>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -19854,8 +20058,9 @@
       <c r="K196" s="1"/>
       <c r="L196" s="1"/>
       <c r="M196" s="1"/>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N196" s="1"/>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -19869,8 +20074,9 @@
       <c r="K197" s="1"/>
       <c r="L197" s="1"/>
       <c r="M197" s="1"/>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N197" s="1"/>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -19884,8 +20090,9 @@
       <c r="K198" s="1"/>
       <c r="L198" s="1"/>
       <c r="M198" s="1"/>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N198" s="1"/>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -19899,8 +20106,9 @@
       <c r="K199" s="1"/>
       <c r="L199" s="1"/>
       <c r="M199" s="1"/>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N199" s="1"/>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -19914,8 +20122,9 @@
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
       <c r="M200" s="1"/>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N200" s="1"/>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -19929,8 +20138,9 @@
       <c r="K201" s="1"/>
       <c r="L201" s="1"/>
       <c r="M201" s="1"/>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N201" s="1"/>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -19944,8 +20154,9 @@
       <c r="K202" s="1"/>
       <c r="L202" s="1"/>
       <c r="M202" s="1"/>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N202" s="1"/>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -19959,8 +20170,9 @@
       <c r="K203" s="1"/>
       <c r="L203" s="1"/>
       <c r="M203" s="1"/>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N203" s="1"/>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -19974,8 +20186,9 @@
       <c r="K204" s="1"/>
       <c r="L204" s="1"/>
       <c r="M204" s="1"/>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N204" s="1"/>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -19989,8 +20202,9 @@
       <c r="K205" s="1"/>
       <c r="L205" s="1"/>
       <c r="M205" s="1"/>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N205" s="1"/>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -20004,8 +20218,9 @@
       <c r="K206" s="1"/>
       <c r="L206" s="1"/>
       <c r="M206" s="1"/>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N206" s="1"/>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -20019,8 +20234,9 @@
       <c r="K207" s="1"/>
       <c r="L207" s="1"/>
       <c r="M207" s="1"/>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N207" s="1"/>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -20034,8 +20250,9 @@
       <c r="K208" s="1"/>
       <c r="L208" s="1"/>
       <c r="M208" s="1"/>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N208" s="1"/>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -20049,8 +20266,9 @@
       <c r="K209" s="1"/>
       <c r="L209" s="1"/>
       <c r="M209" s="1"/>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N209" s="1"/>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -20064,8 +20282,9 @@
       <c r="K210" s="1"/>
       <c r="L210" s="1"/>
       <c r="M210" s="1"/>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N210" s="1"/>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -20079,8 +20298,9 @@
       <c r="K211" s="1"/>
       <c r="L211" s="1"/>
       <c r="M211" s="1"/>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N211" s="1"/>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -20094,8 +20314,9 @@
       <c r="K212" s="1"/>
       <c r="L212" s="1"/>
       <c r="M212" s="1"/>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N212" s="1"/>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -20109,8 +20330,9 @@
       <c r="K213" s="1"/>
       <c r="L213" s="1"/>
       <c r="M213" s="1"/>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N213" s="1"/>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -20124,8 +20346,9 @@
       <c r="K214" s="1"/>
       <c r="L214" s="1"/>
       <c r="M214" s="1"/>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N214" s="1"/>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -20139,8 +20362,9 @@
       <c r="K215" s="1"/>
       <c r="L215" s="1"/>
       <c r="M215" s="1"/>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N215" s="1"/>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -20154,8 +20378,9 @@
       <c r="K216" s="1"/>
       <c r="L216" s="1"/>
       <c r="M216" s="1"/>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N216" s="1"/>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -20169,8 +20394,9 @@
       <c r="K217" s="1"/>
       <c r="L217" s="1"/>
       <c r="M217" s="1"/>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N217" s="1"/>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -20184,8 +20410,9 @@
       <c r="K218" s="1"/>
       <c r="L218" s="1"/>
       <c r="M218" s="1"/>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N218" s="1"/>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -20199,8 +20426,9 @@
       <c r="K219" s="1"/>
       <c r="L219" s="1"/>
       <c r="M219" s="1"/>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N219" s="1"/>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -20214,8 +20442,9 @@
       <c r="K220" s="1"/>
       <c r="L220" s="1"/>
       <c r="M220" s="1"/>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N220" s="1"/>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -20229,8 +20458,9 @@
       <c r="K221" s="1"/>
       <c r="L221" s="1"/>
       <c r="M221" s="1"/>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N221" s="1"/>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -20244,8 +20474,9 @@
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
       <c r="M222" s="1"/>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N222" s="1"/>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -20259,8 +20490,9 @@
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
       <c r="M223" s="1"/>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N223" s="1"/>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -20274,8 +20506,9 @@
       <c r="K224" s="1"/>
       <c r="L224" s="1"/>
       <c r="M224" s="1"/>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N224" s="1"/>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -20289,8 +20522,9 @@
       <c r="K225" s="1"/>
       <c r="L225" s="1"/>
       <c r="M225" s="1"/>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N225" s="1"/>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -20304,8 +20538,9 @@
       <c r="K226" s="1"/>
       <c r="L226" s="1"/>
       <c r="M226" s="1"/>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N226" s="1"/>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -20319,8 +20554,9 @@
       <c r="K227" s="1"/>
       <c r="L227" s="1"/>
       <c r="M227" s="1"/>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N227" s="1"/>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -20334,8 +20570,9 @@
       <c r="K228" s="1"/>
       <c r="L228" s="1"/>
       <c r="M228" s="1"/>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N228" s="1"/>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -20349,8 +20586,9 @@
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
       <c r="M229" s="1"/>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N229" s="1"/>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -20364,8 +20602,9 @@
       <c r="K230" s="1"/>
       <c r="L230" s="1"/>
       <c r="M230" s="1"/>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N230" s="1"/>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -20379,8 +20618,9 @@
       <c r="K231" s="1"/>
       <c r="L231" s="1"/>
       <c r="M231" s="1"/>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N231" s="1"/>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -20394,8 +20634,9 @@
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
       <c r="M232" s="1"/>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N232" s="1"/>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -20409,8 +20650,9 @@
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
       <c r="M233" s="1"/>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N233" s="1"/>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -20424,8 +20666,9 @@
       <c r="K234" s="1"/>
       <c r="L234" s="1"/>
       <c r="M234" s="1"/>
-    </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N234" s="1"/>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -20439,8 +20682,9 @@
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
       <c r="M235" s="1"/>
-    </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N235" s="1"/>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -20454,8 +20698,9 @@
       <c r="K236" s="1"/>
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
-    </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N236" s="1"/>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -20469,8 +20714,9 @@
       <c r="K237" s="1"/>
       <c r="L237" s="1"/>
       <c r="M237" s="1"/>
-    </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N237" s="1"/>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -20484,8 +20730,9 @@
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
-    </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N238" s="1"/>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -20499,8 +20746,9 @@
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
-    </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N239" s="1"/>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -20514,8 +20762,9 @@
       <c r="K240" s="1"/>
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
-    </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N240" s="1"/>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -20529,8 +20778,9 @@
       <c r="K241" s="1"/>
       <c r="L241" s="1"/>
       <c r="M241" s="1"/>
-    </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N241" s="1"/>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -20544,8 +20794,9 @@
       <c r="K242" s="1"/>
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
-    </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N242" s="1"/>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -20559,8 +20810,9 @@
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
-    </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N243" s="1"/>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -20574,8 +20826,9 @@
       <c r="K244" s="1"/>
       <c r="L244" s="1"/>
       <c r="M244" s="1"/>
-    </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N244" s="1"/>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -20589,8 +20842,9 @@
       <c r="K245" s="1"/>
       <c r="L245" s="1"/>
       <c r="M245" s="1"/>
-    </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N245" s="1"/>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -20604,8 +20858,9 @@
       <c r="K246" s="1"/>
       <c r="L246" s="1"/>
       <c r="M246" s="1"/>
-    </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N246" s="1"/>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -20619,8 +20874,9 @@
       <c r="K247" s="1"/>
       <c r="L247" s="1"/>
       <c r="M247" s="1"/>
-    </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N247" s="1"/>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -20634,8 +20890,9 @@
       <c r="K248" s="1"/>
       <c r="L248" s="1"/>
       <c r="M248" s="1"/>
-    </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N248" s="1"/>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -20649,8 +20906,9 @@
       <c r="K249" s="1"/>
       <c r="L249" s="1"/>
       <c r="M249" s="1"/>
-    </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N249" s="1"/>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -20664,8 +20922,9 @@
       <c r="K250" s="1"/>
       <c r="L250" s="1"/>
       <c r="M250" s="1"/>
-    </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N250" s="1"/>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -20679,8 +20938,9 @@
       <c r="K251" s="1"/>
       <c r="L251" s="1"/>
       <c r="M251" s="1"/>
-    </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N251" s="1"/>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -20694,8 +20954,9 @@
       <c r="K252" s="1"/>
       <c r="L252" s="1"/>
       <c r="M252" s="1"/>
-    </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N252" s="1"/>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -20709,8 +20970,9 @@
       <c r="K253" s="1"/>
       <c r="L253" s="1"/>
       <c r="M253" s="1"/>
-    </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N253" s="1"/>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -20724,8 +20986,9 @@
       <c r="K254" s="1"/>
       <c r="L254" s="1"/>
       <c r="M254" s="1"/>
-    </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N254" s="1"/>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -20739,8 +21002,9 @@
       <c r="K255" s="1"/>
       <c r="L255" s="1"/>
       <c r="M255" s="1"/>
-    </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N255" s="1"/>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -20754,8 +21018,9 @@
       <c r="K256" s="1"/>
       <c r="L256" s="1"/>
       <c r="M256" s="1"/>
-    </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N256" s="1"/>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -20769,8 +21034,9 @@
       <c r="K257" s="1"/>
       <c r="L257" s="1"/>
       <c r="M257" s="1"/>
-    </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N257" s="1"/>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -20784,8 +21050,9 @@
       <c r="K258" s="1"/>
       <c r="L258" s="1"/>
       <c r="M258" s="1"/>
-    </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N258" s="1"/>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -20799,8 +21066,9 @@
       <c r="K259" s="1"/>
       <c r="L259" s="1"/>
       <c r="M259" s="1"/>
-    </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N259" s="1"/>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -20814,8 +21082,9 @@
       <c r="K260" s="1"/>
       <c r="L260" s="1"/>
       <c r="M260" s="1"/>
-    </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N260" s="1"/>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -20829,8 +21098,9 @@
       <c r="K261" s="1"/>
       <c r="L261" s="1"/>
       <c r="M261" s="1"/>
-    </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N261" s="1"/>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -20844,8 +21114,9 @@
       <c r="K262" s="1"/>
       <c r="L262" s="1"/>
       <c r="M262" s="1"/>
-    </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N262" s="1"/>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -20859,8 +21130,9 @@
       <c r="K263" s="1"/>
       <c r="L263" s="1"/>
       <c r="M263" s="1"/>
-    </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N263" s="1"/>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -20874,8 +21146,9 @@
       <c r="K264" s="1"/>
       <c r="L264" s="1"/>
       <c r="M264" s="1"/>
-    </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N264" s="1"/>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -20889,8 +21162,9 @@
       <c r="K265" s="1"/>
       <c r="L265" s="1"/>
       <c r="M265" s="1"/>
-    </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N265" s="1"/>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -20904,8 +21178,9 @@
       <c r="K266" s="1"/>
       <c r="L266" s="1"/>
       <c r="M266" s="1"/>
-    </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N266" s="1"/>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -20919,8 +21194,9 @@
       <c r="K267" s="1"/>
       <c r="L267" s="1"/>
       <c r="M267" s="1"/>
-    </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N267" s="1"/>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -20934,8 +21210,9 @@
       <c r="K268" s="1"/>
       <c r="L268" s="1"/>
       <c r="M268" s="1"/>
-    </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N268" s="1"/>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -20949,8 +21226,9 @@
       <c r="K269" s="1"/>
       <c r="L269" s="1"/>
       <c r="M269" s="1"/>
-    </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N269" s="1"/>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -20964,8 +21242,9 @@
       <c r="K270" s="1"/>
       <c r="L270" s="1"/>
       <c r="M270" s="1"/>
-    </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N270" s="1"/>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -20979,8 +21258,9 @@
       <c r="K271" s="1"/>
       <c r="L271" s="1"/>
       <c r="M271" s="1"/>
-    </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N271" s="1"/>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -20994,8 +21274,9 @@
       <c r="K272" s="1"/>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
-    </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N272" s="1"/>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -21009,8 +21290,9 @@
       <c r="K273" s="1"/>
       <c r="L273" s="1"/>
       <c r="M273" s="1"/>
-    </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N273" s="1"/>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -21024,8 +21306,9 @@
       <c r="K274" s="1"/>
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
-    </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N274" s="1"/>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -21039,8 +21322,9 @@
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
-    </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N275" s="1"/>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -21054,8 +21338,9 @@
       <c r="K276" s="1"/>
       <c r="L276" s="1"/>
       <c r="M276" s="1"/>
-    </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N276" s="1"/>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -21069,8 +21354,9 @@
       <c r="K277" s="1"/>
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
-    </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N277" s="1"/>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -21084,8 +21370,9 @@
       <c r="K278" s="1"/>
       <c r="L278" s="1"/>
       <c r="M278" s="1"/>
-    </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N278" s="1"/>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -21099,8 +21386,9 @@
       <c r="K279" s="1"/>
       <c r="L279" s="1"/>
       <c r="M279" s="1"/>
-    </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N279" s="1"/>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -21114,8 +21402,9 @@
       <c r="K280" s="1"/>
       <c r="L280" s="1"/>
       <c r="M280" s="1"/>
-    </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N280" s="1"/>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -21129,8 +21418,9 @@
       <c r="K281" s="1"/>
       <c r="L281" s="1"/>
       <c r="M281" s="1"/>
-    </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N281" s="1"/>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -21144,8 +21434,9 @@
       <c r="K282" s="1"/>
       <c r="L282" s="1"/>
       <c r="M282" s="1"/>
-    </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N282" s="1"/>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -21159,8 +21450,9 @@
       <c r="K283" s="1"/>
       <c r="L283" s="1"/>
       <c r="M283" s="1"/>
-    </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N283" s="1"/>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -21174,8 +21466,9 @@
       <c r="K284" s="1"/>
       <c r="L284" s="1"/>
       <c r="M284" s="1"/>
-    </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N284" s="1"/>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -21189,8 +21482,9 @@
       <c r="K285" s="1"/>
       <c r="L285" s="1"/>
       <c r="M285" s="1"/>
-    </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N285" s="1"/>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -21204,8 +21498,9 @@
       <c r="K286" s="1"/>
       <c r="L286" s="1"/>
       <c r="M286" s="1"/>
-    </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N286" s="1"/>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -21219,8 +21514,9 @@
       <c r="K287" s="1"/>
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
-    </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N287" s="1"/>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -21234,8 +21530,9 @@
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
-    </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N288" s="1"/>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -21249,8 +21546,9 @@
       <c r="K289" s="1"/>
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
-    </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N289" s="1"/>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -21264,8 +21562,9 @@
       <c r="K290" s="1"/>
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
-    </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N290" s="1"/>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -21279,8 +21578,9 @@
       <c r="K291" s="1"/>
       <c r="L291" s="1"/>
       <c r="M291" s="1"/>
-    </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N291" s="1"/>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -21294,8 +21594,9 @@
       <c r="K292" s="1"/>
       <c r="L292" s="1"/>
       <c r="M292" s="1"/>
-    </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N292" s="1"/>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -21309,8 +21610,9 @@
       <c r="K293" s="1"/>
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
-    </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N293" s="1"/>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -21324,8 +21626,9 @@
       <c r="K294" s="1"/>
       <c r="L294" s="1"/>
       <c r="M294" s="1"/>
-    </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N294" s="1"/>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -21339,8 +21642,9 @@
       <c r="K295" s="1"/>
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
-    </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N295" s="1"/>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -21354,8 +21658,9 @@
       <c r="K296" s="1"/>
       <c r="L296" s="1"/>
       <c r="M296" s="1"/>
-    </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N296" s="1"/>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -21369,8 +21674,9 @@
       <c r="K297" s="1"/>
       <c r="L297" s="1"/>
       <c r="M297" s="1"/>
-    </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N297" s="1"/>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -21384,8 +21690,9 @@
       <c r="K298" s="1"/>
       <c r="L298" s="1"/>
       <c r="M298" s="1"/>
-    </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N298" s="1"/>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -21399,8 +21706,9 @@
       <c r="K299" s="1"/>
       <c r="L299" s="1"/>
       <c r="M299" s="1"/>
-    </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N299" s="1"/>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -21414,8 +21722,9 @@
       <c r="K300" s="1"/>
       <c r="L300" s="1"/>
       <c r="M300" s="1"/>
-    </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N300" s="1"/>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -21429,8 +21738,9 @@
       <c r="K301" s="1"/>
       <c r="L301" s="1"/>
       <c r="M301" s="1"/>
-    </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N301" s="1"/>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -21444,8 +21754,9 @@
       <c r="K302" s="1"/>
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
-    </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N302" s="1"/>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -21459,8 +21770,9 @@
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
-    </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N303" s="1"/>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -21474,8 +21786,9 @@
       <c r="K304" s="1"/>
       <c r="L304" s="1"/>
       <c r="M304" s="1"/>
-    </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N304" s="1"/>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -21489,8 +21802,9 @@
       <c r="K305" s="1"/>
       <c r="L305" s="1"/>
       <c r="M305" s="1"/>
-    </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N305" s="1"/>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -21504,8 +21818,9 @@
       <c r="K306" s="1"/>
       <c r="L306" s="1"/>
       <c r="M306" s="1"/>
-    </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N306" s="1"/>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -21519,8 +21834,9 @@
       <c r="K307" s="1"/>
       <c r="L307" s="1"/>
       <c r="M307" s="1"/>
-    </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N307" s="1"/>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -21534,8 +21850,9 @@
       <c r="K308" s="1"/>
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
-    </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N308" s="1"/>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -21549,8 +21866,9 @@
       <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
-    </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N309" s="1"/>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -21564,8 +21882,9 @@
       <c r="K310" s="1"/>
       <c r="L310" s="1"/>
       <c r="M310" s="1"/>
-    </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N310" s="1"/>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -21579,8 +21898,9 @@
       <c r="K311" s="1"/>
       <c r="L311" s="1"/>
       <c r="M311" s="1"/>
-    </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N311" s="1"/>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -21594,8 +21914,9 @@
       <c r="K312" s="1"/>
       <c r="L312" s="1"/>
       <c r="M312" s="1"/>
-    </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N312" s="1"/>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -21609,8 +21930,9 @@
       <c r="K313" s="1"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
-    </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N313" s="1"/>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -21624,8 +21946,9 @@
       <c r="K314" s="1"/>
       <c r="L314" s="1"/>
       <c r="M314" s="1"/>
-    </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N314" s="1"/>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -21639,8 +21962,9 @@
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
-    </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N315" s="1"/>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -21654,8 +21978,9 @@
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
-    </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N316" s="1"/>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -21669,8 +21994,9 @@
       <c r="K317" s="1"/>
       <c r="L317" s="1"/>
       <c r="M317" s="1"/>
-    </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N317" s="1"/>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -21684,8 +22010,9 @@
       <c r="K318" s="1"/>
       <c r="L318" s="1"/>
       <c r="M318" s="1"/>
-    </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N318" s="1"/>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -21699,8 +22026,9 @@
       <c r="K319" s="1"/>
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
-    </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N319" s="1"/>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -21714,8 +22042,9 @@
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
-    </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N320" s="1"/>
+    </row>
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -21729,8 +22058,9 @@
       <c r="K321" s="1"/>
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
-    </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N321" s="1"/>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -21744,8 +22074,9 @@
       <c r="K322" s="1"/>
       <c r="L322" s="1"/>
       <c r="M322" s="1"/>
-    </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N322" s="1"/>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -21759,8 +22090,9 @@
       <c r="K323" s="1"/>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
-    </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N323" s="1"/>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -21774,8 +22106,9 @@
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
       <c r="M324" s="1"/>
-    </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N324" s="1"/>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -21789,8 +22122,9 @@
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
       <c r="M325" s="1"/>
-    </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N325" s="1"/>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -21804,8 +22138,9 @@
       <c r="K326" s="1"/>
       <c r="L326" s="1"/>
       <c r="M326" s="1"/>
-    </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N326" s="1"/>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -21819,8 +22154,9 @@
       <c r="K327" s="1"/>
       <c r="L327" s="1"/>
       <c r="M327" s="1"/>
-    </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N327" s="1"/>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -21834,8 +22170,9 @@
       <c r="K328" s="1"/>
       <c r="L328" s="1"/>
       <c r="M328" s="1"/>
-    </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N328" s="1"/>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -21849,8 +22186,9 @@
       <c r="K329" s="1"/>
       <c r="L329" s="1"/>
       <c r="M329" s="1"/>
-    </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N329" s="1"/>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -21864,8 +22202,9 @@
       <c r="K330" s="1"/>
       <c r="L330" s="1"/>
       <c r="M330" s="1"/>
-    </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N330" s="1"/>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -21879,8 +22218,9 @@
       <c r="K331" s="1"/>
       <c r="L331" s="1"/>
       <c r="M331" s="1"/>
-    </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N331" s="1"/>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -21894,8 +22234,9 @@
       <c r="K332" s="1"/>
       <c r="L332" s="1"/>
       <c r="M332" s="1"/>
-    </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N332" s="1"/>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -21909,8 +22250,9 @@
       <c r="K333" s="1"/>
       <c r="L333" s="1"/>
       <c r="M333" s="1"/>
-    </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N333" s="1"/>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -21924,8 +22266,9 @@
       <c r="K334" s="1"/>
       <c r="L334" s="1"/>
       <c r="M334" s="1"/>
-    </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N334" s="1"/>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -21939,8 +22282,9 @@
       <c r="K335" s="1"/>
       <c r="L335" s="1"/>
       <c r="M335" s="1"/>
-    </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N335" s="1"/>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -21954,8 +22298,9 @@
       <c r="K336" s="1"/>
       <c r="L336" s="1"/>
       <c r="M336" s="1"/>
-    </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N336" s="1"/>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -21969,8 +22314,9 @@
       <c r="K337" s="1"/>
       <c r="L337" s="1"/>
       <c r="M337" s="1"/>
-    </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N337" s="1"/>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -21984,8 +22330,9 @@
       <c r="K338" s="1"/>
       <c r="L338" s="1"/>
       <c r="M338" s="1"/>
-    </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N338" s="1"/>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -21999,8 +22346,9 @@
       <c r="K339" s="1"/>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
-    </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N339" s="1"/>
+    </row>
+    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -22014,8 +22362,9 @@
       <c r="K340" s="1"/>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
-    </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N340" s="1"/>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -22029,8 +22378,9 @@
       <c r="K341" s="1"/>
       <c r="L341" s="1"/>
       <c r="M341" s="1"/>
-    </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N341" s="1"/>
+    </row>
+    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -22044,8 +22394,9 @@
       <c r="K342" s="1"/>
       <c r="L342" s="1"/>
       <c r="M342" s="1"/>
-    </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N342" s="1"/>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -22059,8 +22410,9 @@
       <c r="K343" s="1"/>
       <c r="L343" s="1"/>
       <c r="M343" s="1"/>
-    </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N343" s="1"/>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -22074,8 +22426,9 @@
       <c r="K344" s="1"/>
       <c r="L344" s="1"/>
       <c r="M344" s="1"/>
-    </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N344" s="1"/>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -22089,13 +22442,13 @@
       <c r="K345" s="1"/>
       <c r="L345" s="1"/>
       <c r="M345" s="1"/>
-    </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N345" s="1"/>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
-      <c r="E346" s="1"/>
       <c r="F346" s="1"/>
       <c r="G346" s="1"/>
       <c r="H346" s="1"/>
@@ -22104,13 +22457,13 @@
       <c r="K346" s="1"/>
       <c r="L346" s="1"/>
       <c r="M346" s="1"/>
-    </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N346" s="1"/>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
-      <c r="E347" s="1"/>
       <c r="F347" s="1"/>
       <c r="G347" s="1"/>
       <c r="H347" s="1"/>
@@ -22119,13 +22472,13 @@
       <c r="K347" s="1"/>
       <c r="L347" s="1"/>
       <c r="M347" s="1"/>
-    </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N347" s="1"/>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
-      <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
       <c r="H348" s="1"/>
@@ -22134,13 +22487,14 @@
       <c r="K348" s="1"/>
       <c r="L348" s="1"/>
       <c r="M348" s="1"/>
-    </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N348" s="1"/>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
       <c r="D349" s="1"/>
-      <c r="E349" s="1"/>
+      <c r="F349" s="1"/>
       <c r="G349" s="1"/>
       <c r="H349" s="1"/>
       <c r="I349" s="1"/>
@@ -22149,12 +22503,12 @@
       <c r="L349" s="1"/>
       <c r="M349" s="1"/>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
       <c r="D350" s="1"/>
-      <c r="E350" s="1"/>
+      <c r="F350" s="1"/>
       <c r="G350" s="1"/>
       <c r="H350" s="1"/>
       <c r="I350" s="1"/>
@@ -22163,12 +22517,12 @@
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
-      <c r="E351" s="1"/>
+      <c r="F351" s="1"/>
       <c r="G351" s="1"/>
       <c r="H351" s="1"/>
       <c r="I351" s="1"/>
@@ -22177,17 +22531,16 @@
       <c r="L351" s="1"/>
       <c r="M351" s="1"/>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
-      <c r="E352" s="1"/>
+      <c r="F352" s="1"/>
       <c r="G352" s="1"/>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
       <c r="J352" s="1"/>
-      <c r="K352" s="1"/>
       <c r="M352" s="1"/>
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.2">
@@ -22195,12 +22548,11 @@
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
-      <c r="E353" s="1"/>
+      <c r="F353" s="1"/>
       <c r="G353" s="1"/>
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
-      <c r="K353" s="1"/>
       <c r="M353" s="1"/>
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.2">
@@ -22208,24 +22560,21 @@
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
-      <c r="E354" s="1"/>
+      <c r="F354" s="1"/>
       <c r="G354" s="1"/>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
-      <c r="K354" s="1"/>
       <c r="M354" s="1"/>
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
-      <c r="D355" s="1"/>
-      <c r="E355" s="1"/>
-      <c r="G355" s="1"/>
+      <c r="F355" s="1"/>
+      <c r="H355" s="1"/>
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
-      <c r="K355" s="1"/>
       <c r="M355" s="1"/>
     </row>
   </sheetData>
